--- a/workbook/Commercial_Effectiveness_Model.xlsx
+++ b/workbook/Commercial_Effectiveness_Model.xlsx
@@ -11,73 +11,73 @@
     <sheet name="1) Data Entry" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="v_scope_business">'1) Data Entry'!$G$11</definedName>
-    <definedName name="v_period_start">'1) Data Entry'!$G$12</definedName>
-    <definedName name="v_period_end">'1) Data Entry'!$G$13</definedName>
-    <definedName name="v_currency">'1) Data Entry'!$G$14</definedName>
-    <definedName name="v_revenue_basis">'1) Data Entry'!$G$15</definedName>
-    <definedName name="v_segmentation_basis">'1) Data Entry'!$G$17</definedName>
-    <definedName name="v_theory_of_buying">'1) Data Entry'!$G$18</definedName>
-    <definedName name="v_system_goal">'1) Data Entry'!$G$19</definedName>
-    <definedName name="v_revenue">'1) Data Entry'!$G$21</definedName>
-    <definedName name="v_contracts">'1) Data Entry'!$G$22</definedName>
-    <definedName name="v_plan_target">'1) Data Entry'!$G$23</definedName>
-    <definedName name="v_cost_of_revenue_amt">'1) Data Entry'!$G$24</definedName>
-    <definedName name="v_rnd_amt">'1) Data Entry'!$G$25</definedName>
-    <definedName name="v_gna_amt">'1) Data Entry'!$G$26</definedName>
-    <definedName name="v_cost_of_revenue_pct">'1) Data Entry'!$G$27</definedName>
-    <definedName name="v_rnd_pct">'1) Data Entry'!$G$28</definedName>
-    <definedName name="v_gna_pct">'1) Data Entry'!$G$29</definedName>
-    <definedName name="v_base_salary">'1) Data Entry'!$G$31</definedName>
-    <definedName name="v_load_rate">'1) Data Entry'!$G$32</definedName>
-    <definedName name="v_loaded_salary">'1) Data Entry'!$G$33</definedName>
-    <definedName name="v_trip_fare">'1) Data Entry'!$G$34</definedName>
-    <definedName name="v_trip_ground">'1) Data Entry'!$G$35</definedName>
-    <definedName name="v_trip_meals">'1) Data Entry'!$G$36</definedName>
-    <definedName name="v_trip_lodging">'1) Data Entry'!$G$37</definedName>
-    <definedName name="v_trip_days">'1) Data Entry'!$G$38</definedName>
-    <definedName name="v_trip_entertainment">'1) Data Entry'!$G$39</definedName>
-    <definedName name="v_trips_per_year">'1) Data Entry'!$G$40</definedName>
-    <definedName name="v_travel_per_salesperson">'1) Data Entry'!$G$41</definedName>
-    <definedName name="v_oh_managers">'1) Data Entry'!$G$42</definedName>
-    <definedName name="v_oh_engineers">'1) Data Entry'!$G$43</definedName>
-    <definedName name="v_oh_admin">'1) Data Entry'!$G$44</definedName>
-    <definedName name="v_oh_training">'1) Data Entry'!$G$45</definedName>
-    <definedName name="v_oh_incentives">'1) Data Entry'!$G$46</definedName>
-    <definedName name="v_sales_overhead">'1) Data Entry'!$G$47</definedName>
-    <definedName name="v_mk_people">'1) Data Entry'!$G$48</definedName>
-    <definedName name="v_mk_web">'1) Data Entry'!$G$49</definedName>
-    <definedName name="v_mk_events">'1) Data Entry'!$G$50</definedName>
-    <definedName name="v_mk_ads">'1) Data Entry'!$G$51</definedName>
-    <definedName name="v_mk_mail">'1) Data Entry'!$G$52</definedName>
-    <definedName name="v_mk_leadgen">'1) Data Entry'!$G$53</definedName>
-    <definedName name="v_mk_brand">'1) Data Entry'!$G$54</definedName>
-    <definedName name="v_mk_collateral">'1) Data Entry'!$G$55</definedName>
-    <definedName name="v_marketing">'1) Data Entry'!$G$56</definedName>
-    <definedName name="v_commissions_paid">'1) Data Entry'!$G$57</definedName>
-    <definedName name="v_sales_comp_expense">'1) Data Entry'!$G$58</definedName>
-    <definedName name="v_filled_seats">'1) Data Entry'!$G$60</definedName>
-    <definedName name="v_hires">'1) Data Entry'!$G$61</definedName>
-    <definedName name="v_departures">'1) Data Entry'!$G$62</definedName>
-    <definedName name="v_productive_salespeople">'1) Data Entry'!$G$63</definedName>
-    <definedName name="v_territory_count">'1) Data Entry'!$G$65</definedName>
-    <definedName name="v_open_territories">'1) Data Entry'!$G$66</definedName>
-    <definedName name="v_expected_yield">'1) Data Entry'!$G$67</definedName>
-    <definedName name="v_opps_won">'1) Data Entry'!$G$69</definedName>
-    <definedName name="v_opps_lost">'1) Data Entry'!$G$70</definedName>
-    <definedName name="v_win_rate">'1) Data Entry'!$G$71</definedName>
-    <definedName name="v_cycle_months">'1) Data Entry'!$G$72</definedName>
-    <definedName name="v_deal_size">'1) Data Entry'!$G$73</definedName>
-    <definedName name="v_open_opps_total">'1) Data Entry'!$G$74</definedName>
-    <definedName name="v_opportunities_load">'1) Data Entry'!$G$75</definedName>
-    <definedName name="v_opportunities_capacity">'1) Data Entry'!$G$76</definedName>
-    <definedName name="v_commission_rate">'1) Data Entry'!$G$78</definedName>
-    <definedName name="v_ramp_months">'1) Data Entry'!$G$80</definedName>
-    <definedName name="v_time_to_fill_days">'1) Data Entry'!$G$81</definedName>
-    <definedName name="v_approval_days">'1) Data Entry'!$G$82</definedName>
-    <definedName name="v_qualification_definition">'1) Data Entry'!$G$84</definedName>
-    <definedName name="v_hiring_approval_rule">'1) Data Entry'!$G$85</definedName>
-    <definedName name="v_design_authority">'1) Data Entry'!$G$86</definedName>
+    <definedName name="v_scope_business">'1) Data Entry'!$H$11</definedName>
+    <definedName name="v_period_start">'1) Data Entry'!$H$12</definedName>
+    <definedName name="v_period_end">'1) Data Entry'!$H$13</definedName>
+    <definedName name="v_currency">'1) Data Entry'!$H$14</definedName>
+    <definedName name="v_revenue_basis">'1) Data Entry'!$H$15</definedName>
+    <definedName name="v_segmentation_basis">'1) Data Entry'!$H$17</definedName>
+    <definedName name="v_theory_of_buying">'1) Data Entry'!$H$18</definedName>
+    <definedName name="v_system_goal">'1) Data Entry'!$H$19</definedName>
+    <definedName name="v_revenue">'1) Data Entry'!$H$21</definedName>
+    <definedName name="v_contracts">'1) Data Entry'!$H$22</definedName>
+    <definedName name="v_plan_target">'1) Data Entry'!$H$23</definedName>
+    <definedName name="v_cost_of_revenue_amt">'1) Data Entry'!$H$24</definedName>
+    <definedName name="v_rnd_amt">'1) Data Entry'!$H$25</definedName>
+    <definedName name="v_gna_amt">'1) Data Entry'!$H$26</definedName>
+    <definedName name="v_cost_of_revenue_pct">'1) Data Entry'!$H$27</definedName>
+    <definedName name="v_rnd_pct">'1) Data Entry'!$H$28</definedName>
+    <definedName name="v_gna_pct">'1) Data Entry'!$H$29</definedName>
+    <definedName name="v_base_salary">'1) Data Entry'!$H$31</definedName>
+    <definedName name="v_load_rate">'1) Data Entry'!$H$32</definedName>
+    <definedName name="v_loaded_salary">'1) Data Entry'!$H$33</definedName>
+    <definedName name="v_trip_fare">'1) Data Entry'!$H$34</definedName>
+    <definedName name="v_trip_ground">'1) Data Entry'!$H$35</definedName>
+    <definedName name="v_trip_meals">'1) Data Entry'!$H$36</definedName>
+    <definedName name="v_trip_lodging">'1) Data Entry'!$H$37</definedName>
+    <definedName name="v_trip_days">'1) Data Entry'!$H$38</definedName>
+    <definedName name="v_trip_entertainment">'1) Data Entry'!$H$39</definedName>
+    <definedName name="v_trips_per_year">'1) Data Entry'!$H$40</definedName>
+    <definedName name="v_travel_per_salesperson">'1) Data Entry'!$H$41</definedName>
+    <definedName name="v_oh_managers">'1) Data Entry'!$H$42</definedName>
+    <definedName name="v_oh_engineers">'1) Data Entry'!$H$43</definedName>
+    <definedName name="v_oh_admin">'1) Data Entry'!$H$44</definedName>
+    <definedName name="v_oh_training">'1) Data Entry'!$H$45</definedName>
+    <definedName name="v_oh_incentives">'1) Data Entry'!$H$46</definedName>
+    <definedName name="v_sales_overhead">'1) Data Entry'!$H$47</definedName>
+    <definedName name="v_mk_people">'1) Data Entry'!$H$48</definedName>
+    <definedName name="v_mk_web">'1) Data Entry'!$H$49</definedName>
+    <definedName name="v_mk_events">'1) Data Entry'!$H$50</definedName>
+    <definedName name="v_mk_ads">'1) Data Entry'!$H$51</definedName>
+    <definedName name="v_mk_mail">'1) Data Entry'!$H$52</definedName>
+    <definedName name="v_mk_leadgen">'1) Data Entry'!$H$53</definedName>
+    <definedName name="v_mk_brand">'1) Data Entry'!$H$54</definedName>
+    <definedName name="v_mk_collateral">'1) Data Entry'!$H$55</definedName>
+    <definedName name="v_marketing">'1) Data Entry'!$H$56</definedName>
+    <definedName name="v_commissions_paid">'1) Data Entry'!$H$57</definedName>
+    <definedName name="v_sales_comp_expense">'1) Data Entry'!$H$58</definedName>
+    <definedName name="v_filled_seats">'1) Data Entry'!$H$60</definedName>
+    <definedName name="v_hires">'1) Data Entry'!$H$61</definedName>
+    <definedName name="v_departures">'1) Data Entry'!$H$62</definedName>
+    <definedName name="v_productive_salespeople">'1) Data Entry'!$H$63</definedName>
+    <definedName name="v_territory_count">'1) Data Entry'!$H$65</definedName>
+    <definedName name="v_open_territories">'1) Data Entry'!$H$66</definedName>
+    <definedName name="v_expected_yield">'1) Data Entry'!$H$67</definedName>
+    <definedName name="v_opps_won">'1) Data Entry'!$H$69</definedName>
+    <definedName name="v_opps_lost">'1) Data Entry'!$H$70</definedName>
+    <definedName name="v_win_rate">'1) Data Entry'!$H$71</definedName>
+    <definedName name="v_cycle_months">'1) Data Entry'!$H$72</definedName>
+    <definedName name="v_deal_size">'1) Data Entry'!$H$73</definedName>
+    <definedName name="v_open_opps_total">'1) Data Entry'!$H$74</definedName>
+    <definedName name="v_opportunities_load">'1) Data Entry'!$H$75</definedName>
+    <definedName name="v_opportunities_capacity">'1) Data Entry'!$H$76</definedName>
+    <definedName name="v_commission_rate">'1) Data Entry'!$H$78</definedName>
+    <definedName name="v_ramp_months">'1) Data Entry'!$H$80</definedName>
+    <definedName name="v_time_to_fill_days">'1) Data Entry'!$H$81</definedName>
+    <definedName name="v_approval_days">'1) Data Entry'!$H$82</definedName>
+    <definedName name="v_qualification_definition">'1) Data Entry'!$H$84</definedName>
+    <definedName name="v_hiring_approval_rule">'1) Data Entry'!$H$85</definedName>
+    <definedName name="v_design_authority">'1) Data Entry'!$H$86</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'1) Data Entry'!$9:$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -743,7 +743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:E62"/>
+  <dimension ref="B2:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -956,10 +956,10 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="44.5" customHeight="1">
+    <row r="38" ht="58" customHeight="1">
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Each row on tab 1 is one entry. Its “Value used” cell (blue, outlined) is the only cell the rest of the model reads, by name. The yellow cells to its right are the ways to fill it; “Input method” chooses which one is used. Grey cells are calculated from other entries. Changing how an entry is filled never changes the model's logic.</t>
+          <t>Each row on tab 1 is one entry. Its “Value used” cell (blue, outlined) is the only cell the rest of the model reads, by name. The yellow cells to its right are the ways to fill it; “Input method” chooses which one is used. Grey cells are calculated from other entries. Changing how an entry is filled never changes the model's logic. “Why it matters” keeps the original explanation of each entry. Columns for ID, range, source, owner, where to find it, what would prove it wrong and leverage point are grouped: use the + button above the columns to show them.</t>
         </is>
       </c>
     </row>
@@ -1286,26 +1286,42 @@
         </is>
       </c>
     </row>
-    <row r="62" ht="31" customHeight="1">
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>For a sharper analysis, run the model separately for each sales channel and product line, and separate new-customer revenue from revenue from existing customers.</t>
+    <row r="63" ht="17.5" customHeight="1">
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>A few points</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="31" customHeight="1">
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>This is a general model. For a sharper analysis, run it separately for each sales channel and product line, and separate new-customer revenue from revenue from existing customers. The model can be tailored to your business.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="44.5" customHeight="1">
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>“Increase leads” is not listed as a business scenario because we consider lead generation to be a more leveraged way to conduct sales prospecting. The number of leads, how to acquire them, and how much you can invest to acquire those leads are all handled in the tactical “drill down” spreadsheets that accompany this model.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="39">
+    <mergeCell ref="B65:E65"/>
     <mergeCell ref="B37:E37"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B64:E64"/>
     <mergeCell ref="B33:E33"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B63:E63"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B35:E35"/>
     <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B62:E62"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B59:E59"/>
@@ -1341,31 +1357,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:S97"/>
+  <dimension ref="A1:T97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col hidden="1" outlineLevel="1" width="22" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="36" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col hidden="1" outlineLevel="1" width="12" customWidth="1" min="14" max="14"/>
+    <col hidden="1" outlineLevel="1" width="12" customWidth="1" min="15" max="15"/>
+    <col hidden="1" outlineLevel="1" width="34" customWidth="1" min="16" max="16"/>
+    <col hidden="1" outlineLevel="1" width="18" customWidth="1" min="17" max="17"/>
+    <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="18" max="18"/>
+    <col hidden="1" outlineLevel="1" width="36" customWidth="1" min="19" max="19"/>
+    <col hidden="1" outlineLevel="1" width="9" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1406,23 +1423,23 @@
         </is>
       </c>
       <c r="D5" s="17">
-        <f>SUMPRODUCT((F17:F86="Validated actual")*(LEN(G17:G86)&gt;0))</f>
+        <f>SUMPRODUCT((G17:G86="Validated actual")*(LEN(H17:H86)&gt;0))</f>
         <v/>
       </c>
       <c r="E5" s="17">
-        <f>SUMPRODUCT((F17:F86="Calculated")*(LEN(G17:G86)&gt;0))</f>
+        <f>SUMPRODUCT((G17:G86="Calculated")*(LEN(H17:H86)&gt;0))</f>
         <v/>
       </c>
       <c r="F5" s="17">
-        <f>SUMPRODUCT((F17:F86="Reference value")*(LEN(G17:G86)&gt;0))</f>
+        <f>SUMPRODUCT((G17:G86="Reference value")*(LEN(H17:H86)&gt;0))</f>
         <v/>
       </c>
       <c r="G5" s="17">
-        <f>SUMPRODUCT((F17:F86="Judgment")*(LEN(G17:G86)&gt;0))</f>
+        <f>SUMPRODUCT((G17:G86="Judgment")*(LEN(H17:H86)&gt;0))</f>
         <v/>
       </c>
       <c r="H5" s="17">
-        <f>SUMPRODUCT((LEN(F17:F86)&gt;0)*(LEN(G17:G86)=0)*(LEFT(F17:F86,6)&lt;&gt;"Direct"))</f>
+        <f>SUMPRODUCT((LEN(G17:G86)&gt;0)*(LEN(H17:H86)=0)*(LEFT(G17:G86,6)&lt;&gt;"Direct"))</f>
         <v/>
       </c>
     </row>
@@ -1495,75 +1512,80 @@
       </c>
       <c r="E9" s="19" t="inlineStr">
         <is>
+          <t>Why it matters (original)</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr">
+        <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="G9" s="19" t="inlineStr">
         <is>
           <t>Input method</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="H9" s="19" t="inlineStr">
         <is>
           <t>Value used</t>
         </is>
       </c>
-      <c r="H9" s="19" t="inlineStr">
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="I9" s="19" t="inlineStr">
+      <c r="J9" s="19" t="inlineStr">
         <is>
           <t>Calculated</t>
         </is>
       </c>
-      <c r="J9" s="19" t="inlineStr">
+      <c r="K9" s="19" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="K9" s="19" t="inlineStr">
+      <c r="L9" s="19" t="inlineStr">
         <is>
           <t>Leadership belief (judgment)</t>
         </is>
       </c>
-      <c r="L9" s="19" t="inlineStr">
+      <c r="M9" s="19" t="inlineStr">
+        <is>
+          <t>Belief vs value used</t>
+        </is>
+      </c>
+      <c r="N9" s="19" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="M9" s="19" t="inlineStr">
+      <c r="O9" s="19" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N9" s="19" t="inlineStr">
+      <c r="P9" s="19" t="inlineStr">
         <is>
           <t>Source or reference context</t>
         </is>
       </c>
-      <c r="O9" s="19" t="inlineStr">
+      <c r="Q9" s="19" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="P9" s="19" t="inlineStr">
+      <c r="R9" s="19" t="inlineStr">
         <is>
           <t>Where to find it</t>
         </is>
       </c>
-      <c r="Q9" s="19" t="inlineStr">
+      <c r="S9" s="19" t="inlineStr">
         <is>
           <t>What would prove it wrong</t>
         </is>
       </c>
-      <c r="R9" s="19" t="inlineStr">
-        <is>
-          <t>Belief vs value used</t>
-        </is>
-      </c>
-      <c r="S9" s="19" t="inlineStr">
+      <c r="T9" s="19" t="inlineStr">
         <is>
           <t>Leverage point</t>
         </is>
@@ -1593,6 +1615,7 @@
       <c r="Q10" s="21" t="n"/>
       <c r="R10" s="21" t="n"/>
       <c r="S10" s="21" t="n"/>
+      <c r="T10" s="21" t="n"/>
     </row>
     <row r="11" ht="31" customHeight="1">
       <c r="A11" s="11" t="n">
@@ -1613,41 +1636,42 @@
           <t>Whole company, or one channel, product line or sales motion</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr"/>
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>Direct entry</t>
         </is>
       </c>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="H11" s="24" t="inlineStr">
         <is>
           <t>Whole company</t>
         </is>
       </c>
-      <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="12" t="n"/>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="12" t="n"/>
       <c r="M11" s="12" t="n"/>
-      <c r="N11" s="12" t="inlineStr"/>
-      <c r="O11" s="12" t="inlineStr">
+      <c r="N11" s="12" t="n"/>
+      <c r="O11" s="12" t="n"/>
+      <c r="P11" s="12" t="inlineStr"/>
+      <c r="Q11" s="12" t="inlineStr">
         <is>
           <t>Sponsor</t>
         </is>
       </c>
-      <c r="P11" s="12" t="inlineStr">
+      <c r="R11" s="12" t="inlineStr">
         <is>
           <t>Sponsor decision</t>
         </is>
       </c>
-      <c r="Q11" s="12" t="inlineStr"/>
-      <c r="R11" s="12" t="n"/>
-      <c r="S11" s="11" t="n"/>
+      <c r="S11" s="12" t="inlineStr"/>
+      <c r="T11" s="11" t="n"/>
     </row>
     <row r="12" ht="31" customHeight="1">
       <c r="A12" s="11" t="n">
@@ -1668,37 +1692,38 @@
           <t>First day of the 12-month period every value describes</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr"/>
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>Direct entry</t>
         </is>
       </c>
-      <c r="G12" s="25" t="n"/>
-      <c r="H12" s="12" t="n"/>
+      <c r="H12" s="25" t="n"/>
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="12" t="n"/>
       <c r="M12" s="12" t="n"/>
-      <c r="N12" s="12" t="inlineStr"/>
-      <c r="O12" s="12" t="inlineStr">
+      <c r="N12" s="12" t="n"/>
+      <c r="O12" s="12" t="n"/>
+      <c r="P12" s="12" t="inlineStr"/>
+      <c r="Q12" s="12" t="inlineStr">
         <is>
           <t>Sponsor</t>
         </is>
       </c>
-      <c r="P12" s="12" t="inlineStr">
+      <c r="R12" s="12" t="inlineStr">
         <is>
           <t>Sponsor decision</t>
         </is>
       </c>
-      <c r="Q12" s="12" t="inlineStr"/>
-      <c r="R12" s="12" t="n"/>
-      <c r="S12" s="11" t="n"/>
+      <c r="S12" s="12" t="inlineStr"/>
+      <c r="T12" s="11" t="n"/>
     </row>
     <row r="13" ht="17.5" customHeight="1">
       <c r="A13" s="11" t="n">
@@ -1719,39 +1744,40 @@
           <t>Last day of the period</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr"/>
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>Direct entry</t>
         </is>
       </c>
-      <c r="G13" s="25" t="n"/>
-      <c r="H13" s="12" t="n"/>
+      <c r="H13" s="25" t="n"/>
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="12" t="n"/>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="12" t="n"/>
       <c r="M13" s="12" t="n"/>
-      <c r="N13" s="12" t="inlineStr"/>
-      <c r="O13" s="12" t="inlineStr">
+      <c r="N13" s="12" t="n"/>
+      <c r="O13" s="12" t="n"/>
+      <c r="P13" s="12" t="inlineStr"/>
+      <c r="Q13" s="12" t="inlineStr">
         <is>
           <t>Sponsor</t>
         </is>
       </c>
-      <c r="P13" s="12" t="inlineStr">
+      <c r="R13" s="12" t="inlineStr">
         <is>
           <t>Sponsor decision</t>
         </is>
       </c>
-      <c r="Q13" s="12" t="inlineStr"/>
-      <c r="R13" s="12" t="n"/>
-      <c r="S13" s="11" t="n"/>
-    </row>
-    <row r="14" ht="17.5" customHeight="1">
+      <c r="S13" s="12" t="inlineStr"/>
+      <c r="T13" s="11" t="n"/>
+    </row>
+    <row r="14" ht="31" customHeight="1">
       <c r="A14" s="11" t="n">
         <v>1</v>
       </c>
@@ -1770,41 +1796,42 @@
           <t>Reporting currency for every money value</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr"/>
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>Direct entry</t>
         </is>
       </c>
-      <c r="G14" s="24" t="inlineStr">
+      <c r="H14" s="24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
       <c r="J14" s="12" t="n"/>
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="12" t="n"/>
       <c r="M14" s="12" t="n"/>
-      <c r="N14" s="12" t="inlineStr"/>
-      <c r="O14" s="12" t="inlineStr">
+      <c r="N14" s="12" t="n"/>
+      <c r="O14" s="12" t="n"/>
+      <c r="P14" s="12" t="inlineStr"/>
+      <c r="Q14" s="12" t="inlineStr">
         <is>
           <t>Sponsor</t>
         </is>
       </c>
-      <c r="P14" s="12" t="inlineStr">
+      <c r="R14" s="12" t="inlineStr">
         <is>
           <t>Sponsor decision</t>
         </is>
       </c>
-      <c r="Q14" s="12" t="inlineStr"/>
-      <c r="R14" s="12" t="n"/>
-      <c r="S14" s="11" t="n"/>
+      <c r="S14" s="12" t="inlineStr"/>
+      <c r="T14" s="11" t="n"/>
     </row>
     <row r="15" ht="31" customHeight="1">
       <c r="A15" s="11" t="n">
@@ -1825,41 +1852,42 @@
           <t>Recognized revenue or bookings; every revenue value follows it</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr"/>
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>Direct entry</t>
         </is>
       </c>
-      <c r="G15" s="24" t="inlineStr">
+      <c r="H15" s="24" t="inlineStr">
         <is>
           <t>Recognized revenue</t>
         </is>
       </c>
-      <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
       <c r="L15" s="12" t="n"/>
       <c r="M15" s="12" t="n"/>
-      <c r="N15" s="12" t="inlineStr"/>
-      <c r="O15" s="12" t="inlineStr">
+      <c r="N15" s="12" t="n"/>
+      <c r="O15" s="12" t="n"/>
+      <c r="P15" s="12" t="inlineStr"/>
+      <c r="Q15" s="12" t="inlineStr">
         <is>
           <t>Sponsor</t>
         </is>
       </c>
-      <c r="P15" s="12" t="inlineStr">
+      <c r="R15" s="12" t="inlineStr">
         <is>
           <t>Sponsor decision</t>
         </is>
       </c>
-      <c r="Q15" s="12" t="inlineStr"/>
-      <c r="R15" s="12" t="n"/>
-      <c r="S15" s="11" t="n"/>
+      <c r="S15" s="12" t="inlineStr"/>
+      <c r="T15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="20" t="inlineStr">
@@ -1885,6 +1913,7 @@
       <c r="Q16" s="21" t="n"/>
       <c r="R16" s="21" t="n"/>
       <c r="S16" s="21" t="n"/>
+      <c r="T16" s="21" t="n"/>
     </row>
     <row r="17" ht="31" customHeight="1">
       <c r="A17" s="11" t="n">
@@ -1905,44 +1934,45 @@
           <t>Geography, industry, company size, named accounts, buyer problem, or a mix</t>
         </is>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr"/>
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="F17" s="26" t="inlineStr">
+      <c r="G17" s="26" t="inlineStr">
         <is>
           <t>Judgment</t>
         </is>
       </c>
-      <c r="G17" s="27">
-        <f>IF(F17="Validated actual",IF(H17="","",H17),IF(F17="Calculated",IF(I17="","",I17),IF(F17="Reference value",IF(J17="","",J17),IF(F17="Judgment",IF(K17="","",K17),""))))</f>
-        <v/>
-      </c>
-      <c r="H17" s="28" t="n"/>
-      <c r="I17" s="29" t="n"/>
-      <c r="J17" s="28" t="n"/>
+      <c r="H17" s="27">
+        <f>IF(G17="Validated actual",IF(I17="","",I17),IF(G17="Calculated",IF(J17="","",J17),IF(G17="Reference value",IF(K17="","",K17),IF(G17="Judgment",IF(L17="","",L17),""))))</f>
+        <v/>
+      </c>
+      <c r="I17" s="28" t="n"/>
+      <c r="J17" s="29" t="n"/>
       <c r="K17" s="28" t="n"/>
       <c r="L17" s="28" t="n"/>
-      <c r="M17" s="28" t="n"/>
-      <c r="N17" s="26" t="inlineStr"/>
-      <c r="O17" s="12" t="inlineStr">
+      <c r="M17" s="12" t="n"/>
+      <c r="N17" s="28" t="n"/>
+      <c r="O17" s="28" t="n"/>
+      <c r="P17" s="26" t="inlineStr"/>
+      <c r="Q17" s="12" t="inlineStr">
         <is>
           <t>Sales leader</t>
         </is>
       </c>
-      <c r="P17" s="12" t="inlineStr">
+      <c r="R17" s="12" t="inlineStr">
         <is>
           <t>Sales leader</t>
         </is>
       </c>
-      <c r="Q17" s="12" t="inlineStr">
+      <c r="S17" s="12" t="inlineStr">
         <is>
           <t>Territory results differ more within a segment than between segments</t>
         </is>
       </c>
-      <c r="R17" s="12" t="n"/>
-      <c r="S17" s="11" t="n">
+      <c r="T17" s="11" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1965,44 +1995,45 @@
           <t>The stated theory of who decides, how, and why</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr"/>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="F18" s="26" t="inlineStr">
+      <c r="G18" s="26" t="inlineStr">
         <is>
           <t>Judgment</t>
         </is>
       </c>
-      <c r="G18" s="27">
-        <f>IF(F18="Validated actual",IF(H18="","",H18),IF(F18="Calculated",IF(I18="","",I18),IF(F18="Reference value",IF(J18="","",J18),IF(F18="Judgment",IF(K18="","",K18),""))))</f>
-        <v/>
-      </c>
-      <c r="H18" s="28" t="n"/>
-      <c r="I18" s="29" t="n"/>
-      <c r="J18" s="28" t="n"/>
+      <c r="H18" s="27">
+        <f>IF(G18="Validated actual",IF(I18="","",I18),IF(G18="Calculated",IF(J18="","",J18),IF(G18="Reference value",IF(K18="","",K18),IF(G18="Judgment",IF(L18="","",L18),""))))</f>
+        <v/>
+      </c>
+      <c r="I18" s="28" t="n"/>
+      <c r="J18" s="29" t="n"/>
       <c r="K18" s="28" t="n"/>
       <c r="L18" s="28" t="n"/>
-      <c r="M18" s="28" t="n"/>
-      <c r="N18" s="26" t="inlineStr"/>
-      <c r="O18" s="12" t="inlineStr">
+      <c r="M18" s="12" t="n"/>
+      <c r="N18" s="28" t="n"/>
+      <c r="O18" s="28" t="n"/>
+      <c r="P18" s="26" t="inlineStr"/>
+      <c r="Q18" s="12" t="inlineStr">
         <is>
           <t>Sales leader</t>
         </is>
       </c>
-      <c r="P18" s="12" t="inlineStr">
+      <c r="R18" s="12" t="inlineStr">
         <is>
           <t>Sales leader</t>
         </is>
       </c>
-      <c r="Q18" s="12" t="inlineStr">
+      <c r="S18" s="12" t="inlineStr">
         <is>
           <t>Won and lost deals do not follow the stated pattern</t>
         </is>
       </c>
-      <c r="R18" s="12" t="n"/>
-      <c r="S18" s="11" t="n">
+      <c r="T18" s="11" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2025,44 +2056,45 @@
           <t>Bookings, margin, new logos, retention, or another goal</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr"/>
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="F19" s="26" t="inlineStr">
+      <c r="G19" s="26" t="inlineStr">
         <is>
           <t>Judgment</t>
         </is>
       </c>
-      <c r="G19" s="27">
-        <f>IF(F19="Validated actual",IF(H19="","",H19),IF(F19="Calculated",IF(I19="","",I19),IF(F19="Reference value",IF(J19="","",J19),IF(F19="Judgment",IF(K19="","",K19),""))))</f>
-        <v/>
-      </c>
-      <c r="H19" s="28" t="n"/>
-      <c r="I19" s="29" t="n"/>
-      <c r="J19" s="28" t="n"/>
+      <c r="H19" s="27">
+        <f>IF(G19="Validated actual",IF(I19="","",I19),IF(G19="Calculated",IF(J19="","",J19),IF(G19="Reference value",IF(K19="","",K19),IF(G19="Judgment",IF(L19="","",L19),""))))</f>
+        <v/>
+      </c>
+      <c r="I19" s="28" t="n"/>
+      <c r="J19" s="29" t="n"/>
       <c r="K19" s="28" t="n"/>
       <c r="L19" s="28" t="n"/>
-      <c r="M19" s="28" t="n"/>
-      <c r="N19" s="26" t="inlineStr"/>
-      <c r="O19" s="12" t="inlineStr">
+      <c r="M19" s="12" t="n"/>
+      <c r="N19" s="28" t="n"/>
+      <c r="O19" s="28" t="n"/>
+      <c r="P19" s="26" t="inlineStr"/>
+      <c r="Q19" s="12" t="inlineStr">
         <is>
           <t>Sales leader</t>
         </is>
       </c>
-      <c r="P19" s="12" t="inlineStr">
+      <c r="R19" s="12" t="inlineStr">
         <is>
           <t>Sponsor and sales leader</t>
         </is>
       </c>
-      <c r="Q19" s="12" t="inlineStr">
+      <c r="S19" s="12" t="inlineStr">
         <is>
           <t>Compensation and reviews reward something else</t>
         </is>
       </c>
-      <c r="R19" s="12" t="n"/>
-      <c r="S19" s="11" t="n">
+      <c r="T19" s="11" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2090,6 +2122,7 @@
       <c r="Q20" s="21" t="n"/>
       <c r="R20" s="21" t="n"/>
       <c r="S20" s="21" t="n"/>
+      <c r="T20" s="21" t="n"/>
     </row>
     <row r="21" ht="31" customHeight="1">
       <c r="A21" s="11" t="n">
@@ -2110,53 +2143,54 @@
           <t>Revenue for the period and scope, on the chosen basis</t>
         </is>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr"/>
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F21" s="26" t="inlineStr">
+      <c r="G21" s="26" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="G21" s="30">
-        <f>IF(F21="Validated actual",IF(H21="","",H21),IF(F21="Calculated",IF(I21="","",I21),IF(F21="Reference value",IF(J21="","",J21),IF(F21="Judgment",IF(K21="","",K21),""))))</f>
-        <v/>
-      </c>
-      <c r="H21" s="31" t="n">
+      <c r="H21" s="30">
+        <f>IF(G21="Validated actual",IF(I21="","",I21),IF(G21="Calculated",IF(J21="","",J21),IF(G21="Reference value",IF(K21="","",K21),IF(G21="Judgment",IF(L21="","",L21),""))))</f>
+        <v/>
+      </c>
+      <c r="I21" s="31" t="n">
         <v>25000000</v>
       </c>
-      <c r="I21" s="29" t="n"/>
-      <c r="J21" s="31" t="n"/>
+      <c r="J21" s="29" t="n"/>
       <c r="K21" s="31" t="n"/>
       <c r="L21" s="31" t="n"/>
-      <c r="M21" s="31" t="n"/>
-      <c r="N21" s="26" t="inlineStr">
+      <c r="M21" s="32">
+        <f>IF(OR(L21="",H21="",G21="Judgment"),"",IFERROR(L21/H21-1,""))</f>
+        <v/>
+      </c>
+      <c r="N21" s="31" t="n"/>
+      <c r="O21" s="31" t="n"/>
+      <c r="P21" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O21" s="12" t="inlineStr">
+      <c r="Q21" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P21" s="12" t="inlineStr">
+      <c r="R21" s="12" t="inlineStr">
         <is>
           <t>Income statement or segment report</t>
         </is>
       </c>
-      <c r="Q21" s="12" t="inlineStr">
+      <c r="S21" s="12" t="inlineStr">
         <is>
           <t>Contracts × deal size, and the capacity chain, should reproduce it</t>
         </is>
       </c>
-      <c r="R21" s="32">
-        <f>IF(OR(K21="",G21="",F21="Judgment"),"",IFERROR(K21/G21-1,""))</f>
-        <v/>
-      </c>
-      <c r="S21" s="11" t="n">
+      <c r="T21" s="11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2179,53 +2213,54 @@
           <t>Executed agreements in the period that produced that revenue</t>
         </is>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr"/>
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="F22" s="26" t="inlineStr">
+      <c r="G22" s="26" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="G22" s="33">
-        <f>IF(F22="Validated actual",IF(H22="","",H22),IF(F22="Calculated",IF(I22="","",I22),IF(F22="Reference value",IF(J22="","",J22),IF(F22="Judgment",IF(K22="","",K22),""))))</f>
-        <v/>
-      </c>
-      <c r="H22" s="34" t="n">
+      <c r="H22" s="33">
+        <f>IF(G22="Validated actual",IF(I22="","",I22),IF(G22="Calculated",IF(J22="","",J22),IF(G22="Reference value",IF(K22="","",K22),IF(G22="Judgment",IF(L22="","",L22),""))))</f>
+        <v/>
+      </c>
+      <c r="I22" s="34" t="n">
         <v>755</v>
       </c>
-      <c r="I22" s="29" t="n"/>
-      <c r="J22" s="34" t="n"/>
+      <c r="J22" s="29" t="n"/>
       <c r="K22" s="34" t="n"/>
       <c r="L22" s="34" t="n"/>
-      <c r="M22" s="34" t="n"/>
-      <c r="N22" s="26" t="inlineStr">
+      <c r="M22" s="32">
+        <f>IF(OR(L22="",H22="",G22="Judgment"),"",IFERROR(L22/H22-1,""))</f>
+        <v/>
+      </c>
+      <c r="N22" s="34" t="n"/>
+      <c r="O22" s="34" t="n"/>
+      <c r="P22" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O22" s="12" t="inlineStr">
+      <c r="Q22" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P22" s="12" t="inlineStr">
+      <c r="R22" s="12" t="inlineStr">
         <is>
           <t>Billing or contract system</t>
         </is>
       </c>
-      <c r="Q22" s="12" t="inlineStr">
+      <c r="S22" s="12" t="inlineStr">
         <is>
           <t>Won opportunities in the CRM should match</t>
         </is>
       </c>
-      <c r="R22" s="32">
-        <f>IF(OR(K22="",G22="",F22="Judgment"),"",IFERROR(K22/G22-1,""))</f>
-        <v/>
-      </c>
-      <c r="S22" s="11" t="n">
+      <c r="T22" s="11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2248,47 +2283,48 @@
           <t>Revenue the plan expected for the period</t>
         </is>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr"/>
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F23" s="26" t="inlineStr">
+      <c r="G23" s="26" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="G23" s="30">
-        <f>IF(F23="Validated actual",IF(H23="","",H23),IF(F23="Calculated",IF(I23="","",I23),IF(F23="Reference value",IF(J23="","",J23),IF(F23="Judgment",IF(K23="","",K23),""))))</f>
-        <v/>
-      </c>
-      <c r="H23" s="31" t="n"/>
-      <c r="I23" s="29" t="n"/>
-      <c r="J23" s="31" t="n"/>
+      <c r="H23" s="30">
+        <f>IF(G23="Validated actual",IF(I23="","",I23),IF(G23="Calculated",IF(J23="","",J23),IF(G23="Reference value",IF(K23="","",K23),IF(G23="Judgment",IF(L23="","",L23),""))))</f>
+        <v/>
+      </c>
+      <c r="I23" s="31" t="n"/>
+      <c r="J23" s="29" t="n"/>
       <c r="K23" s="31" t="n"/>
       <c r="L23" s="31" t="n"/>
-      <c r="M23" s="31" t="n"/>
-      <c r="N23" s="26" t="inlineStr"/>
-      <c r="O23" s="12" t="inlineStr">
+      <c r="M23" s="32">
+        <f>IF(OR(L23="",H23="",G23="Judgment"),"",IFERROR(L23/H23-1,""))</f>
+        <v/>
+      </c>
+      <c r="N23" s="31" t="n"/>
+      <c r="O23" s="31" t="n"/>
+      <c r="P23" s="26" t="inlineStr"/>
+      <c r="Q23" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P23" s="12" t="inlineStr">
+      <c r="R23" s="12" t="inlineStr">
         <is>
           <t>Annual plan</t>
         </is>
       </c>
-      <c r="Q23" s="12" t="inlineStr">
+      <c r="S23" s="12" t="inlineStr">
         <is>
           <t>Territories × expected yield per territory should match</t>
         </is>
       </c>
-      <c r="R23" s="32">
-        <f>IF(OR(K23="",G23="",F23="Judgment"),"",IFERROR(K23/G23-1,""))</f>
-        <v/>
-      </c>
-      <c r="S23" s="11" t="n">
+      <c r="T23" s="11" t="n">
         <v>3</v>
       </c>
     </row>
@@ -2311,43 +2347,44 @@
           <t>Direct cost of delivering that revenue</t>
         </is>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr"/>
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F24" s="26" t="inlineStr">
+      <c r="G24" s="26" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="G24" s="30">
-        <f>IF(F24="Validated actual",IF(H24="","",H24),IF(F24="Calculated",IF(I24="","",I24),IF(F24="Reference value",IF(J24="","",J24),IF(F24="Judgment",IF(K24="","",K24),""))))</f>
-        <v/>
-      </c>
-      <c r="H24" s="31" t="n"/>
-      <c r="I24" s="29" t="n"/>
-      <c r="J24" s="31" t="n"/>
+      <c r="H24" s="30">
+        <f>IF(G24="Validated actual",IF(I24="","",I24),IF(G24="Calculated",IF(J24="","",J24),IF(G24="Reference value",IF(K24="","",K24),IF(G24="Judgment",IF(L24="","",L24),""))))</f>
+        <v/>
+      </c>
+      <c r="I24" s="31" t="n"/>
+      <c r="J24" s="29" t="n"/>
       <c r="K24" s="31" t="n"/>
       <c r="L24" s="31" t="n"/>
-      <c r="M24" s="31" t="n"/>
-      <c r="N24" s="26" t="inlineStr"/>
-      <c r="O24" s="12" t="inlineStr">
+      <c r="M24" s="32">
+        <f>IF(OR(L24="",H24="",G24="Judgment"),"",IFERROR(L24/H24-1,""))</f>
+        <v/>
+      </c>
+      <c r="N24" s="31" t="n"/>
+      <c r="O24" s="31" t="n"/>
+      <c r="P24" s="26" t="inlineStr"/>
+      <c r="Q24" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P24" s="12" t="inlineStr">
+      <c r="R24" s="12" t="inlineStr">
         <is>
           <t>Income statement</t>
         </is>
       </c>
-      <c r="Q24" s="12" t="inlineStr"/>
-      <c r="R24" s="32">
-        <f>IF(OR(K24="",G24="",F24="Judgment"),"",IFERROR(K24/G24-1,""))</f>
-        <v/>
-      </c>
-      <c r="S24" s="11" t="n"/>
+      <c r="S24" s="12" t="inlineStr"/>
+      <c r="T24" s="11" t="n"/>
     </row>
     <row r="25" ht="17.5" customHeight="1">
       <c r="A25" s="11" t="n">
@@ -2368,43 +2405,44 @@
           <t>R&amp;D expense for the period</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="12" t="inlineStr"/>
+      <c r="F25" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F25" s="26" t="inlineStr">
+      <c r="G25" s="26" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="G25" s="30">
-        <f>IF(F25="Validated actual",IF(H25="","",H25),IF(F25="Calculated",IF(I25="","",I25),IF(F25="Reference value",IF(J25="","",J25),IF(F25="Judgment",IF(K25="","",K25),""))))</f>
-        <v/>
-      </c>
-      <c r="H25" s="31" t="n"/>
-      <c r="I25" s="29" t="n"/>
-      <c r="J25" s="31" t="n"/>
+      <c r="H25" s="30">
+        <f>IF(G25="Validated actual",IF(I25="","",I25),IF(G25="Calculated",IF(J25="","",J25),IF(G25="Reference value",IF(K25="","",K25),IF(G25="Judgment",IF(L25="","",L25),""))))</f>
+        <v/>
+      </c>
+      <c r="I25" s="31" t="n"/>
+      <c r="J25" s="29" t="n"/>
       <c r="K25" s="31" t="n"/>
       <c r="L25" s="31" t="n"/>
-      <c r="M25" s="31" t="n"/>
-      <c r="N25" s="26" t="inlineStr"/>
-      <c r="O25" s="12" t="inlineStr">
+      <c r="M25" s="32">
+        <f>IF(OR(L25="",H25="",G25="Judgment"),"",IFERROR(L25/H25-1,""))</f>
+        <v/>
+      </c>
+      <c r="N25" s="31" t="n"/>
+      <c r="O25" s="31" t="n"/>
+      <c r="P25" s="26" t="inlineStr"/>
+      <c r="Q25" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P25" s="12" t="inlineStr">
+      <c r="R25" s="12" t="inlineStr">
         <is>
           <t>Income statement</t>
         </is>
       </c>
-      <c r="Q25" s="12" t="inlineStr"/>
-      <c r="R25" s="32">
-        <f>IF(OR(K25="",G25="",F25="Judgment"),"",IFERROR(K25/G25-1,""))</f>
-        <v/>
-      </c>
-      <c r="S25" s="11" t="n"/>
+      <c r="S25" s="12" t="inlineStr"/>
+      <c r="T25" s="11" t="n"/>
     </row>
     <row r="26" ht="17.5" customHeight="1">
       <c r="A26" s="11" t="n">
@@ -2425,45 +2463,46 @@
           <t>G&amp;A expense for the period</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="12" t="inlineStr"/>
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F26" s="26" t="inlineStr">
+      <c r="G26" s="26" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="G26" s="30">
-        <f>IF(F26="Validated actual",IF(H26="","",H26),IF(F26="Calculated",IF(I26="","",I26),IF(F26="Reference value",IF(J26="","",J26),IF(F26="Judgment",IF(K26="","",K26),""))))</f>
-        <v/>
-      </c>
-      <c r="H26" s="31" t="n"/>
-      <c r="I26" s="29" t="n"/>
-      <c r="J26" s="31" t="n"/>
+      <c r="H26" s="30">
+        <f>IF(G26="Validated actual",IF(I26="","",I26),IF(G26="Calculated",IF(J26="","",J26),IF(G26="Reference value",IF(K26="","",K26),IF(G26="Judgment",IF(L26="","",L26),""))))</f>
+        <v/>
+      </c>
+      <c r="I26" s="31" t="n"/>
+      <c r="J26" s="29" t="n"/>
       <c r="K26" s="31" t="n"/>
       <c r="L26" s="31" t="n"/>
-      <c r="M26" s="31" t="n"/>
-      <c r="N26" s="26" t="inlineStr"/>
-      <c r="O26" s="12" t="inlineStr">
+      <c r="M26" s="32">
+        <f>IF(OR(L26="",H26="",G26="Judgment"),"",IFERROR(L26/H26-1,""))</f>
+        <v/>
+      </c>
+      <c r="N26" s="31" t="n"/>
+      <c r="O26" s="31" t="n"/>
+      <c r="P26" s="26" t="inlineStr"/>
+      <c r="Q26" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P26" s="12" t="inlineStr">
+      <c r="R26" s="12" t="inlineStr">
         <is>
           <t>Income statement</t>
         </is>
       </c>
-      <c r="Q26" s="12" t="inlineStr"/>
-      <c r="R26" s="32">
-        <f>IF(OR(K26="",G26="",F26="Judgment"),"",IFERROR(K26/G26-1,""))</f>
-        <v/>
-      </c>
-      <c r="S26" s="11" t="n"/>
-    </row>
-    <row r="27" ht="44.5" customHeight="1">
+      <c r="S26" s="12" t="inlineStr"/>
+      <c r="T26" s="11" t="n"/>
+    </row>
+    <row r="27" ht="31" customHeight="1">
       <c r="A27" s="11" t="n">
         <v>3</v>
       </c>
@@ -2482,56 +2521,57 @@
           <t>Cost of revenue ÷ revenue</t>
         </is>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="12" t="inlineStr"/>
+      <c r="F27" s="12" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="F27" s="26" t="inlineStr">
+      <c r="G27" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G27" s="36">
-        <f>IF(F27="Validated actual",IF(H27="","",H27),IF(F27="Calculated",IF(I27="","",I27),IF(F27="Reference value",IF(J27="","",J27),IF(F27="Judgment",IF(K27="","",K27),""))))</f>
-        <v/>
-      </c>
-      <c r="H27" s="37" t="n"/>
-      <c r="I27" s="38">
+      <c r="H27" s="36">
+        <f>IF(G27="Validated actual",IF(I27="","",I27),IF(G27="Calculated",IF(J27="","",J27),IF(G27="Reference value",IF(K27="","",K27),IF(G27="Judgment",IF(L27="","",L27),""))))</f>
+        <v/>
+      </c>
+      <c r="I27" s="37" t="n"/>
+      <c r="J27" s="38">
         <f>IFERROR(v_cost_of_revenue_amt/v_revenue,"")</f>
         <v/>
       </c>
-      <c r="J27" s="37" t="n">
+      <c r="K27" s="37" t="n">
         <v>0.1322</v>
       </c>
-      <c r="K27" s="37" t="n"/>
       <c r="L27" s="37" t="n"/>
-      <c r="M27" s="37" t="n"/>
-      <c r="N27" s="26" t="inlineStr">
+      <c r="M27" s="32">
+        <f>IF(OR(L27="",H27="",G27="Judgment"),"",IFERROR(L27/H27-1,""))</f>
+        <v/>
+      </c>
+      <c r="N27" s="37" t="n"/>
+      <c r="O27" s="37" t="n"/>
+      <c r="P27" s="26" t="inlineStr">
         <is>
           <t>Industry average used in the as-is model</t>
         </is>
       </c>
-      <c r="O27" s="12" t="inlineStr">
+      <c r="Q27" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P27" s="12" t="inlineStr">
+      <c r="R27" s="12" t="inlineStr">
         <is>
           <t>Income statement</t>
         </is>
       </c>
-      <c r="Q27" s="12" t="inlineStr">
+      <c r="S27" s="12" t="inlineStr">
         <is>
           <t>Income statement history shows a different ratio or a fixed component</t>
         </is>
       </c>
-      <c r="R27" s="32">
-        <f>IF(OR(K27="",G27="",F27="Judgment"),"",IFERROR(K27/G27-1,""))</f>
-        <v/>
-      </c>
-      <c r="S27" s="11" t="n">
+      <c r="T27" s="11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2554,56 +2594,57 @@
           <t>R&amp;D ÷ revenue</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="12" t="inlineStr"/>
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="F28" s="26" t="inlineStr">
+      <c r="G28" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G28" s="36">
-        <f>IF(F28="Validated actual",IF(H28="","",H28),IF(F28="Calculated",IF(I28="","",I28),IF(F28="Reference value",IF(J28="","",J28),IF(F28="Judgment",IF(K28="","",K28),""))))</f>
-        <v/>
-      </c>
-      <c r="H28" s="37" t="n"/>
-      <c r="I28" s="38">
+      <c r="H28" s="36">
+        <f>IF(G28="Validated actual",IF(I28="","",I28),IF(G28="Calculated",IF(J28="","",J28),IF(G28="Reference value",IF(K28="","",K28),IF(G28="Judgment",IF(L28="","",L28),""))))</f>
+        <v/>
+      </c>
+      <c r="I28" s="37" t="n"/>
+      <c r="J28" s="38">
         <f>IFERROR(v_rnd_amt/v_revenue,"")</f>
         <v/>
       </c>
-      <c r="J28" s="37" t="n">
+      <c r="K28" s="37" t="n">
         <v>0.1019</v>
       </c>
-      <c r="K28" s="37" t="n"/>
       <c r="L28" s="37" t="n"/>
-      <c r="M28" s="37" t="n"/>
-      <c r="N28" s="26" t="inlineStr">
+      <c r="M28" s="32">
+        <f>IF(OR(L28="",H28="",G28="Judgment"),"",IFERROR(L28/H28-1,""))</f>
+        <v/>
+      </c>
+      <c r="N28" s="37" t="n"/>
+      <c r="O28" s="37" t="n"/>
+      <c r="P28" s="26" t="inlineStr">
         <is>
           <t>Industry average used in the as-is model</t>
         </is>
       </c>
-      <c r="O28" s="12" t="inlineStr">
+      <c r="Q28" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P28" s="12" t="inlineStr">
+      <c r="R28" s="12" t="inlineStr">
         <is>
           <t>Income statement</t>
         </is>
       </c>
-      <c r="Q28" s="12" t="inlineStr">
+      <c r="S28" s="12" t="inlineStr">
         <is>
           <t>R&amp;D does not move with revenue</t>
         </is>
       </c>
-      <c r="R28" s="32">
-        <f>IF(OR(K28="",G28="",F28="Judgment"),"",IFERROR(K28/G28-1,""))</f>
-        <v/>
-      </c>
-      <c r="S28" s="11" t="n">
+      <c r="T28" s="11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2626,56 +2667,57 @@
           <t>G&amp;A ÷ revenue</t>
         </is>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="12" t="inlineStr"/>
+      <c r="F29" s="12" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="F29" s="26" t="inlineStr">
+      <c r="G29" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G29" s="36">
-        <f>IF(F29="Validated actual",IF(H29="","",H29),IF(F29="Calculated",IF(I29="","",I29),IF(F29="Reference value",IF(J29="","",J29),IF(F29="Judgment",IF(K29="","",K29),""))))</f>
-        <v/>
-      </c>
-      <c r="H29" s="37" t="n"/>
-      <c r="I29" s="38">
+      <c r="H29" s="36">
+        <f>IF(G29="Validated actual",IF(I29="","",I29),IF(G29="Calculated",IF(J29="","",J29),IF(G29="Reference value",IF(K29="","",K29),IF(G29="Judgment",IF(L29="","",L29),""))))</f>
+        <v/>
+      </c>
+      <c r="I29" s="37" t="n"/>
+      <c r="J29" s="38">
         <f>IFERROR(v_gna_amt/v_revenue,"")</f>
         <v/>
       </c>
-      <c r="J29" s="37" t="n">
+      <c r="K29" s="37" t="n">
         <v>0.154</v>
       </c>
-      <c r="K29" s="37" t="n"/>
       <c r="L29" s="37" t="n"/>
-      <c r="M29" s="37" t="n"/>
-      <c r="N29" s="26" t="inlineStr">
+      <c r="M29" s="32">
+        <f>IF(OR(L29="",H29="",G29="Judgment"),"",IFERROR(L29/H29-1,""))</f>
+        <v/>
+      </c>
+      <c r="N29" s="37" t="n"/>
+      <c r="O29" s="37" t="n"/>
+      <c r="P29" s="26" t="inlineStr">
         <is>
           <t>Industry average used in the as-is model</t>
         </is>
       </c>
-      <c r="O29" s="12" t="inlineStr">
+      <c r="Q29" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P29" s="12" t="inlineStr">
+      <c r="R29" s="12" t="inlineStr">
         <is>
           <t>Income statement</t>
         </is>
       </c>
-      <c r="Q29" s="12" t="inlineStr">
+      <c r="S29" s="12" t="inlineStr">
         <is>
           <t>G&amp;A does not move with revenue</t>
         </is>
       </c>
-      <c r="R29" s="32">
-        <f>IF(OR(K29="",G29="",F29="Judgment"),"",IFERROR(K29/G29-1,""))</f>
-        <v/>
-      </c>
-      <c r="S29" s="11" t="n">
+      <c r="T29" s="11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2703,6 +2745,7 @@
       <c r="Q30" s="21" t="n"/>
       <c r="R30" s="21" t="n"/>
       <c r="S30" s="21" t="n"/>
+      <c r="T30" s="21" t="n"/>
     </row>
     <row r="31" ht="44.5" customHeight="1">
       <c r="A31" s="11" t="n">
@@ -2723,53 +2766,54 @@
           <t>Base pay of quota-carrying salespeople only; excludes managers, sales engineers and executives</t>
         </is>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="12" t="inlineStr"/>
+      <c r="F31" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F31" s="26" t="inlineStr">
+      <c r="G31" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G31" s="30">
-        <f>IF(F31="Validated actual",IF(H31="","",H31),IF(F31="Calculated",IF(I31="","",I31),IF(F31="Reference value",IF(J31="","",J31),IF(F31="Judgment",IF(K31="","",K31),""))))</f>
-        <v/>
-      </c>
-      <c r="H31" s="31" t="n"/>
-      <c r="I31" s="29" t="n"/>
-      <c r="J31" s="31" t="n">
+      <c r="H31" s="30">
+        <f>IF(G31="Validated actual",IF(I31="","",I31),IF(G31="Calculated",IF(J31="","",J31),IF(G31="Reference value",IF(K31="","",K31),IF(G31="Judgment",IF(L31="","",L31),""))))</f>
+        <v/>
+      </c>
+      <c r="I31" s="31" t="n"/>
+      <c r="J31" s="29" t="n"/>
+      <c r="K31" s="31" t="n">
         <v>95000</v>
       </c>
-      <c r="K31" s="31" t="n"/>
       <c r="L31" s="31" t="n"/>
-      <c r="M31" s="31" t="n"/>
-      <c r="N31" s="26" t="inlineStr">
+      <c r="M31" s="32">
+        <f>IF(OR(L31="",H31="",G31="Judgment"),"",IFERROR(L31/H31-1,""))</f>
+        <v/>
+      </c>
+      <c r="N31" s="31" t="n"/>
+      <c r="O31" s="31" t="n"/>
+      <c r="P31" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O31" s="12" t="inlineStr">
+      <c r="Q31" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P31" s="12" t="inlineStr">
+      <c r="R31" s="12" t="inlineStr">
         <is>
           <t>Payroll register</t>
         </is>
       </c>
-      <c r="Q31" s="12" t="inlineStr">
+      <c r="S31" s="12" t="inlineStr">
         <is>
           <t>Payroll for quota-carrying roles differs</t>
         </is>
       </c>
-      <c r="R31" s="32">
-        <f>IF(OR(K31="",G31="",F31="Judgment"),"",IFERROR(K31/G31-1,""))</f>
-        <v/>
-      </c>
-      <c r="S31" s="11" t="n">
+      <c r="T31" s="11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2792,57 +2836,58 @@
           <t>Benefits and payroll taxes ÷ base salary (no overhead allocation)</t>
         </is>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="12" t="inlineStr"/>
+      <c r="F32" s="12" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="F32" s="26" t="inlineStr">
+      <c r="G32" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G32" s="36">
-        <f>IF(F32="Validated actual",IF(H32="","",H32),IF(F32="Calculated",IF(I32="","",I32),IF(F32="Reference value",IF(J32="","",J32),IF(F32="Judgment",IF(K32="","",K32),""))))</f>
-        <v/>
-      </c>
-      <c r="H32" s="37" t="n"/>
-      <c r="I32" s="29" t="n"/>
-      <c r="J32" s="37" t="n">
+      <c r="H32" s="36">
+        <f>IF(G32="Validated actual",IF(I32="","",I32),IF(G32="Calculated",IF(J32="","",J32),IF(G32="Reference value",IF(K32="","",K32),IF(G32="Judgment",IF(L32="","",L32),""))))</f>
+        <v/>
+      </c>
+      <c r="I32" s="37" t="n"/>
+      <c r="J32" s="29" t="n"/>
+      <c r="K32" s="37" t="n">
         <v>0.23</v>
       </c>
-      <c r="K32" s="37" t="n"/>
       <c r="L32" s="37" t="n"/>
-      <c r="M32" s="37" t="n"/>
-      <c r="N32" s="26" t="inlineStr">
+      <c r="M32" s="32">
+        <f>IF(OR(L32="",H32="",G32="Judgment"),"",IFERROR(L32/H32-1,""))</f>
+        <v/>
+      </c>
+      <c r="N32" s="37" t="n"/>
+      <c r="O32" s="37" t="n"/>
+      <c r="P32" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O32" s="12" t="inlineStr">
+      <c r="Q32" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P32" s="12" t="inlineStr">
+      <c r="R32" s="12" t="inlineStr">
         <is>
           <t>Payroll and benefits ledger</t>
         </is>
       </c>
-      <c r="Q32" s="12" t="inlineStr">
+      <c r="S32" s="12" t="inlineStr">
         <is>
           <t>Benefits ledger ÷ base payroll differs</t>
         </is>
       </c>
-      <c r="R32" s="32">
-        <f>IF(OR(K32="",G32="",F32="Judgment"),"",IFERROR(K32/G32-1,""))</f>
-        <v/>
-      </c>
-      <c r="S32" s="11" t="n">
+      <c r="T32" s="11" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="33" ht="31" customHeight="1">
+    <row r="33" ht="112" customHeight="1">
       <c r="A33" s="11" t="n">
         <v>4</v>
       </c>
@@ -2863,48 +2908,53 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
+          <t>To help develop the most effective market development effort, we must better understand our cost of sales and what drives them. Right now we are focusing on the salaries of the sales team only. Do not count salaries of non-quota carrying managers, sales engineers, or other executives. Your CFO should know what your benefits load rate is. This metric assumes a fully loaded resource (insurance, 401K, FICA, allocation of overhead, etc).</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="inlineStr">
+        <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F33" s="26" t="inlineStr">
+      <c r="G33" s="26" t="inlineStr">
         <is>
           <t>Calculated</t>
         </is>
       </c>
-      <c r="G33" s="30">
-        <f>IF(F33="Validated actual",IF(H33="","",H33),IF(F33="Calculated",IF(I33="","",I33),IF(F33="Reference value",IF(J33="","",J33),IF(F33="Judgment",IF(K33="","",K33),""))))</f>
-        <v/>
-      </c>
-      <c r="H33" s="31" t="n"/>
-      <c r="I33" s="39">
+      <c r="H33" s="30">
+        <f>IF(G33="Validated actual",IF(I33="","",I33),IF(G33="Calculated",IF(J33="","",J33),IF(G33="Reference value",IF(K33="","",K33),IF(G33="Judgment",IF(L33="","",L33),""))))</f>
+        <v/>
+      </c>
+      <c r="I33" s="31" t="n"/>
+      <c r="J33" s="39">
         <f>IFERROR(v_base_salary*(1+v_load_rate),"")</f>
         <v/>
       </c>
-      <c r="J33" s="31" t="n"/>
       <c r="K33" s="31" t="n"/>
       <c r="L33" s="31" t="n"/>
-      <c r="M33" s="31" t="n"/>
-      <c r="N33" s="26" t="inlineStr"/>
-      <c r="O33" s="12" t="inlineStr">
+      <c r="M33" s="32">
+        <f>IF(OR(L33="",H33="",G33="Judgment"),"",IFERROR(L33/H33-1,""))</f>
+        <v/>
+      </c>
+      <c r="N33" s="31" t="n"/>
+      <c r="O33" s="31" t="n"/>
+      <c r="P33" s="26" t="inlineStr"/>
+      <c r="Q33" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P33" s="12" t="inlineStr">
+      <c r="R33" s="12" t="inlineStr">
         <is>
           <t>Calculated from the two lines above</t>
         </is>
       </c>
-      <c r="Q33" s="12" t="inlineStr">
+      <c r="S33" s="12" t="inlineStr">
         <is>
           <t>Compensation cross-check against the ledger</t>
         </is>
       </c>
-      <c r="R33" s="32">
-        <f>IF(OR(K33="",G33="",F33="Judgment"),"",IFERROR(K33/G33-1,""))</f>
-        <v/>
-      </c>
-      <c r="S33" s="11" t="n">
+      <c r="T33" s="11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2927,49 +2977,50 @@
           <t>Round trip, one salesperson</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr"/>
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F34" s="26" t="inlineStr">
+      <c r="G34" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G34" s="30">
-        <f>IF(F34="Validated actual",IF(H34="","",H34),IF(F34="Calculated",IF(I34="","",I34),IF(F34="Reference value",IF(J34="","",J34),IF(F34="Judgment",IF(K34="","",K34),""))))</f>
-        <v/>
-      </c>
-      <c r="H34" s="31" t="n"/>
-      <c r="I34" s="29" t="n"/>
-      <c r="J34" s="31" t="n">
+      <c r="H34" s="30">
+        <f>IF(G34="Validated actual",IF(I34="","",I34),IF(G34="Calculated",IF(J34="","",J34),IF(G34="Reference value",IF(K34="","",K34),IF(G34="Judgment",IF(L34="","",L34),""))))</f>
+        <v/>
+      </c>
+      <c r="I34" s="31" t="n"/>
+      <c r="J34" s="29" t="n"/>
+      <c r="K34" s="31" t="n">
         <v>750</v>
       </c>
-      <c r="K34" s="31" t="n"/>
       <c r="L34" s="31" t="n"/>
-      <c r="M34" s="31" t="n"/>
-      <c r="N34" s="26" t="inlineStr">
+      <c r="M34" s="32">
+        <f>IF(OR(L34="",H34="",G34="Judgment"),"",IFERROR(L34/H34-1,""))</f>
+        <v/>
+      </c>
+      <c r="N34" s="31" t="n"/>
+      <c r="O34" s="31" t="n"/>
+      <c r="P34" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O34" s="12" t="inlineStr">
+      <c r="Q34" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P34" s="12" t="inlineStr">
+      <c r="R34" s="12" t="inlineStr">
         <is>
           <t>Expense reports</t>
         </is>
       </c>
-      <c r="Q34" s="12" t="inlineStr"/>
-      <c r="R34" s="32">
-        <f>IF(OR(K34="",G34="",F34="Judgment"),"",IFERROR(K34/G34-1,""))</f>
-        <v/>
-      </c>
-      <c r="S34" s="11" t="n"/>
+      <c r="S34" s="12" t="inlineStr"/>
+      <c r="T34" s="11" t="n"/>
     </row>
     <row r="35" ht="31" customHeight="1">
       <c r="A35" s="11" t="n">
@@ -2990,49 +3041,50 @@
           <t>Per trip</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr"/>
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F35" s="26" t="inlineStr">
+      <c r="G35" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G35" s="30">
-        <f>IF(F35="Validated actual",IF(H35="","",H35),IF(F35="Calculated",IF(I35="","",I35),IF(F35="Reference value",IF(J35="","",J35),IF(F35="Judgment",IF(K35="","",K35),""))))</f>
-        <v/>
-      </c>
-      <c r="H35" s="31" t="n"/>
-      <c r="I35" s="29" t="n"/>
-      <c r="J35" s="31" t="n">
+      <c r="H35" s="30">
+        <f>IF(G35="Validated actual",IF(I35="","",I35),IF(G35="Calculated",IF(J35="","",J35),IF(G35="Reference value",IF(K35="","",K35),IF(G35="Judgment",IF(L35="","",L35),""))))</f>
+        <v/>
+      </c>
+      <c r="I35" s="31" t="n"/>
+      <c r="J35" s="29" t="n"/>
+      <c r="K35" s="31" t="n">
         <v>200</v>
       </c>
-      <c r="K35" s="31" t="n"/>
       <c r="L35" s="31" t="n"/>
-      <c r="M35" s="31" t="n"/>
-      <c r="N35" s="26" t="inlineStr">
+      <c r="M35" s="32">
+        <f>IF(OR(L35="",H35="",G35="Judgment"),"",IFERROR(L35/H35-1,""))</f>
+        <v/>
+      </c>
+      <c r="N35" s="31" t="n"/>
+      <c r="O35" s="31" t="n"/>
+      <c r="P35" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O35" s="12" t="inlineStr">
+      <c r="Q35" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P35" s="12" t="inlineStr">
+      <c r="R35" s="12" t="inlineStr">
         <is>
           <t>Expense reports</t>
         </is>
       </c>
-      <c r="Q35" s="12" t="inlineStr"/>
-      <c r="R35" s="32">
-        <f>IF(OR(K35="",G35="",F35="Judgment"),"",IFERROR(K35/G35-1,""))</f>
-        <v/>
-      </c>
-      <c r="S35" s="11" t="n"/>
+      <c r="S35" s="12" t="inlineStr"/>
+      <c r="T35" s="11" t="n"/>
     </row>
     <row r="36" ht="31" customHeight="1">
       <c r="A36" s="11" t="n">
@@ -3053,49 +3105,50 @@
           <t>Breakfast, lunch, dinner</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr"/>
+      <c r="F36" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F36" s="26" t="inlineStr">
+      <c r="G36" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G36" s="30">
-        <f>IF(F36="Validated actual",IF(H36="","",H36),IF(F36="Calculated",IF(I36="","",I36),IF(F36="Reference value",IF(J36="","",J36),IF(F36="Judgment",IF(K36="","",K36),""))))</f>
-        <v/>
-      </c>
-      <c r="H36" s="31" t="n"/>
-      <c r="I36" s="29" t="n"/>
-      <c r="J36" s="31" t="n">
+      <c r="H36" s="30">
+        <f>IF(G36="Validated actual",IF(I36="","",I36),IF(G36="Calculated",IF(J36="","",J36),IF(G36="Reference value",IF(K36="","",K36),IF(G36="Judgment",IF(L36="","",L36),""))))</f>
+        <v/>
+      </c>
+      <c r="I36" s="31" t="n"/>
+      <c r="J36" s="29" t="n"/>
+      <c r="K36" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="K36" s="31" t="n"/>
       <c r="L36" s="31" t="n"/>
-      <c r="M36" s="31" t="n"/>
-      <c r="N36" s="26" t="inlineStr">
+      <c r="M36" s="32">
+        <f>IF(OR(L36="",H36="",G36="Judgment"),"",IFERROR(L36/H36-1,""))</f>
+        <v/>
+      </c>
+      <c r="N36" s="31" t="n"/>
+      <c r="O36" s="31" t="n"/>
+      <c r="P36" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O36" s="12" t="inlineStr">
+      <c r="Q36" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P36" s="12" t="inlineStr">
+      <c r="R36" s="12" t="inlineStr">
         <is>
           <t>Expense reports</t>
         </is>
       </c>
-      <c r="Q36" s="12" t="inlineStr"/>
-      <c r="R36" s="32">
-        <f>IF(OR(K36="",G36="",F36="Judgment"),"",IFERROR(K36/G36-1,""))</f>
-        <v/>
-      </c>
-      <c r="S36" s="11" t="n"/>
+      <c r="S36" s="12" t="inlineStr"/>
+      <c r="T36" s="11" t="n"/>
     </row>
     <row r="37" ht="31" customHeight="1">
       <c r="A37" s="11" t="n">
@@ -3116,49 +3169,50 @@
           <t>Average room cost</t>
         </is>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr"/>
+      <c r="F37" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F37" s="26" t="inlineStr">
+      <c r="G37" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G37" s="30">
-        <f>IF(F37="Validated actual",IF(H37="","",H37),IF(F37="Calculated",IF(I37="","",I37),IF(F37="Reference value",IF(J37="","",J37),IF(F37="Judgment",IF(K37="","",K37),""))))</f>
-        <v/>
-      </c>
-      <c r="H37" s="31" t="n"/>
-      <c r="I37" s="29" t="n"/>
-      <c r="J37" s="31" t="n">
+      <c r="H37" s="30">
+        <f>IF(G37="Validated actual",IF(I37="","",I37),IF(G37="Calculated",IF(J37="","",J37),IF(G37="Reference value",IF(K37="","",K37),IF(G37="Judgment",IF(L37="","",L37),""))))</f>
+        <v/>
+      </c>
+      <c r="I37" s="31" t="n"/>
+      <c r="J37" s="29" t="n"/>
+      <c r="K37" s="31" t="n">
         <v>250</v>
       </c>
-      <c r="K37" s="31" t="n"/>
       <c r="L37" s="31" t="n"/>
-      <c r="M37" s="31" t="n"/>
-      <c r="N37" s="26" t="inlineStr">
+      <c r="M37" s="32">
+        <f>IF(OR(L37="",H37="",G37="Judgment"),"",IFERROR(L37/H37-1,""))</f>
+        <v/>
+      </c>
+      <c r="N37" s="31" t="n"/>
+      <c r="O37" s="31" t="n"/>
+      <c r="P37" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O37" s="12" t="inlineStr">
+      <c r="Q37" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P37" s="12" t="inlineStr">
+      <c r="R37" s="12" t="inlineStr">
         <is>
           <t>Expense reports</t>
         </is>
       </c>
-      <c r="Q37" s="12" t="inlineStr"/>
-      <c r="R37" s="32">
-        <f>IF(OR(K37="",G37="",F37="Judgment"),"",IFERROR(K37/G37-1,""))</f>
-        <v/>
-      </c>
-      <c r="S37" s="11" t="n"/>
+      <c r="S37" s="12" t="inlineStr"/>
+      <c r="T37" s="11" t="n"/>
     </row>
     <row r="38" ht="31" customHeight="1">
       <c r="A38" s="11" t="n">
@@ -3179,49 +3233,50 @@
           <t>Days away per trip</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="12" t="inlineStr"/>
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="F38" s="26" t="inlineStr">
+      <c r="G38" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G38" s="33">
-        <f>IF(F38="Validated actual",IF(H38="","",H38),IF(F38="Calculated",IF(I38="","",I38),IF(F38="Reference value",IF(J38="","",J38),IF(F38="Judgment",IF(K38="","",K38),""))))</f>
-        <v/>
-      </c>
-      <c r="H38" s="34" t="n"/>
-      <c r="I38" s="29" t="n"/>
-      <c r="J38" s="34" t="n">
+      <c r="H38" s="33">
+        <f>IF(G38="Validated actual",IF(I38="","",I38),IF(G38="Calculated",IF(J38="","",J38),IF(G38="Reference value",IF(K38="","",K38),IF(G38="Judgment",IF(L38="","",L38),""))))</f>
+        <v/>
+      </c>
+      <c r="I38" s="34" t="n"/>
+      <c r="J38" s="29" t="n"/>
+      <c r="K38" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="K38" s="34" t="n"/>
       <c r="L38" s="34" t="n"/>
-      <c r="M38" s="34" t="n"/>
-      <c r="N38" s="26" t="inlineStr">
+      <c r="M38" s="32">
+        <f>IF(OR(L38="",H38="",G38="Judgment"),"",IFERROR(L38/H38-1,""))</f>
+        <v/>
+      </c>
+      <c r="N38" s="34" t="n"/>
+      <c r="O38" s="34" t="n"/>
+      <c r="P38" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O38" s="12" t="inlineStr">
+      <c r="Q38" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P38" s="12" t="inlineStr">
+      <c r="R38" s="12" t="inlineStr">
         <is>
           <t>Expense reports</t>
         </is>
       </c>
-      <c r="Q38" s="12" t="inlineStr"/>
-      <c r="R38" s="32">
-        <f>IF(OR(K38="",G38="",F38="Judgment"),"",IFERROR(K38/G38-1,""))</f>
-        <v/>
-      </c>
-      <c r="S38" s="11" t="n"/>
+      <c r="S38" s="12" t="inlineStr"/>
+      <c r="T38" s="11" t="n"/>
     </row>
     <row r="39" ht="31" customHeight="1">
       <c r="A39" s="11" t="n">
@@ -3242,49 +3297,50 @@
           <t>Client meals and events per trip</t>
         </is>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E39" s="12" t="inlineStr"/>
+      <c r="F39" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F39" s="26" t="inlineStr">
+      <c r="G39" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G39" s="30">
-        <f>IF(F39="Validated actual",IF(H39="","",H39),IF(F39="Calculated",IF(I39="","",I39),IF(F39="Reference value",IF(J39="","",J39),IF(F39="Judgment",IF(K39="","",K39),""))))</f>
-        <v/>
-      </c>
-      <c r="H39" s="31" t="n"/>
-      <c r="I39" s="29" t="n"/>
-      <c r="J39" s="31" t="n">
+      <c r="H39" s="30">
+        <f>IF(G39="Validated actual",IF(I39="","",I39),IF(G39="Calculated",IF(J39="","",J39),IF(G39="Reference value",IF(K39="","",K39),IF(G39="Judgment",IF(L39="","",L39),""))))</f>
+        <v/>
+      </c>
+      <c r="I39" s="31" t="n"/>
+      <c r="J39" s="29" t="n"/>
+      <c r="K39" s="31" t="n">
         <v>250</v>
       </c>
-      <c r="K39" s="31" t="n"/>
       <c r="L39" s="31" t="n"/>
-      <c r="M39" s="31" t="n"/>
-      <c r="N39" s="26" t="inlineStr">
+      <c r="M39" s="32">
+        <f>IF(OR(L39="",H39="",G39="Judgment"),"",IFERROR(L39/H39-1,""))</f>
+        <v/>
+      </c>
+      <c r="N39" s="31" t="n"/>
+      <c r="O39" s="31" t="n"/>
+      <c r="P39" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O39" s="12" t="inlineStr">
+      <c r="Q39" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P39" s="12" t="inlineStr">
+      <c r="R39" s="12" t="inlineStr">
         <is>
           <t>Expense reports</t>
         </is>
       </c>
-      <c r="Q39" s="12" t="inlineStr"/>
-      <c r="R39" s="32">
-        <f>IF(OR(K39="",G39="",F39="Judgment"),"",IFERROR(K39/G39-1,""))</f>
-        <v/>
-      </c>
-      <c r="S39" s="11" t="n"/>
+      <c r="S39" s="12" t="inlineStr"/>
+      <c r="T39" s="11" t="n"/>
     </row>
     <row r="40" ht="31" customHeight="1">
       <c r="A40" s="11" t="n">
@@ -3305,51 +3361,52 @@
           <t>Sales trips per salesperson per year</t>
         </is>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="12" t="inlineStr"/>
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="F40" s="26" t="inlineStr">
+      <c r="G40" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G40" s="33">
-        <f>IF(F40="Validated actual",IF(H40="","",H40),IF(F40="Calculated",IF(I40="","",I40),IF(F40="Reference value",IF(J40="","",J40),IF(F40="Judgment",IF(K40="","",K40),""))))</f>
-        <v/>
-      </c>
-      <c r="H40" s="34" t="n"/>
-      <c r="I40" s="29" t="n"/>
-      <c r="J40" s="34" t="n">
+      <c r="H40" s="33">
+        <f>IF(G40="Validated actual",IF(I40="","",I40),IF(G40="Calculated",IF(J40="","",J40),IF(G40="Reference value",IF(K40="","",K40),IF(G40="Judgment",IF(L40="","",L40),""))))</f>
+        <v/>
+      </c>
+      <c r="I40" s="34" t="n"/>
+      <c r="J40" s="29" t="n"/>
+      <c r="K40" s="34" t="n">
         <v>25</v>
       </c>
-      <c r="K40" s="34" t="n"/>
       <c r="L40" s="34" t="n"/>
-      <c r="M40" s="34" t="n"/>
-      <c r="N40" s="26" t="inlineStr">
+      <c r="M40" s="32">
+        <f>IF(OR(L40="",H40="",G40="Judgment"),"",IFERROR(L40/H40-1,""))</f>
+        <v/>
+      </c>
+      <c r="N40" s="34" t="n"/>
+      <c r="O40" s="34" t="n"/>
+      <c r="P40" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O40" s="12" t="inlineStr">
+      <c r="Q40" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P40" s="12" t="inlineStr">
+      <c r="R40" s="12" t="inlineStr">
         <is>
           <t>Expense reports or calendars</t>
         </is>
       </c>
-      <c r="Q40" s="12" t="inlineStr"/>
-      <c r="R40" s="32">
-        <f>IF(OR(K40="",G40="",F40="Judgment"),"",IFERROR(K40/G40-1,""))</f>
-        <v/>
-      </c>
-      <c r="S40" s="11" t="n"/>
-    </row>
-    <row r="41" ht="31" customHeight="1">
+      <c r="S40" s="12" t="inlineStr"/>
+      <c r="T40" s="11" t="n"/>
+    </row>
+    <row r="41" ht="179.5" customHeight="1">
       <c r="A41" s="11" t="n">
         <v>4</v>
       </c>
@@ -3370,48 +3427,53 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
+          <t>Most CFO's track overall travel expenses and try to reduce costs by limiting per diems, hotel expenses, etc. However, the real driver is a sales call. Sales people only incur these travel costs on the road. The best way to reduce travel costs is to get a better return out of each sales trip. Oftentimes, sales people will go on multiple client site visits to gain information easily gathered over the phone, or to have meetings with buyers who lack the right marketing materials to decide to buy your solution. Below are the elements of a sales trip. Estimate the costs assumed for each sales trip. Again, only assume the cost of a single sales person. Sales engineers and other costs are too complex for simple analysis.</t>
+        </is>
+      </c>
+      <c r="F41" s="12" t="inlineStr">
+        <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F41" s="26" t="inlineStr">
+      <c r="G41" s="26" t="inlineStr">
         <is>
           <t>Calculated</t>
         </is>
       </c>
-      <c r="G41" s="30">
-        <f>IF(F41="Validated actual",IF(H41="","",H41),IF(F41="Calculated",IF(I41="","",I41),IF(F41="Reference value",IF(J41="","",J41),IF(F41="Judgment",IF(K41="","",K41),""))))</f>
-        <v/>
-      </c>
-      <c r="H41" s="31" t="n"/>
-      <c r="I41" s="39">
+      <c r="H41" s="30">
+        <f>IF(G41="Validated actual",IF(I41="","",I41),IF(G41="Calculated",IF(J41="","",J41),IF(G41="Reference value",IF(K41="","",K41),IF(G41="Judgment",IF(L41="","",L41),""))))</f>
+        <v/>
+      </c>
+      <c r="I41" s="31" t="n"/>
+      <c r="J41" s="39">
         <f>IFERROR(((v_trip_fare+v_trip_ground+v_trip_entertainment)+v_trip_days*(v_trip_meals+v_trip_lodging))*v_trips_per_year,"")</f>
         <v/>
       </c>
-      <c r="J41" s="31" t="n"/>
       <c r="K41" s="31" t="n"/>
       <c r="L41" s="31" t="n"/>
-      <c r="M41" s="31" t="n"/>
-      <c r="N41" s="26" t="inlineStr"/>
-      <c r="O41" s="12" t="inlineStr">
+      <c r="M41" s="32">
+        <f>IF(OR(L41="",H41="",G41="Judgment"),"",IFERROR(L41/H41-1,""))</f>
+        <v/>
+      </c>
+      <c r="N41" s="31" t="n"/>
+      <c r="O41" s="31" t="n"/>
+      <c r="P41" s="26" t="inlineStr"/>
+      <c r="Q41" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P41" s="12" t="inlineStr">
+      <c r="R41" s="12" t="inlineStr">
         <is>
           <t>Expense ledger</t>
         </is>
       </c>
-      <c r="Q41" s="12" t="inlineStr">
+      <c r="S41" s="12" t="inlineStr">
         <is>
           <t>T&amp;E ledger for quota salespeople differs</t>
         </is>
       </c>
-      <c r="R41" s="32">
-        <f>IF(OR(K41="",G41="",F41="Judgment"),"",IFERROR(K41/G41-1,""))</f>
-        <v/>
-      </c>
-      <c r="S41" s="11" t="n">
+      <c r="T41" s="11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3434,49 +3496,50 @@
           <t>Managers who carry no quota</t>
         </is>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr"/>
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F42" s="26" t="inlineStr">
+      <c r="G42" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G42" s="30">
-        <f>IF(F42="Validated actual",IF(H42="","",H42),IF(F42="Calculated",IF(I42="","",I42),IF(F42="Reference value",IF(J42="","",J42),IF(F42="Judgment",IF(K42="","",K42),""))))</f>
-        <v/>
-      </c>
-      <c r="H42" s="31" t="n"/>
-      <c r="I42" s="29" t="n"/>
-      <c r="J42" s="31" t="n">
+      <c r="H42" s="30">
+        <f>IF(G42="Validated actual",IF(I42="","",I42),IF(G42="Calculated",IF(J42="","",J42),IF(G42="Reference value",IF(K42="","",K42),IF(G42="Judgment",IF(L42="","",L42),""))))</f>
+        <v/>
+      </c>
+      <c r="I42" s="31" t="n"/>
+      <c r="J42" s="29" t="n"/>
+      <c r="K42" s="31" t="n">
         <v>2750000</v>
       </c>
-      <c r="K42" s="31" t="n"/>
       <c r="L42" s="31" t="n"/>
-      <c r="M42" s="31" t="n"/>
-      <c r="N42" s="26" t="inlineStr">
+      <c r="M42" s="32">
+        <f>IF(OR(L42="",H42="",G42="Judgment"),"",IFERROR(L42/H42-1,""))</f>
+        <v/>
+      </c>
+      <c r="N42" s="31" t="n"/>
+      <c r="O42" s="31" t="n"/>
+      <c r="P42" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O42" s="12" t="inlineStr">
+      <c r="Q42" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P42" s="12" t="inlineStr">
+      <c r="R42" s="12" t="inlineStr">
         <is>
           <t>General ledger</t>
         </is>
       </c>
-      <c r="Q42" s="12" t="inlineStr"/>
-      <c r="R42" s="32">
-        <f>IF(OR(K42="",G42="",F42="Judgment"),"",IFERROR(K42/G42-1,""))</f>
-        <v/>
-      </c>
-      <c r="S42" s="11" t="n"/>
+      <c r="S42" s="12" t="inlineStr"/>
+      <c r="T42" s="11" t="n"/>
     </row>
     <row r="43" ht="31" customHeight="1">
       <c r="A43" s="11" t="n">
@@ -3497,49 +3560,50 @@
           <t>Pre-sales and support roles</t>
         </is>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr"/>
+      <c r="F43" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F43" s="26" t="inlineStr">
+      <c r="G43" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G43" s="30">
-        <f>IF(F43="Validated actual",IF(H43="","",H43),IF(F43="Calculated",IF(I43="","",I43),IF(F43="Reference value",IF(J43="","",J43),IF(F43="Judgment",IF(K43="","",K43),""))))</f>
-        <v/>
-      </c>
-      <c r="H43" s="31" t="n"/>
-      <c r="I43" s="29" t="n"/>
-      <c r="J43" s="31" t="n">
+      <c r="H43" s="30">
+        <f>IF(G43="Validated actual",IF(I43="","",I43),IF(G43="Calculated",IF(J43="","",J43),IF(G43="Reference value",IF(K43="","",K43),IF(G43="Judgment",IF(L43="","",L43),""))))</f>
+        <v/>
+      </c>
+      <c r="I43" s="31" t="n"/>
+      <c r="J43" s="29" t="n"/>
+      <c r="K43" s="31" t="n">
         <v>6000000</v>
       </c>
-      <c r="K43" s="31" t="n"/>
       <c r="L43" s="31" t="n"/>
-      <c r="M43" s="31" t="n"/>
-      <c r="N43" s="26" t="inlineStr">
+      <c r="M43" s="32">
+        <f>IF(OR(L43="",H43="",G43="Judgment"),"",IFERROR(L43/H43-1,""))</f>
+        <v/>
+      </c>
+      <c r="N43" s="31" t="n"/>
+      <c r="O43" s="31" t="n"/>
+      <c r="P43" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O43" s="12" t="inlineStr">
+      <c r="Q43" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P43" s="12" t="inlineStr">
+      <c r="R43" s="12" t="inlineStr">
         <is>
           <t>General ledger</t>
         </is>
       </c>
-      <c r="Q43" s="12" t="inlineStr"/>
-      <c r="R43" s="32">
-        <f>IF(OR(K43="",G43="",F43="Judgment"),"",IFERROR(K43/G43-1,""))</f>
-        <v/>
-      </c>
-      <c r="S43" s="11" t="n"/>
+      <c r="S43" s="12" t="inlineStr"/>
+      <c r="T43" s="11" t="n"/>
     </row>
     <row r="44" ht="31" customHeight="1">
       <c r="A44" s="11" t="n">
@@ -3560,49 +3624,50 @@
           <t>Sales ops and admin staff</t>
         </is>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr"/>
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F44" s="26" t="inlineStr">
+      <c r="G44" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G44" s="30">
-        <f>IF(F44="Validated actual",IF(H44="","",H44),IF(F44="Calculated",IF(I44="","",I44),IF(F44="Reference value",IF(J44="","",J44),IF(F44="Judgment",IF(K44="","",K44),""))))</f>
-        <v/>
-      </c>
-      <c r="H44" s="31" t="n"/>
-      <c r="I44" s="29" t="n"/>
-      <c r="J44" s="31" t="n">
+      <c r="H44" s="30">
+        <f>IF(G44="Validated actual",IF(I44="","",I44),IF(G44="Calculated",IF(J44="","",J44),IF(G44="Reference value",IF(K44="","",K44),IF(G44="Judgment",IF(L44="","",L44),""))))</f>
+        <v/>
+      </c>
+      <c r="I44" s="31" t="n"/>
+      <c r="J44" s="29" t="n"/>
+      <c r="K44" s="31" t="n">
         <v>800000</v>
       </c>
-      <c r="K44" s="31" t="n"/>
       <c r="L44" s="31" t="n"/>
-      <c r="M44" s="31" t="n"/>
-      <c r="N44" s="26" t="inlineStr">
+      <c r="M44" s="32">
+        <f>IF(OR(L44="",H44="",G44="Judgment"),"",IFERROR(L44/H44-1,""))</f>
+        <v/>
+      </c>
+      <c r="N44" s="31" t="n"/>
+      <c r="O44" s="31" t="n"/>
+      <c r="P44" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O44" s="12" t="inlineStr">
+      <c r="Q44" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P44" s="12" t="inlineStr">
+      <c r="R44" s="12" t="inlineStr">
         <is>
           <t>General ledger</t>
         </is>
       </c>
-      <c r="Q44" s="12" t="inlineStr"/>
-      <c r="R44" s="32">
-        <f>IF(OR(K44="",G44="",F44="Judgment"),"",IFERROR(K44/G44-1,""))</f>
-        <v/>
-      </c>
-      <c r="S44" s="11" t="n"/>
+      <c r="S44" s="12" t="inlineStr"/>
+      <c r="T44" s="11" t="n"/>
     </row>
     <row r="45" ht="31" customHeight="1">
       <c r="A45" s="11" t="n">
@@ -3623,49 +3688,50 @@
           <t>Training costs, travel for training, related headcount</t>
         </is>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="12" t="inlineStr"/>
+      <c r="F45" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F45" s="26" t="inlineStr">
+      <c r="G45" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G45" s="30">
-        <f>IF(F45="Validated actual",IF(H45="","",H45),IF(F45="Calculated",IF(I45="","",I45),IF(F45="Reference value",IF(J45="","",J45),IF(F45="Judgment",IF(K45="","",K45),""))))</f>
-        <v/>
-      </c>
-      <c r="H45" s="31" t="n"/>
-      <c r="I45" s="29" t="n"/>
-      <c r="J45" s="31" t="n">
+      <c r="H45" s="30">
+        <f>IF(G45="Validated actual",IF(I45="","",I45),IF(G45="Calculated",IF(J45="","",J45),IF(G45="Reference value",IF(K45="","",K45),IF(G45="Judgment",IF(L45="","",L45),""))))</f>
+        <v/>
+      </c>
+      <c r="I45" s="31" t="n"/>
+      <c r="J45" s="29" t="n"/>
+      <c r="K45" s="31" t="n">
         <v>500000</v>
       </c>
-      <c r="K45" s="31" t="n"/>
       <c r="L45" s="31" t="n"/>
-      <c r="M45" s="31" t="n"/>
-      <c r="N45" s="26" t="inlineStr">
+      <c r="M45" s="32">
+        <f>IF(OR(L45="",H45="",G45="Judgment"),"",IFERROR(L45/H45-1,""))</f>
+        <v/>
+      </c>
+      <c r="N45" s="31" t="n"/>
+      <c r="O45" s="31" t="n"/>
+      <c r="P45" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O45" s="12" t="inlineStr">
+      <c r="Q45" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P45" s="12" t="inlineStr">
+      <c r="R45" s="12" t="inlineStr">
         <is>
           <t>General ledger</t>
         </is>
       </c>
-      <c r="Q45" s="12" t="inlineStr"/>
-      <c r="R45" s="32">
-        <f>IF(OR(K45="",G45="",F45="Judgment"),"",IFERROR(K45/G45-1,""))</f>
-        <v/>
-      </c>
-      <c r="S45" s="11" t="n"/>
+      <c r="S45" s="12" t="inlineStr"/>
+      <c r="T45" s="11" t="n"/>
     </row>
     <row r="46" ht="31" customHeight="1">
       <c r="A46" s="11" t="n">
@@ -3686,51 +3752,52 @@
           <t>Contests, recognition trips, non-quota commissions</t>
         </is>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="12" t="inlineStr"/>
+      <c r="F46" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F46" s="26" t="inlineStr">
+      <c r="G46" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G46" s="30">
-        <f>IF(F46="Validated actual",IF(H46="","",H46),IF(F46="Calculated",IF(I46="","",I46),IF(F46="Reference value",IF(J46="","",J46),IF(F46="Judgment",IF(K46="","",K46),""))))</f>
-        <v/>
-      </c>
-      <c r="H46" s="31" t="n"/>
-      <c r="I46" s="29" t="n"/>
-      <c r="J46" s="31" t="n">
+      <c r="H46" s="30">
+        <f>IF(G46="Validated actual",IF(I46="","",I46),IF(G46="Calculated",IF(J46="","",J46),IF(G46="Reference value",IF(K46="","",K46),IF(G46="Judgment",IF(L46="","",L46),""))))</f>
+        <v/>
+      </c>
+      <c r="I46" s="31" t="n"/>
+      <c r="J46" s="29" t="n"/>
+      <c r="K46" s="31" t="n">
         <v>750000</v>
       </c>
-      <c r="K46" s="31" t="n"/>
       <c r="L46" s="31" t="n"/>
-      <c r="M46" s="31" t="n"/>
-      <c r="N46" s="26" t="inlineStr">
+      <c r="M46" s="32">
+        <f>IF(OR(L46="",H46="",G46="Judgment"),"",IFERROR(L46/H46-1,""))</f>
+        <v/>
+      </c>
+      <c r="N46" s="31" t="n"/>
+      <c r="O46" s="31" t="n"/>
+      <c r="P46" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O46" s="12" t="inlineStr">
+      <c r="Q46" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P46" s="12" t="inlineStr">
+      <c r="R46" s="12" t="inlineStr">
         <is>
           <t>General ledger</t>
         </is>
       </c>
-      <c r="Q46" s="12" t="inlineStr"/>
-      <c r="R46" s="32">
-        <f>IF(OR(K46="",G46="",F46="Judgment"),"",IFERROR(K46/G46-1,""))</f>
-        <v/>
-      </c>
-      <c r="S46" s="11" t="n"/>
-    </row>
-    <row r="47" ht="31" customHeight="1">
+      <c r="S46" s="12" t="inlineStr"/>
+      <c r="T46" s="11" t="n"/>
+    </row>
+    <row r="47" ht="125.5" customHeight="1">
       <c r="A47" s="11" t="n">
         <v>4</v>
       </c>
@@ -3751,48 +3818,54 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
+          <t>Our goal with this exercise is to assess how well your company is is utilizing its sales and marketing assets. To do this, we have to examine all of the associated costs that are related to sales and marketing performance. This will help you put these investments in the right context and determine the effectiveness of these investments.
+This tracks all of the non-variable costs associated with running a sales organization, and includes executive salaries, sales support, training, and performance plans.</t>
+        </is>
+      </c>
+      <c r="F47" s="12" t="inlineStr">
+        <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F47" s="26" t="inlineStr">
+      <c r="G47" s="26" t="inlineStr">
         <is>
           <t>Calculated</t>
         </is>
       </c>
-      <c r="G47" s="30">
-        <f>IF(F47="Validated actual",IF(H47="","",H47),IF(F47="Calculated",IF(I47="","",I47),IF(F47="Reference value",IF(J47="","",J47),IF(F47="Judgment",IF(K47="","",K47),""))))</f>
-        <v/>
-      </c>
-      <c r="H47" s="31" t="n"/>
-      <c r="I47" s="39">
+      <c r="H47" s="30">
+        <f>IF(G47="Validated actual",IF(I47="","",I47),IF(G47="Calculated",IF(J47="","",J47),IF(G47="Reference value",IF(K47="","",K47),IF(G47="Judgment",IF(L47="","",L47),""))))</f>
+        <v/>
+      </c>
+      <c r="I47" s="31" t="n"/>
+      <c r="J47" s="39">
         <f>IFERROR(v_oh_managers+v_oh_engineers+v_oh_admin+v_oh_training+v_oh_incentives,"")</f>
         <v/>
       </c>
-      <c r="J47" s="31" t="n"/>
       <c r="K47" s="31" t="n"/>
       <c r="L47" s="31" t="n"/>
-      <c r="M47" s="31" t="n"/>
-      <c r="N47" s="26" t="inlineStr"/>
-      <c r="O47" s="12" t="inlineStr">
+      <c r="M47" s="32">
+        <f>IF(OR(L47="",H47="",G47="Judgment"),"",IFERROR(L47/H47-1,""))</f>
+        <v/>
+      </c>
+      <c r="N47" s="31" t="n"/>
+      <c r="O47" s="31" t="n"/>
+      <c r="P47" s="26" t="inlineStr"/>
+      <c r="Q47" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P47" s="12" t="inlineStr">
+      <c r="R47" s="12" t="inlineStr">
         <is>
           <t>Sum of the lines above</t>
         </is>
       </c>
-      <c r="Q47" s="12" t="inlineStr">
+      <c r="S47" s="12" t="inlineStr">
         <is>
           <t>Ledger total differs</t>
         </is>
       </c>
-      <c r="R47" s="32">
-        <f>IF(OR(K47="",G47="",F47="Judgment"),"",IFERROR(K47/G47-1,""))</f>
-        <v/>
-      </c>
-      <c r="S47" s="11" t="n">
+      <c r="T47" s="11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3815,49 +3888,50 @@
           <t>All marketing staff</t>
         </is>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="12" t="inlineStr"/>
+      <c r="F48" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F48" s="26" t="inlineStr">
+      <c r="G48" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G48" s="30">
-        <f>IF(F48="Validated actual",IF(H48="","",H48),IF(F48="Calculated",IF(I48="","",I48),IF(F48="Reference value",IF(J48="","",J48),IF(F48="Judgment",IF(K48="","",K48),""))))</f>
-        <v/>
-      </c>
-      <c r="H48" s="31" t="n"/>
-      <c r="I48" s="29" t="n"/>
-      <c r="J48" s="31" t="n">
+      <c r="H48" s="30">
+        <f>IF(G48="Validated actual",IF(I48="","",I48),IF(G48="Calculated",IF(J48="","",J48),IF(G48="Reference value",IF(K48="","",K48),IF(G48="Judgment",IF(L48="","",L48),""))))</f>
+        <v/>
+      </c>
+      <c r="I48" s="31" t="n"/>
+      <c r="J48" s="29" t="n"/>
+      <c r="K48" s="31" t="n">
         <v>1000000</v>
       </c>
-      <c r="K48" s="31" t="n"/>
       <c r="L48" s="31" t="n"/>
-      <c r="M48" s="31" t="n"/>
-      <c r="N48" s="26" t="inlineStr">
+      <c r="M48" s="32">
+        <f>IF(OR(L48="",H48="",G48="Judgment"),"",IFERROR(L48/H48-1,""))</f>
+        <v/>
+      </c>
+      <c r="N48" s="31" t="n"/>
+      <c r="O48" s="31" t="n"/>
+      <c r="P48" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O48" s="12" t="inlineStr">
+      <c r="Q48" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P48" s="12" t="inlineStr">
+      <c r="R48" s="12" t="inlineStr">
         <is>
           <t>General ledger</t>
         </is>
       </c>
-      <c r="Q48" s="12" t="inlineStr"/>
-      <c r="R48" s="32">
-        <f>IF(OR(K48="",G48="",F48="Judgment"),"",IFERROR(K48/G48-1,""))</f>
-        <v/>
-      </c>
-      <c r="S48" s="11" t="n"/>
+      <c r="S48" s="12" t="inlineStr"/>
+      <c r="T48" s="11" t="n"/>
     </row>
     <row r="49" ht="31" customHeight="1">
       <c r="A49" s="11" t="n">
@@ -3878,49 +3952,50 @@
           <t>Website investment and maintenance</t>
         </is>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="12" t="inlineStr"/>
+      <c r="F49" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F49" s="26" t="inlineStr">
+      <c r="G49" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G49" s="30">
-        <f>IF(F49="Validated actual",IF(H49="","",H49),IF(F49="Calculated",IF(I49="","",I49),IF(F49="Reference value",IF(J49="","",J49),IF(F49="Judgment",IF(K49="","",K49),""))))</f>
-        <v/>
-      </c>
-      <c r="H49" s="31" t="n"/>
-      <c r="I49" s="29" t="n"/>
-      <c r="J49" s="31" t="n">
+      <c r="H49" s="30">
+        <f>IF(G49="Validated actual",IF(I49="","",I49),IF(G49="Calculated",IF(J49="","",J49),IF(G49="Reference value",IF(K49="","",K49),IF(G49="Judgment",IF(L49="","",L49),""))))</f>
+        <v/>
+      </c>
+      <c r="I49" s="31" t="n"/>
+      <c r="J49" s="29" t="n"/>
+      <c r="K49" s="31" t="n">
         <v>250000</v>
       </c>
-      <c r="K49" s="31" t="n"/>
       <c r="L49" s="31" t="n"/>
-      <c r="M49" s="31" t="n"/>
-      <c r="N49" s="26" t="inlineStr">
+      <c r="M49" s="32">
+        <f>IF(OR(L49="",H49="",G49="Judgment"),"",IFERROR(L49/H49-1,""))</f>
+        <v/>
+      </c>
+      <c r="N49" s="31" t="n"/>
+      <c r="O49" s="31" t="n"/>
+      <c r="P49" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O49" s="12" t="inlineStr">
+      <c r="Q49" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P49" s="12" t="inlineStr">
+      <c r="R49" s="12" t="inlineStr">
         <is>
           <t>General ledger</t>
         </is>
       </c>
-      <c r="Q49" s="12" t="inlineStr"/>
-      <c r="R49" s="32">
-        <f>IF(OR(K49="",G49="",F49="Judgment"),"",IFERROR(K49/G49-1,""))</f>
-        <v/>
-      </c>
-      <c r="S49" s="11" t="n"/>
+      <c r="S49" s="12" t="inlineStr"/>
+      <c r="T49" s="11" t="n"/>
     </row>
     <row r="50" ht="31" customHeight="1">
       <c r="A50" s="11" t="n">
@@ -3941,49 +4016,50 @@
           <t>Online events and roadshows</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="12" t="inlineStr"/>
+      <c r="F50" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F50" s="26" t="inlineStr">
+      <c r="G50" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G50" s="30">
-        <f>IF(F50="Validated actual",IF(H50="","",H50),IF(F50="Calculated",IF(I50="","",I50),IF(F50="Reference value",IF(J50="","",J50),IF(F50="Judgment",IF(K50="","",K50),""))))</f>
-        <v/>
-      </c>
-      <c r="H50" s="31" t="n"/>
-      <c r="I50" s="29" t="n"/>
-      <c r="J50" s="31" t="n">
+      <c r="H50" s="30">
+        <f>IF(G50="Validated actual",IF(I50="","",I50),IF(G50="Calculated",IF(J50="","",J50),IF(G50="Reference value",IF(K50="","",K50),IF(G50="Judgment",IF(L50="","",L50),""))))</f>
+        <v/>
+      </c>
+      <c r="I50" s="31" t="n"/>
+      <c r="J50" s="29" t="n"/>
+      <c r="K50" s="31" t="n">
         <v>500000</v>
       </c>
-      <c r="K50" s="31" t="n"/>
       <c r="L50" s="31" t="n"/>
-      <c r="M50" s="31" t="n"/>
-      <c r="N50" s="26" t="inlineStr">
+      <c r="M50" s="32">
+        <f>IF(OR(L50="",H50="",G50="Judgment"),"",IFERROR(L50/H50-1,""))</f>
+        <v/>
+      </c>
+      <c r="N50" s="31" t="n"/>
+      <c r="O50" s="31" t="n"/>
+      <c r="P50" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O50" s="12" t="inlineStr">
+      <c r="Q50" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P50" s="12" t="inlineStr">
+      <c r="R50" s="12" t="inlineStr">
         <is>
           <t>General ledger</t>
         </is>
       </c>
-      <c r="Q50" s="12" t="inlineStr"/>
-      <c r="R50" s="32">
-        <f>IF(OR(K50="",G50="",F50="Judgment"),"",IFERROR(K50/G50-1,""))</f>
-        <v/>
-      </c>
-      <c r="S50" s="11" t="n"/>
+      <c r="S50" s="12" t="inlineStr"/>
+      <c r="T50" s="11" t="n"/>
     </row>
     <row r="51" ht="31" customHeight="1">
       <c r="A51" s="11" t="n">
@@ -4004,49 +4080,50 @@
           <t>Paid media</t>
         </is>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="12" t="inlineStr"/>
+      <c r="F51" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F51" s="26" t="inlineStr">
+      <c r="G51" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G51" s="30">
-        <f>IF(F51="Validated actual",IF(H51="","",H51),IF(F51="Calculated",IF(I51="","",I51),IF(F51="Reference value",IF(J51="","",J51),IF(F51="Judgment",IF(K51="","",K51),""))))</f>
-        <v/>
-      </c>
-      <c r="H51" s="31" t="n"/>
-      <c r="I51" s="29" t="n"/>
-      <c r="J51" s="31" t="n">
+      <c r="H51" s="30">
+        <f>IF(G51="Validated actual",IF(I51="","",I51),IF(G51="Calculated",IF(J51="","",J51),IF(G51="Reference value",IF(K51="","",K51),IF(G51="Judgment",IF(L51="","",L51),""))))</f>
+        <v/>
+      </c>
+      <c r="I51" s="31" t="n"/>
+      <c r="J51" s="29" t="n"/>
+      <c r="K51" s="31" t="n">
         <v>500000</v>
       </c>
-      <c r="K51" s="31" t="n"/>
       <c r="L51" s="31" t="n"/>
-      <c r="M51" s="31" t="n"/>
-      <c r="N51" s="26" t="inlineStr">
+      <c r="M51" s="32">
+        <f>IF(OR(L51="",H51="",G51="Judgment"),"",IFERROR(L51/H51-1,""))</f>
+        <v/>
+      </c>
+      <c r="N51" s="31" t="n"/>
+      <c r="O51" s="31" t="n"/>
+      <c r="P51" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O51" s="12" t="inlineStr">
+      <c r="Q51" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P51" s="12" t="inlineStr">
+      <c r="R51" s="12" t="inlineStr">
         <is>
           <t>General ledger</t>
         </is>
       </c>
-      <c r="Q51" s="12" t="inlineStr"/>
-      <c r="R51" s="32">
-        <f>IF(OR(K51="",G51="",F51="Judgment"),"",IFERROR(K51/G51-1,""))</f>
-        <v/>
-      </c>
-      <c r="S51" s="11" t="n"/>
+      <c r="S51" s="12" t="inlineStr"/>
+      <c r="T51" s="11" t="n"/>
     </row>
     <row r="52" ht="31" customHeight="1">
       <c r="A52" s="11" t="n">
@@ -4067,49 +4144,50 @@
           <t>Print and online</t>
         </is>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="12" t="inlineStr"/>
+      <c r="F52" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F52" s="26" t="inlineStr">
+      <c r="G52" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G52" s="30">
-        <f>IF(F52="Validated actual",IF(H52="","",H52),IF(F52="Calculated",IF(I52="","",I52),IF(F52="Reference value",IF(J52="","",J52),IF(F52="Judgment",IF(K52="","",K52),""))))</f>
-        <v/>
-      </c>
-      <c r="H52" s="31" t="n"/>
-      <c r="I52" s="29" t="n"/>
-      <c r="J52" s="31" t="n">
+      <c r="H52" s="30">
+        <f>IF(G52="Validated actual",IF(I52="","",I52),IF(G52="Calculated",IF(J52="","",J52),IF(G52="Reference value",IF(K52="","",K52),IF(G52="Judgment",IF(L52="","",L52),""))))</f>
+        <v/>
+      </c>
+      <c r="I52" s="31" t="n"/>
+      <c r="J52" s="29" t="n"/>
+      <c r="K52" s="31" t="n">
         <v>250000</v>
       </c>
-      <c r="K52" s="31" t="n"/>
       <c r="L52" s="31" t="n"/>
-      <c r="M52" s="31" t="n"/>
-      <c r="N52" s="26" t="inlineStr">
+      <c r="M52" s="32">
+        <f>IF(OR(L52="",H52="",G52="Judgment"),"",IFERROR(L52/H52-1,""))</f>
+        <v/>
+      </c>
+      <c r="N52" s="31" t="n"/>
+      <c r="O52" s="31" t="n"/>
+      <c r="P52" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O52" s="12" t="inlineStr">
+      <c r="Q52" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P52" s="12" t="inlineStr">
+      <c r="R52" s="12" t="inlineStr">
         <is>
           <t>General ledger</t>
         </is>
       </c>
-      <c r="Q52" s="12" t="inlineStr"/>
-      <c r="R52" s="32">
-        <f>IF(OR(K52="",G52="",F52="Judgment"),"",IFERROR(K52/G52-1,""))</f>
-        <v/>
-      </c>
-      <c r="S52" s="11" t="n"/>
+      <c r="S52" s="12" t="inlineStr"/>
+      <c r="T52" s="11" t="n"/>
     </row>
     <row r="53" ht="31" customHeight="1">
       <c r="A53" s="11" t="n">
@@ -4130,49 +4208,50 @@
           <t>Telemarketing, SDR and BDR programs</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
+      <c r="E53" s="12" t="inlineStr"/>
+      <c r="F53" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F53" s="26" t="inlineStr">
+      <c r="G53" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G53" s="30">
-        <f>IF(F53="Validated actual",IF(H53="","",H53),IF(F53="Calculated",IF(I53="","",I53),IF(F53="Reference value",IF(J53="","",J53),IF(F53="Judgment",IF(K53="","",K53),""))))</f>
-        <v/>
-      </c>
-      <c r="H53" s="31" t="n"/>
-      <c r="I53" s="29" t="n"/>
-      <c r="J53" s="31" t="n">
+      <c r="H53" s="30">
+        <f>IF(G53="Validated actual",IF(I53="","",I53),IF(G53="Calculated",IF(J53="","",J53),IF(G53="Reference value",IF(K53="","",K53),IF(G53="Judgment",IF(L53="","",L53),""))))</f>
+        <v/>
+      </c>
+      <c r="I53" s="31" t="n"/>
+      <c r="J53" s="29" t="n"/>
+      <c r="K53" s="31" t="n">
         <v>250000</v>
       </c>
-      <c r="K53" s="31" t="n"/>
       <c r="L53" s="31" t="n"/>
-      <c r="M53" s="31" t="n"/>
-      <c r="N53" s="26" t="inlineStr">
+      <c r="M53" s="32">
+        <f>IF(OR(L53="",H53="",G53="Judgment"),"",IFERROR(L53/H53-1,""))</f>
+        <v/>
+      </c>
+      <c r="N53" s="31" t="n"/>
+      <c r="O53" s="31" t="n"/>
+      <c r="P53" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O53" s="12" t="inlineStr">
+      <c r="Q53" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P53" s="12" t="inlineStr">
+      <c r="R53" s="12" t="inlineStr">
         <is>
           <t>General ledger</t>
         </is>
       </c>
-      <c r="Q53" s="12" t="inlineStr"/>
-      <c r="R53" s="32">
-        <f>IF(OR(K53="",G53="",F53="Judgment"),"",IFERROR(K53/G53-1,""))</f>
-        <v/>
-      </c>
-      <c r="S53" s="11" t="n"/>
+      <c r="S53" s="12" t="inlineStr"/>
+      <c r="T53" s="11" t="n"/>
     </row>
     <row r="54" ht="31" customHeight="1">
       <c r="A54" s="11" t="n">
@@ -4193,49 +4272,50 @@
           <t>Identity, PR, consulting</t>
         </is>
       </c>
-      <c r="E54" s="12" t="inlineStr">
+      <c r="E54" s="12" t="inlineStr"/>
+      <c r="F54" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F54" s="26" t="inlineStr">
+      <c r="G54" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G54" s="30">
-        <f>IF(F54="Validated actual",IF(H54="","",H54),IF(F54="Calculated",IF(I54="","",I54),IF(F54="Reference value",IF(J54="","",J54),IF(F54="Judgment",IF(K54="","",K54),""))))</f>
-        <v/>
-      </c>
-      <c r="H54" s="31" t="n"/>
-      <c r="I54" s="29" t="n"/>
-      <c r="J54" s="31" t="n">
+      <c r="H54" s="30">
+        <f>IF(G54="Validated actual",IF(I54="","",I54),IF(G54="Calculated",IF(J54="","",J54),IF(G54="Reference value",IF(K54="","",K54),IF(G54="Judgment",IF(L54="","",L54),""))))</f>
+        <v/>
+      </c>
+      <c r="I54" s="31" t="n"/>
+      <c r="J54" s="29" t="n"/>
+      <c r="K54" s="31" t="n">
         <v>200000</v>
       </c>
-      <c r="K54" s="31" t="n"/>
       <c r="L54" s="31" t="n"/>
-      <c r="M54" s="31" t="n"/>
-      <c r="N54" s="26" t="inlineStr">
+      <c r="M54" s="32">
+        <f>IF(OR(L54="",H54="",G54="Judgment"),"",IFERROR(L54/H54-1,""))</f>
+        <v/>
+      </c>
+      <c r="N54" s="31" t="n"/>
+      <c r="O54" s="31" t="n"/>
+      <c r="P54" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O54" s="12" t="inlineStr">
+      <c r="Q54" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P54" s="12" t="inlineStr">
+      <c r="R54" s="12" t="inlineStr">
         <is>
           <t>General ledger</t>
         </is>
       </c>
-      <c r="Q54" s="12" t="inlineStr"/>
-      <c r="R54" s="32">
-        <f>IF(OR(K54="",G54="",F54="Judgment"),"",IFERROR(K54/G54-1,""))</f>
-        <v/>
-      </c>
-      <c r="S54" s="11" t="n"/>
+      <c r="S54" s="12" t="inlineStr"/>
+      <c r="T54" s="11" t="n"/>
     </row>
     <row r="55" ht="31" customHeight="1">
       <c r="A55" s="11" t="n">
@@ -4256,51 +4336,52 @@
           <t>Sales tools, white papers, brochures, printing</t>
         </is>
       </c>
-      <c r="E55" s="12" t="inlineStr">
+      <c r="E55" s="12" t="inlineStr"/>
+      <c r="F55" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F55" s="26" t="inlineStr">
+      <c r="G55" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G55" s="30">
-        <f>IF(F55="Validated actual",IF(H55="","",H55),IF(F55="Calculated",IF(I55="","",I55),IF(F55="Reference value",IF(J55="","",J55),IF(F55="Judgment",IF(K55="","",K55),""))))</f>
-        <v/>
-      </c>
-      <c r="H55" s="31" t="n"/>
-      <c r="I55" s="29" t="n"/>
-      <c r="J55" s="31" t="n">
+      <c r="H55" s="30">
+        <f>IF(G55="Validated actual",IF(I55="","",I55),IF(G55="Calculated",IF(J55="","",J55),IF(G55="Reference value",IF(K55="","",K55),IF(G55="Judgment",IF(L55="","",L55),""))))</f>
+        <v/>
+      </c>
+      <c r="I55" s="31" t="n"/>
+      <c r="J55" s="29" t="n"/>
+      <c r="K55" s="31" t="n">
         <v>750000</v>
       </c>
-      <c r="K55" s="31" t="n"/>
       <c r="L55" s="31" t="n"/>
-      <c r="M55" s="31" t="n"/>
-      <c r="N55" s="26" t="inlineStr">
+      <c r="M55" s="32">
+        <f>IF(OR(L55="",H55="",G55="Judgment"),"",IFERROR(L55/H55-1,""))</f>
+        <v/>
+      </c>
+      <c r="N55" s="31" t="n"/>
+      <c r="O55" s="31" t="n"/>
+      <c r="P55" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O55" s="12" t="inlineStr">
+      <c r="Q55" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P55" s="12" t="inlineStr">
+      <c r="R55" s="12" t="inlineStr">
         <is>
           <t>General ledger</t>
         </is>
       </c>
-      <c r="Q55" s="12" t="inlineStr"/>
-      <c r="R55" s="32">
-        <f>IF(OR(K55="",G55="",F55="Judgment"),"",IFERROR(K55/G55-1,""))</f>
-        <v/>
-      </c>
-      <c r="S55" s="11" t="n"/>
-    </row>
-    <row r="56" ht="31" customHeight="1">
+      <c r="S55" s="12" t="inlineStr"/>
+      <c r="T55" s="11" t="n"/>
+    </row>
+    <row r="56" ht="71.5" customHeight="1">
       <c r="A56" s="11" t="n">
         <v>4</v>
       </c>
@@ -4321,48 +4402,53 @@
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
+          <t>This tracks all of the overall investments the company makes to help drive revenue. Marketing resources are extremely important to consider because in most organizations the sales and marketing departments are not coordinated and this results in tremendous waste.</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="inlineStr">
+        <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F56" s="26" t="inlineStr">
+      <c r="G56" s="26" t="inlineStr">
         <is>
           <t>Calculated</t>
         </is>
       </c>
-      <c r="G56" s="30">
-        <f>IF(F56="Validated actual",IF(H56="","",H56),IF(F56="Calculated",IF(I56="","",I56),IF(F56="Reference value",IF(J56="","",J56),IF(F56="Judgment",IF(K56="","",K56),""))))</f>
-        <v/>
-      </c>
-      <c r="H56" s="31" t="n"/>
-      <c r="I56" s="39">
+      <c r="H56" s="30">
+        <f>IF(G56="Validated actual",IF(I56="","",I56),IF(G56="Calculated",IF(J56="","",J56),IF(G56="Reference value",IF(K56="","",K56),IF(G56="Judgment",IF(L56="","",L56),""))))</f>
+        <v/>
+      </c>
+      <c r="I56" s="31" t="n"/>
+      <c r="J56" s="39">
         <f>IFERROR(v_mk_people+v_mk_web+v_mk_events+v_mk_ads+v_mk_mail+v_mk_leadgen+v_mk_brand+v_mk_collateral,"")</f>
         <v/>
       </c>
-      <c r="J56" s="31" t="n"/>
       <c r="K56" s="31" t="n"/>
       <c r="L56" s="31" t="n"/>
-      <c r="M56" s="31" t="n"/>
-      <c r="N56" s="26" t="inlineStr"/>
-      <c r="O56" s="12" t="inlineStr">
+      <c r="M56" s="32">
+        <f>IF(OR(L56="",H56="",G56="Judgment"),"",IFERROR(L56/H56-1,""))</f>
+        <v/>
+      </c>
+      <c r="N56" s="31" t="n"/>
+      <c r="O56" s="31" t="n"/>
+      <c r="P56" s="26" t="inlineStr"/>
+      <c r="Q56" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P56" s="12" t="inlineStr">
+      <c r="R56" s="12" t="inlineStr">
         <is>
           <t>Sum of the lines above</t>
         </is>
       </c>
-      <c r="Q56" s="12" t="inlineStr">
+      <c r="S56" s="12" t="inlineStr">
         <is>
           <t>Ledger total differs</t>
         </is>
       </c>
-      <c r="R56" s="32">
-        <f>IF(OR(K56="",G56="",F56="Judgment"),"",IFERROR(K56/G56-1,""))</f>
-        <v/>
-      </c>
-      <c r="S56" s="11" t="n">
+      <c r="T56" s="11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4385,43 +4471,44 @@
           <t>Commission expense for the period</t>
         </is>
       </c>
-      <c r="E57" s="12" t="inlineStr">
+      <c r="E57" s="12" t="inlineStr"/>
+      <c r="F57" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F57" s="26" t="inlineStr">
+      <c r="G57" s="26" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="G57" s="30">
-        <f>IF(F57="Validated actual",IF(H57="","",H57),IF(F57="Calculated",IF(I57="","",I57),IF(F57="Reference value",IF(J57="","",J57),IF(F57="Judgment",IF(K57="","",K57),""))))</f>
-        <v/>
-      </c>
-      <c r="H57" s="31" t="n"/>
-      <c r="I57" s="29" t="n"/>
-      <c r="J57" s="31" t="n"/>
+      <c r="H57" s="30">
+        <f>IF(G57="Validated actual",IF(I57="","",I57),IF(G57="Calculated",IF(J57="","",J57),IF(G57="Reference value",IF(K57="","",K57),IF(G57="Judgment",IF(L57="","",L57),""))))</f>
+        <v/>
+      </c>
+      <c r="I57" s="31" t="n"/>
+      <c r="J57" s="29" t="n"/>
       <c r="K57" s="31" t="n"/>
       <c r="L57" s="31" t="n"/>
-      <c r="M57" s="31" t="n"/>
-      <c r="N57" s="26" t="inlineStr"/>
-      <c r="O57" s="12" t="inlineStr">
+      <c r="M57" s="32">
+        <f>IF(OR(L57="",H57="",G57="Judgment"),"",IFERROR(L57/H57-1,""))</f>
+        <v/>
+      </c>
+      <c r="N57" s="31" t="n"/>
+      <c r="O57" s="31" t="n"/>
+      <c r="P57" s="26" t="inlineStr"/>
+      <c r="Q57" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P57" s="12" t="inlineStr">
+      <c r="R57" s="12" t="inlineStr">
         <is>
           <t>General ledger</t>
         </is>
       </c>
-      <c r="Q57" s="12" t="inlineStr"/>
-      <c r="R57" s="32">
-        <f>IF(OR(K57="",G57="",F57="Judgment"),"",IFERROR(K57/G57-1,""))</f>
-        <v/>
-      </c>
-      <c r="S57" s="11" t="n"/>
+      <c r="S57" s="12" t="inlineStr"/>
+      <c r="T57" s="11" t="n"/>
     </row>
     <row r="58" ht="31" customHeight="1">
       <c r="A58" s="11" t="n">
@@ -4442,47 +4529,48 @@
           <t>Salaries, benefits and commissions of quota-carrying salespeople</t>
         </is>
       </c>
-      <c r="E58" s="12" t="inlineStr">
+      <c r="E58" s="12" t="inlineStr"/>
+      <c r="F58" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F58" s="26" t="inlineStr">
+      <c r="G58" s="26" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="G58" s="30">
-        <f>IF(F58="Validated actual",IF(H58="","",H58),IF(F58="Calculated",IF(I58="","",I58),IF(F58="Reference value",IF(J58="","",J58),IF(F58="Judgment",IF(K58="","",K58),""))))</f>
-        <v/>
-      </c>
-      <c r="H58" s="31" t="n"/>
-      <c r="I58" s="29" t="n"/>
-      <c r="J58" s="31" t="n"/>
+      <c r="H58" s="30">
+        <f>IF(G58="Validated actual",IF(I58="","",I58),IF(G58="Calculated",IF(J58="","",J58),IF(G58="Reference value",IF(K58="","",K58),IF(G58="Judgment",IF(L58="","",L58),""))))</f>
+        <v/>
+      </c>
+      <c r="I58" s="31" t="n"/>
+      <c r="J58" s="29" t="n"/>
       <c r="K58" s="31" t="n"/>
       <c r="L58" s="31" t="n"/>
-      <c r="M58" s="31" t="n"/>
-      <c r="N58" s="26" t="inlineStr"/>
-      <c r="O58" s="12" t="inlineStr">
+      <c r="M58" s="32">
+        <f>IF(OR(L58="",H58="",G58="Judgment"),"",IFERROR(L58/H58-1,""))</f>
+        <v/>
+      </c>
+      <c r="N58" s="31" t="n"/>
+      <c r="O58" s="31" t="n"/>
+      <c r="P58" s="26" t="inlineStr"/>
+      <c r="Q58" s="12" t="inlineStr">
         <is>
           <t>Finance</t>
         </is>
       </c>
-      <c r="P58" s="12" t="inlineStr">
+      <c r="R58" s="12" t="inlineStr">
         <is>
           <t>General ledger</t>
         </is>
       </c>
-      <c r="Q58" s="12" t="inlineStr">
+      <c r="S58" s="12" t="inlineStr">
         <is>
           <t>Used by the compensation cross-check</t>
         </is>
       </c>
-      <c r="R58" s="32">
-        <f>IF(OR(K58="",G58="",F58="Judgment"),"",IFERROR(K58/G58-1,""))</f>
-        <v/>
-      </c>
-      <c r="S58" s="11" t="n">
+      <c r="T58" s="11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4510,6 +4598,7 @@
       <c r="Q59" s="21" t="n"/>
       <c r="R59" s="21" t="n"/>
       <c r="S59" s="21" t="n"/>
+      <c r="T59" s="21" t="n"/>
     </row>
     <row r="60" ht="31" customHeight="1">
       <c r="A60" s="11" t="n">
@@ -4530,47 +4619,48 @@
           <t>People employed in quota-carrying roles</t>
         </is>
       </c>
-      <c r="E60" s="12" t="inlineStr">
+      <c r="E60" s="12" t="inlineStr"/>
+      <c r="F60" s="12" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="F60" s="26" t="inlineStr">
+      <c r="G60" s="26" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="G60" s="33">
-        <f>IF(F60="Validated actual",IF(H60="","",H60),IF(F60="Calculated",IF(I60="","",I60),IF(F60="Reference value",IF(J60="","",J60),IF(F60="Judgment",IF(K60="","",K60),""))))</f>
-        <v/>
-      </c>
-      <c r="H60" s="34" t="n"/>
-      <c r="I60" s="29" t="n"/>
-      <c r="J60" s="34" t="n"/>
+      <c r="H60" s="33">
+        <f>IF(G60="Validated actual",IF(I60="","",I60),IF(G60="Calculated",IF(J60="","",J60),IF(G60="Reference value",IF(K60="","",K60),IF(G60="Judgment",IF(L60="","",L60),""))))</f>
+        <v/>
+      </c>
+      <c r="I60" s="34" t="n"/>
+      <c r="J60" s="29" t="n"/>
       <c r="K60" s="34" t="n"/>
       <c r="L60" s="34" t="n"/>
-      <c r="M60" s="34" t="n"/>
-      <c r="N60" s="26" t="inlineStr"/>
-      <c r="O60" s="12" t="inlineStr">
+      <c r="M60" s="32">
+        <f>IF(OR(L60="",H60="",G60="Judgment"),"",IFERROR(L60/H60-1,""))</f>
+        <v/>
+      </c>
+      <c r="N60" s="34" t="n"/>
+      <c r="O60" s="34" t="n"/>
+      <c r="P60" s="26" t="inlineStr"/>
+      <c r="Q60" s="12" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="P60" s="12" t="inlineStr">
+      <c r="R60" s="12" t="inlineStr">
         <is>
           <t>HR roster export</t>
         </is>
       </c>
-      <c r="Q60" s="12" t="inlineStr">
+      <c r="S60" s="12" t="inlineStr">
         <is>
           <t>Territory plan shows a different number of filled territories</t>
         </is>
       </c>
-      <c r="R60" s="32">
-        <f>IF(OR(K60="",G60="",F60="Judgment"),"",IFERROR(K60/G60-1,""))</f>
-        <v/>
-      </c>
-      <c r="S60" s="11" t="n">
+      <c r="T60" s="11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4593,43 +4683,44 @@
           <t>Quota-carrying hires</t>
         </is>
       </c>
-      <c r="E61" s="12" t="inlineStr">
+      <c r="E61" s="12" t="inlineStr"/>
+      <c r="F61" s="12" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="F61" s="26" t="inlineStr">
+      <c r="G61" s="26" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="G61" s="33">
-        <f>IF(F61="Validated actual",IF(H61="","",H61),IF(F61="Calculated",IF(I61="","",I61),IF(F61="Reference value",IF(J61="","",J61),IF(F61="Judgment",IF(K61="","",K61),""))))</f>
-        <v/>
-      </c>
-      <c r="H61" s="34" t="n"/>
-      <c r="I61" s="29" t="n"/>
-      <c r="J61" s="34" t="n"/>
+      <c r="H61" s="33">
+        <f>IF(G61="Validated actual",IF(I61="","",I61),IF(G61="Calculated",IF(J61="","",J61),IF(G61="Reference value",IF(K61="","",K61),IF(G61="Judgment",IF(L61="","",L61),""))))</f>
+        <v/>
+      </c>
+      <c r="I61" s="34" t="n"/>
+      <c r="J61" s="29" t="n"/>
       <c r="K61" s="34" t="n"/>
       <c r="L61" s="34" t="n"/>
-      <c r="M61" s="34" t="n"/>
-      <c r="N61" s="26" t="inlineStr"/>
-      <c r="O61" s="12" t="inlineStr">
+      <c r="M61" s="32">
+        <f>IF(OR(L61="",H61="",G61="Judgment"),"",IFERROR(L61/H61-1,""))</f>
+        <v/>
+      </c>
+      <c r="N61" s="34" t="n"/>
+      <c r="O61" s="34" t="n"/>
+      <c r="P61" s="26" t="inlineStr"/>
+      <c r="Q61" s="12" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="P61" s="12" t="inlineStr">
+      <c r="R61" s="12" t="inlineStr">
         <is>
           <t>HR roster export</t>
         </is>
       </c>
-      <c r="Q61" s="12" t="inlineStr"/>
-      <c r="R61" s="32">
-        <f>IF(OR(K61="",G61="",F61="Judgment"),"",IFERROR(K61/G61-1,""))</f>
-        <v/>
-      </c>
-      <c r="S61" s="11" t="n">
+      <c r="S61" s="12" t="inlineStr"/>
+      <c r="T61" s="11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4652,47 +4743,48 @@
           <t>Quota-carrying departures</t>
         </is>
       </c>
-      <c r="E62" s="12" t="inlineStr">
+      <c r="E62" s="12" t="inlineStr"/>
+      <c r="F62" s="12" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="F62" s="26" t="inlineStr">
+      <c r="G62" s="26" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="G62" s="33">
-        <f>IF(F62="Validated actual",IF(H62="","",H62),IF(F62="Calculated",IF(I62="","",I62),IF(F62="Reference value",IF(J62="","",J62),IF(F62="Judgment",IF(K62="","",K62),""))))</f>
-        <v/>
-      </c>
-      <c r="H62" s="34" t="n"/>
-      <c r="I62" s="29" t="n"/>
-      <c r="J62" s="34" t="n"/>
+      <c r="H62" s="33">
+        <f>IF(G62="Validated actual",IF(I62="","",I62),IF(G62="Calculated",IF(J62="","",J62),IF(G62="Reference value",IF(K62="","",K62),IF(G62="Judgment",IF(L62="","",L62),""))))</f>
+        <v/>
+      </c>
+      <c r="I62" s="34" t="n"/>
+      <c r="J62" s="29" t="n"/>
       <c r="K62" s="34" t="n"/>
       <c r="L62" s="34" t="n"/>
-      <c r="M62" s="34" t="n"/>
-      <c r="N62" s="26" t="inlineStr"/>
-      <c r="O62" s="12" t="inlineStr">
+      <c r="M62" s="32">
+        <f>IF(OR(L62="",H62="",G62="Judgment"),"",IFERROR(L62/H62-1,""))</f>
+        <v/>
+      </c>
+      <c r="N62" s="34" t="n"/>
+      <c r="O62" s="34" t="n"/>
+      <c r="P62" s="26" t="inlineStr"/>
+      <c r="Q62" s="12" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="P62" s="12" t="inlineStr">
+      <c r="R62" s="12" t="inlineStr">
         <is>
           <t>HR roster export</t>
         </is>
       </c>
-      <c r="Q62" s="12" t="inlineStr"/>
-      <c r="R62" s="32">
-        <f>IF(OR(K62="",G62="",F62="Judgment"),"",IFERROR(K62/G62-1,""))</f>
-        <v/>
-      </c>
-      <c r="S62" s="11" t="n">
+      <c r="S62" s="12" t="inlineStr"/>
+      <c r="T62" s="11" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="63" ht="44.5" customHeight="1">
+    <row r="63" ht="58" customHeight="1">
       <c r="A63" s="11" t="n">
         <v>5</v>
       </c>
@@ -4711,50 +4803,51 @@
           <t>Salespeople working at full productivity on average. Calculated: filled seats − hires × share of year spent ramping</t>
         </is>
       </c>
-      <c r="E63" s="12" t="inlineStr">
+      <c r="E63" s="12" t="inlineStr"/>
+      <c r="F63" s="12" t="inlineStr">
         <is>
           <t>count1</t>
         </is>
       </c>
-      <c r="F63" s="26" t="inlineStr">
+      <c r="G63" s="26" t="inlineStr">
         <is>
           <t>Calculated</t>
         </is>
       </c>
-      <c r="G63" s="40">
-        <f>IF(F63="Validated actual",IF(H63="","",H63),IF(F63="Calculated",IF(I63="","",I63),IF(F63="Reference value",IF(J63="","",J63),IF(F63="Judgment",IF(K63="","",K63),""))))</f>
-        <v/>
-      </c>
-      <c r="H63" s="41" t="n"/>
-      <c r="I63" s="42">
+      <c r="H63" s="40">
+        <f>IF(G63="Validated actual",IF(I63="","",I63),IF(G63="Calculated",IF(J63="","",J63),IF(G63="Reference value",IF(K63="","",K63),IF(G63="Judgment",IF(L63="","",L63),""))))</f>
+        <v/>
+      </c>
+      <c r="I63" s="41" t="n"/>
+      <c r="J63" s="42">
         <f>IFERROR(MAX(0,v_filled_seats-v_hires*MIN(1,v_ramp_months/12)),"")</f>
         <v/>
       </c>
-      <c r="J63" s="41" t="n"/>
       <c r="K63" s="41" t="n"/>
       <c r="L63" s="41" t="n"/>
-      <c r="M63" s="41" t="n"/>
-      <c r="N63" s="26" t="inlineStr"/>
-      <c r="O63" s="12" t="inlineStr">
+      <c r="M63" s="32">
+        <f>IF(OR(L63="",H63="",G63="Judgment"),"",IFERROR(L63/H63-1,""))</f>
+        <v/>
+      </c>
+      <c r="N63" s="41" t="n"/>
+      <c r="O63" s="41" t="n"/>
+      <c r="P63" s="26" t="inlineStr"/>
+      <c r="Q63" s="12" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="P63" s="12" t="inlineStr">
+      <c r="R63" s="12" t="inlineStr">
         <is>
           <t>Roster with start dates</t>
         </is>
       </c>
-      <c r="Q63" s="12" t="inlineStr">
+      <c r="S63" s="12" t="inlineStr">
         <is>
           <t>Productivity by tenure shows a different ramp</t>
         </is>
       </c>
-      <c r="R63" s="32">
-        <f>IF(OR(K63="",G63="",F63="Judgment"),"",IFERROR(K63/G63-1,""))</f>
-        <v/>
-      </c>
-      <c r="S63" s="11" t="n">
+      <c r="T63" s="11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4782,8 +4875,9 @@
       <c r="Q64" s="21" t="n"/>
       <c r="R64" s="21" t="n"/>
       <c r="S64" s="21" t="n"/>
-    </row>
-    <row r="65" ht="44.5" customHeight="1">
+      <c r="T64" s="21" t="n"/>
+    </row>
+    <row r="65" ht="58" customHeight="1">
       <c r="A65" s="11" t="n">
         <v>6</v>
       </c>
@@ -4804,51 +4898,56 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
+          <t>Enter the number of open sales territories you had last year. This is not based on individual people, so if someone has left the company, but the territory is still open, count that as a sales territory.</t>
+        </is>
+      </c>
+      <c r="F65" s="12" t="inlineStr">
+        <is>
           <t>count</t>
         </is>
       </c>
-      <c r="F65" s="26" t="inlineStr">
+      <c r="G65" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G65" s="33">
-        <f>IF(F65="Validated actual",IF(H65="","",H65),IF(F65="Calculated",IF(I65="","",I65),IF(F65="Reference value",IF(J65="","",J65),IF(F65="Judgment",IF(K65="","",K65),""))))</f>
-        <v/>
-      </c>
-      <c r="H65" s="34" t="n"/>
-      <c r="I65" s="29" t="n"/>
-      <c r="J65" s="34" t="n">
+      <c r="H65" s="33">
+        <f>IF(G65="Validated actual",IF(I65="","",I65),IF(G65="Calculated",IF(J65="","",J65),IF(G65="Reference value",IF(K65="","",K65),IF(G65="Judgment",IF(L65="","",L65),""))))</f>
+        <v/>
+      </c>
+      <c r="I65" s="34" t="n"/>
+      <c r="J65" s="29" t="n"/>
+      <c r="K65" s="34" t="n">
         <v>100</v>
       </c>
-      <c r="K65" s="34" t="n"/>
       <c r="L65" s="34" t="n"/>
-      <c r="M65" s="34" t="n"/>
-      <c r="N65" s="26" t="inlineStr">
+      <c r="M65" s="32">
+        <f>IF(OR(L65="",H65="",G65="Judgment"),"",IFERROR(L65/H65-1,""))</f>
+        <v/>
+      </c>
+      <c r="N65" s="34" t="n"/>
+      <c r="O65" s="34" t="n"/>
+      <c r="P65" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O65" s="12" t="inlineStr">
+      <c r="Q65" s="12" t="inlineStr">
         <is>
           <t>Sales Operations</t>
         </is>
       </c>
-      <c r="P65" s="12" t="inlineStr">
+      <c r="R65" s="12" t="inlineStr">
         <is>
           <t>Territory plan</t>
         </is>
       </c>
-      <c r="Q65" s="12" t="inlineStr">
+      <c r="S65" s="12" t="inlineStr">
         <is>
           <t>Filled + open territories differ from this count</t>
         </is>
       </c>
-      <c r="R65" s="32">
-        <f>IF(OR(K65="",G65="",F65="Judgment"),"",IFERROR(K65/G65-1,""))</f>
-        <v/>
-      </c>
-      <c r="S65" s="11" t="n">
+      <c r="T65" s="11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4871,47 +4970,48 @@
           <t>Funded territories with no salesperson assigned</t>
         </is>
       </c>
-      <c r="E66" s="12" t="inlineStr">
+      <c r="E66" s="12" t="inlineStr"/>
+      <c r="F66" s="12" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="F66" s="26" t="inlineStr">
+      <c r="G66" s="26" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="G66" s="33">
-        <f>IF(F66="Validated actual",IF(H66="","",H66),IF(F66="Calculated",IF(I66="","",I66),IF(F66="Reference value",IF(J66="","",J66),IF(F66="Judgment",IF(K66="","",K66),""))))</f>
-        <v/>
-      </c>
-      <c r="H66" s="34" t="n"/>
-      <c r="I66" s="29" t="n"/>
-      <c r="J66" s="34" t="n"/>
+      <c r="H66" s="33">
+        <f>IF(G66="Validated actual",IF(I66="","",I66),IF(G66="Calculated",IF(J66="","",J66),IF(G66="Reference value",IF(K66="","",K66),IF(G66="Judgment",IF(L66="","",L66),""))))</f>
+        <v/>
+      </c>
+      <c r="I66" s="34" t="n"/>
+      <c r="J66" s="29" t="n"/>
       <c r="K66" s="34" t="n"/>
       <c r="L66" s="34" t="n"/>
-      <c r="M66" s="34" t="n"/>
-      <c r="N66" s="26" t="inlineStr"/>
-      <c r="O66" s="12" t="inlineStr">
+      <c r="M66" s="32">
+        <f>IF(OR(L66="",H66="",G66="Judgment"),"",IFERROR(L66/H66-1,""))</f>
+        <v/>
+      </c>
+      <c r="N66" s="34" t="n"/>
+      <c r="O66" s="34" t="n"/>
+      <c r="P66" s="26" t="inlineStr"/>
+      <c r="Q66" s="12" t="inlineStr">
         <is>
           <t>Sales Operations</t>
         </is>
       </c>
-      <c r="P66" s="12" t="inlineStr">
+      <c r="R66" s="12" t="inlineStr">
         <is>
           <t>Territory plan</t>
         </is>
       </c>
-      <c r="Q66" s="12" t="inlineStr">
+      <c r="S66" s="12" t="inlineStr">
         <is>
           <t>Roster and plan disagree</t>
         </is>
       </c>
-      <c r="R66" s="32">
-        <f>IF(OR(K66="",G66="",F66="Judgment"),"",IFERROR(K66/G66-1,""))</f>
-        <v/>
-      </c>
-      <c r="S66" s="11" t="n">
+      <c r="T66" s="11" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4934,50 +5034,51 @@
           <t>Revenue a filled, ramped territory is expected to produce in a year</t>
         </is>
       </c>
-      <c r="E67" s="12" t="inlineStr">
+      <c r="E67" s="12" t="inlineStr"/>
+      <c r="F67" s="12" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F67" s="26" t="inlineStr">
+      <c r="G67" s="26" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="G67" s="30">
-        <f>IF(F67="Validated actual",IF(H67="","",H67),IF(F67="Calculated",IF(I67="","",I67),IF(F67="Reference value",IF(J67="","",J67),IF(F67="Judgment",IF(K67="","",K67),""))))</f>
-        <v/>
-      </c>
-      <c r="H67" s="31" t="n"/>
-      <c r="I67" s="39">
+      <c r="H67" s="30">
+        <f>IF(G67="Validated actual",IF(I67="","",I67),IF(G67="Calculated",IF(J67="","",J67),IF(G67="Reference value",IF(K67="","",K67),IF(G67="Judgment",IF(L67="","",L67),""))))</f>
+        <v/>
+      </c>
+      <c r="I67" s="31" t="n"/>
+      <c r="J67" s="39">
         <f>IFERROR(v_plan_target/v_territory_count,"")</f>
         <v/>
       </c>
-      <c r="J67" s="31" t="n"/>
       <c r="K67" s="31" t="n"/>
       <c r="L67" s="31" t="n"/>
-      <c r="M67" s="31" t="n"/>
-      <c r="N67" s="26" t="inlineStr"/>
-      <c r="O67" s="12" t="inlineStr">
+      <c r="M67" s="32">
+        <f>IF(OR(L67="",H67="",G67="Judgment"),"",IFERROR(L67/H67-1,""))</f>
+        <v/>
+      </c>
+      <c r="N67" s="31" t="n"/>
+      <c r="O67" s="31" t="n"/>
+      <c r="P67" s="26" t="inlineStr"/>
+      <c r="Q67" s="12" t="inlineStr">
         <is>
           <t>Sales Operations</t>
         </is>
       </c>
-      <c r="P67" s="12" t="inlineStr">
+      <c r="R67" s="12" t="inlineStr">
         <is>
           <t>Territory plan or quota letters</t>
         </is>
       </c>
-      <c r="Q67" s="12" t="inlineStr">
+      <c r="S67" s="12" t="inlineStr">
         <is>
           <t>Territories × expected yield differs from the plan</t>
         </is>
       </c>
-      <c r="R67" s="32">
-        <f>IF(OR(K67="",G67="",F67="Judgment"),"",IFERROR(K67/G67-1,""))</f>
-        <v/>
-      </c>
-      <c r="S67" s="11" t="n">
+      <c r="T67" s="11" t="n">
         <v>3</v>
       </c>
     </row>
@@ -5005,6 +5106,7 @@
       <c r="Q68" s="21" t="n"/>
       <c r="R68" s="21" t="n"/>
       <c r="S68" s="21" t="n"/>
+      <c r="T68" s="21" t="n"/>
     </row>
     <row r="69" ht="17.5" customHeight="1">
       <c r="A69" s="11" t="n">
@@ -5025,43 +5127,44 @@
           <t>Closed as won in the period</t>
         </is>
       </c>
-      <c r="E69" s="12" t="inlineStr">
+      <c r="E69" s="12" t="inlineStr"/>
+      <c r="F69" s="12" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="F69" s="26" t="inlineStr">
+      <c r="G69" s="26" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="G69" s="33">
-        <f>IF(F69="Validated actual",IF(H69="","",H69),IF(F69="Calculated",IF(I69="","",I69),IF(F69="Reference value",IF(J69="","",J69),IF(F69="Judgment",IF(K69="","",K69),""))))</f>
-        <v/>
-      </c>
-      <c r="H69" s="34" t="n"/>
-      <c r="I69" s="29" t="n"/>
-      <c r="J69" s="34" t="n"/>
+      <c r="H69" s="33">
+        <f>IF(G69="Validated actual",IF(I69="","",I69),IF(G69="Calculated",IF(J69="","",J69),IF(G69="Reference value",IF(K69="","",K69),IF(G69="Judgment",IF(L69="","",L69),""))))</f>
+        <v/>
+      </c>
+      <c r="I69" s="34" t="n"/>
+      <c r="J69" s="29" t="n"/>
       <c r="K69" s="34" t="n"/>
       <c r="L69" s="34" t="n"/>
-      <c r="M69" s="34" t="n"/>
-      <c r="N69" s="26" t="inlineStr"/>
-      <c r="O69" s="12" t="inlineStr">
+      <c r="M69" s="32">
+        <f>IF(OR(L69="",H69="",G69="Judgment"),"",IFERROR(L69/H69-1,""))</f>
+        <v/>
+      </c>
+      <c r="N69" s="34" t="n"/>
+      <c r="O69" s="34" t="n"/>
+      <c r="P69" s="26" t="inlineStr"/>
+      <c r="Q69" s="12" t="inlineStr">
         <is>
           <t>Sales Operations</t>
         </is>
       </c>
-      <c r="P69" s="12" t="inlineStr">
+      <c r="R69" s="12" t="inlineStr">
         <is>
           <t>CRM closed-opportunity report</t>
         </is>
       </c>
-      <c r="Q69" s="12" t="inlineStr"/>
-      <c r="R69" s="32">
-        <f>IF(OR(K69="",G69="",F69="Judgment"),"",IFERROR(K69/G69-1,""))</f>
-        <v/>
-      </c>
-      <c r="S69" s="11" t="n"/>
+      <c r="S69" s="12" t="inlineStr"/>
+      <c r="T69" s="11" t="n"/>
     </row>
     <row r="70" ht="17.5" customHeight="1">
       <c r="A70" s="11" t="n">
@@ -5082,45 +5185,46 @@
           <t>Closed as lost in the period</t>
         </is>
       </c>
-      <c r="E70" s="12" t="inlineStr">
+      <c r="E70" s="12" t="inlineStr"/>
+      <c r="F70" s="12" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="F70" s="26" t="inlineStr">
+      <c r="G70" s="26" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="G70" s="33">
-        <f>IF(F70="Validated actual",IF(H70="","",H70),IF(F70="Calculated",IF(I70="","",I70),IF(F70="Reference value",IF(J70="","",J70),IF(F70="Judgment",IF(K70="","",K70),""))))</f>
-        <v/>
-      </c>
-      <c r="H70" s="34" t="n"/>
-      <c r="I70" s="29" t="n"/>
-      <c r="J70" s="34" t="n"/>
+      <c r="H70" s="33">
+        <f>IF(G70="Validated actual",IF(I70="","",I70),IF(G70="Calculated",IF(J70="","",J70),IF(G70="Reference value",IF(K70="","",K70),IF(G70="Judgment",IF(L70="","",L70),""))))</f>
+        <v/>
+      </c>
+      <c r="I70" s="34" t="n"/>
+      <c r="J70" s="29" t="n"/>
       <c r="K70" s="34" t="n"/>
       <c r="L70" s="34" t="n"/>
-      <c r="M70" s="34" t="n"/>
-      <c r="N70" s="26" t="inlineStr"/>
-      <c r="O70" s="12" t="inlineStr">
+      <c r="M70" s="32">
+        <f>IF(OR(L70="",H70="",G70="Judgment"),"",IFERROR(L70/H70-1,""))</f>
+        <v/>
+      </c>
+      <c r="N70" s="34" t="n"/>
+      <c r="O70" s="34" t="n"/>
+      <c r="P70" s="26" t="inlineStr"/>
+      <c r="Q70" s="12" t="inlineStr">
         <is>
           <t>Sales Operations</t>
         </is>
       </c>
-      <c r="P70" s="12" t="inlineStr">
+      <c r="R70" s="12" t="inlineStr">
         <is>
           <t>CRM closed-opportunity report</t>
         </is>
       </c>
-      <c r="Q70" s="12" t="inlineStr"/>
-      <c r="R70" s="32">
-        <f>IF(OR(K70="",G70="",F70="Judgment"),"",IFERROR(K70/G70-1,""))</f>
-        <v/>
-      </c>
-      <c r="S70" s="11" t="n"/>
-    </row>
-    <row r="71" ht="31" customHeight="1">
+      <c r="S70" s="12" t="inlineStr"/>
+      <c r="T70" s="11" t="n"/>
+    </row>
+    <row r="71" ht="85" customHeight="1">
       <c r="A71" s="11" t="n">
         <v>7</v>
       </c>
@@ -5141,58 +5245,63 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
+          <t>This certainly can mean a lot of things to different people. Here we want to understand the effectiveness of how well your organization manages the sales process from first sales meeting to eventual close. Please estimate the percentage of all of the pipeline opportunities that your organization has worked that have resulted in an executed agreement.</t>
+        </is>
+      </c>
+      <c r="F71" s="12" t="inlineStr">
+        <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="F71" s="26" t="inlineStr">
+      <c r="G71" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G71" s="36">
-        <f>IF(F71="Validated actual",IF(H71="","",H71),IF(F71="Calculated",IF(I71="","",I71),IF(F71="Reference value",IF(J71="","",J71),IF(F71="Judgment",IF(K71="","",K71),""))))</f>
-        <v/>
-      </c>
-      <c r="H71" s="37" t="n"/>
-      <c r="I71" s="38">
+      <c r="H71" s="36">
+        <f>IF(G71="Validated actual",IF(I71="","",I71),IF(G71="Calculated",IF(J71="","",J71),IF(G71="Reference value",IF(K71="","",K71),IF(G71="Judgment",IF(L71="","",L71),""))))</f>
+        <v/>
+      </c>
+      <c r="I71" s="37" t="n"/>
+      <c r="J71" s="38">
         <f>IFERROR(v_opps_won/(v_opps_won+v_opps_lost),"")</f>
         <v/>
       </c>
-      <c r="J71" s="37" t="n">
+      <c r="K71" s="37" t="n">
         <v>0.25</v>
       </c>
-      <c r="K71" s="37" t="n"/>
       <c r="L71" s="37" t="n"/>
-      <c r="M71" s="37" t="n"/>
-      <c r="N71" s="26" t="inlineStr">
+      <c r="M71" s="32">
+        <f>IF(OR(L71="",H71="",G71="Judgment"),"",IFERROR(L71/H71-1,""))</f>
+        <v/>
+      </c>
+      <c r="N71" s="37" t="n"/>
+      <c r="O71" s="37" t="n"/>
+      <c r="P71" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O71" s="12" t="inlineStr">
+      <c r="Q71" s="12" t="inlineStr">
         <is>
           <t>Sales Operations</t>
         </is>
       </c>
-      <c r="P71" s="12" t="inlineStr">
+      <c r="R71" s="12" t="inlineStr">
         <is>
           <t>CRM closed-opportunity report</t>
         </is>
       </c>
-      <c r="Q71" s="12" t="inlineStr">
+      <c r="S71" s="12" t="inlineStr">
         <is>
           <t>CRM won ÷ (won + lost) differs</t>
         </is>
       </c>
-      <c r="R71" s="32">
-        <f>IF(OR(K71="",G71="",F71="Judgment"),"",IFERROR(K71/G71-1,""))</f>
-        <v/>
-      </c>
-      <c r="S71" s="11" t="n">
+      <c r="T71" s="11" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="72" ht="31" customHeight="1">
+    <row r="72" ht="112" customHeight="1">
       <c r="A72" s="11" t="n">
         <v>7</v>
       </c>
@@ -5213,55 +5322,60 @@
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
+          <t>Tracks how long from when a qualified opportunity enters the pipeline to when it closes as a sale. Your sales process may have many steps, so for simplicity track the time it takes from first meeting to the date the agreement is received by accounting. Most organizations do not track this information, so if you do not have the data - make an estimate. The single greatest impact you can have on your business is to shorten your sales cycle times.</t>
+        </is>
+      </c>
+      <c r="F72" s="12" t="inlineStr">
+        <is>
           <t>months</t>
         </is>
       </c>
-      <c r="F72" s="26" t="inlineStr">
+      <c r="G72" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G72" s="43">
-        <f>IF(F72="Validated actual",IF(H72="","",H72),IF(F72="Calculated",IF(I72="","",I72),IF(F72="Reference value",IF(J72="","",J72),IF(F72="Judgment",IF(K72="","",K72),""))))</f>
-        <v/>
-      </c>
-      <c r="H72" s="44" t="n"/>
-      <c r="I72" s="29" t="n"/>
-      <c r="J72" s="44" t="n">
+      <c r="H72" s="43">
+        <f>IF(G72="Validated actual",IF(I72="","",I72),IF(G72="Calculated",IF(J72="","",J72),IF(G72="Reference value",IF(K72="","",K72),IF(G72="Judgment",IF(L72="","",L72),""))))</f>
+        <v/>
+      </c>
+      <c r="I72" s="44" t="n"/>
+      <c r="J72" s="29" t="n"/>
+      <c r="K72" s="44" t="n">
         <v>6</v>
       </c>
-      <c r="K72" s="44" t="n"/>
       <c r="L72" s="44" t="n"/>
-      <c r="M72" s="44" t="n"/>
-      <c r="N72" s="26" t="inlineStr">
+      <c r="M72" s="32">
+        <f>IF(OR(L72="",H72="",G72="Judgment"),"",IFERROR(L72/H72-1,""))</f>
+        <v/>
+      </c>
+      <c r="N72" s="44" t="n"/>
+      <c r="O72" s="44" t="n"/>
+      <c r="P72" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O72" s="12" t="inlineStr">
+      <c r="Q72" s="12" t="inlineStr">
         <is>
           <t>Sales Operations</t>
         </is>
       </c>
-      <c r="P72" s="12" t="inlineStr">
+      <c r="R72" s="12" t="inlineStr">
         <is>
           <t>CRM closed-opportunity report</t>
         </is>
       </c>
-      <c r="Q72" s="12" t="inlineStr">
+      <c r="S72" s="12" t="inlineStr">
         <is>
           <t>CRM median cycle differs; Little's Law check fails</t>
         </is>
       </c>
-      <c r="R72" s="32">
-        <f>IF(OR(K72="",G72="",F72="Judgment"),"",IFERROR(K72/G72-1,""))</f>
-        <v/>
-      </c>
-      <c r="S72" s="11" t="n">
+      <c r="T72" s="11" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="73" ht="58" customHeight="1">
+    <row r="73" ht="112" customHeight="1">
       <c r="A73" s="11" t="n">
         <v>7</v>
       </c>
@@ -5282,54 +5396,59 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
+          <t>This is the average deal size for your company. For this simple analysis, you can get this figure by dividing your revenue by total number of contracts. For more detailed analysis, we recommend that you break things down into product lines, services offerings, and sales channels. You should also separate new client revenue from upselling your installed base. For professional services, credit the total esimated hours for a project towards one sales transaction.</t>
+        </is>
+      </c>
+      <c r="F73" s="12" t="inlineStr">
+        <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F73" s="26" t="inlineStr">
+      <c r="G73" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G73" s="30">
-        <f>IF(F73="Validated actual",IF(H73="","",H73),IF(F73="Calculated",IF(I73="","",I73),IF(F73="Reference value",IF(J73="","",J73),IF(F73="Judgment",IF(K73="","",K73),""))))</f>
-        <v/>
-      </c>
-      <c r="H73" s="31" t="n"/>
-      <c r="I73" s="39">
+      <c r="H73" s="30">
+        <f>IF(G73="Validated actual",IF(I73="","",I73),IF(G73="Calculated",IF(J73="","",J73),IF(G73="Reference value",IF(K73="","",K73),IF(G73="Judgment",IF(L73="","",L73),""))))</f>
+        <v/>
+      </c>
+      <c r="I73" s="31" t="n"/>
+      <c r="J73" s="39">
         <f>IFERROR(v_revenue/v_contracts,"")</f>
         <v/>
       </c>
-      <c r="J73" s="31" t="n">
+      <c r="K73" s="31" t="n">
         <v>75000</v>
       </c>
-      <c r="K73" s="31" t="n"/>
       <c r="L73" s="31" t="n"/>
-      <c r="M73" s="31" t="n"/>
-      <c r="N73" s="26" t="inlineStr">
+      <c r="M73" s="32">
+        <f>IF(OR(L73="",H73="",G73="Judgment"),"",IFERROR(L73/H73-1,""))</f>
+        <v/>
+      </c>
+      <c r="N73" s="31" t="n"/>
+      <c r="O73" s="31" t="n"/>
+      <c r="P73" s="26" t="inlineStr">
         <is>
           <t>Reference value from another client, chosen so the model fits companies of any size (as-is model)</t>
         </is>
       </c>
-      <c r="O73" s="12" t="inlineStr">
+      <c r="Q73" s="12" t="inlineStr">
         <is>
           <t>Sales Operations</t>
         </is>
       </c>
-      <c r="P73" s="12" t="inlineStr">
+      <c r="R73" s="12" t="inlineStr">
         <is>
           <t>Calculated from step 3</t>
         </is>
       </c>
-      <c r="Q73" s="12" t="inlineStr">
+      <c r="S73" s="12" t="inlineStr">
         <is>
           <t>Revenue ÷ contracts differs (deal size cross-check)</t>
         </is>
       </c>
-      <c r="R73" s="32">
-        <f>IF(OR(K73="",G73="",F73="Judgment"),"",IFERROR(K73/G73-1,""))</f>
-        <v/>
-      </c>
-      <c r="S73" s="11" t="n">
+      <c r="T73" s="11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5352,45 +5471,46 @@
           <t>Average of month-end open qualified opportunities</t>
         </is>
       </c>
-      <c r="E74" s="12" t="inlineStr">
+      <c r="E74" s="12" t="inlineStr"/>
+      <c r="F74" s="12" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="F74" s="26" t="inlineStr">
+      <c r="G74" s="26" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="G74" s="33">
-        <f>IF(F74="Validated actual",IF(H74="","",H74),IF(F74="Calculated",IF(I74="","",I74),IF(F74="Reference value",IF(J74="","",J74),IF(F74="Judgment",IF(K74="","",K74),""))))</f>
-        <v/>
-      </c>
-      <c r="H74" s="34" t="n"/>
-      <c r="I74" s="29" t="n"/>
-      <c r="J74" s="34" t="n"/>
+      <c r="H74" s="33">
+        <f>IF(G74="Validated actual",IF(I74="","",I74),IF(G74="Calculated",IF(J74="","",J74),IF(G74="Reference value",IF(K74="","",K74),IF(G74="Judgment",IF(L74="","",L74),""))))</f>
+        <v/>
+      </c>
+      <c r="I74" s="34" t="n"/>
+      <c r="J74" s="29" t="n"/>
       <c r="K74" s="34" t="n"/>
       <c r="L74" s="34" t="n"/>
-      <c r="M74" s="34" t="n"/>
-      <c r="N74" s="26" t="inlineStr"/>
-      <c r="O74" s="12" t="inlineStr">
+      <c r="M74" s="32">
+        <f>IF(OR(L74="",H74="",G74="Judgment"),"",IFERROR(L74/H74-1,""))</f>
+        <v/>
+      </c>
+      <c r="N74" s="34" t="n"/>
+      <c r="O74" s="34" t="n"/>
+      <c r="P74" s="26" t="inlineStr"/>
+      <c r="Q74" s="12" t="inlineStr">
         <is>
           <t>Sales Operations</t>
         </is>
       </c>
-      <c r="P74" s="12" t="inlineStr">
+      <c r="R74" s="12" t="inlineStr">
         <is>
           <t>CRM month-end snapshots</t>
         </is>
       </c>
-      <c r="Q74" s="12" t="inlineStr"/>
-      <c r="R74" s="32">
-        <f>IF(OR(K74="",G74="",F74="Judgment"),"",IFERROR(K74/G74-1,""))</f>
-        <v/>
-      </c>
-      <c r="S74" s="11" t="n"/>
-    </row>
-    <row r="75" ht="17.5" customHeight="1">
+      <c r="S74" s="12" t="inlineStr"/>
+      <c r="T74" s="11" t="n"/>
+    </row>
+    <row r="75" ht="31" customHeight="1">
       <c r="A75" s="11" t="n">
         <v>7</v>
       </c>
@@ -5409,54 +5529,55 @@
           <t>Open qualified opportunities ÷ salespeople</t>
         </is>
       </c>
-      <c r="E75" s="12" t="inlineStr">
+      <c r="E75" s="12" t="inlineStr"/>
+      <c r="F75" s="12" t="inlineStr">
         <is>
           <t>count1</t>
         </is>
       </c>
-      <c r="F75" s="26" t="inlineStr">
+      <c r="G75" s="26" t="inlineStr">
         <is>
           <t>Calculated</t>
         </is>
       </c>
-      <c r="G75" s="40">
-        <f>IF(F75="Validated actual",IF(H75="","",H75),IF(F75="Calculated",IF(I75="","",I75),IF(F75="Reference value",IF(J75="","",J75),IF(F75="Judgment",IF(K75="","",K75),""))))</f>
-        <v/>
-      </c>
-      <c r="H75" s="41" t="n"/>
-      <c r="I75" s="42">
+      <c r="H75" s="40">
+        <f>IF(G75="Validated actual",IF(I75="","",I75),IF(G75="Calculated",IF(J75="","",J75),IF(G75="Reference value",IF(K75="","",K75),IF(G75="Judgment",IF(L75="","",L75),""))))</f>
+        <v/>
+      </c>
+      <c r="I75" s="41" t="n"/>
+      <c r="J75" s="42">
         <f>IFERROR(v_open_opps_total/v_filled_seats,"")</f>
         <v/>
       </c>
-      <c r="J75" s="41" t="n"/>
       <c r="K75" s="41" t="n"/>
       <c r="L75" s="41" t="n"/>
-      <c r="M75" s="41" t="n"/>
-      <c r="N75" s="26" t="inlineStr"/>
-      <c r="O75" s="12" t="inlineStr">
+      <c r="M75" s="32">
+        <f>IF(OR(L75="",H75="",G75="Judgment"),"",IFERROR(L75/H75-1,""))</f>
+        <v/>
+      </c>
+      <c r="N75" s="41" t="n"/>
+      <c r="O75" s="41" t="n"/>
+      <c r="P75" s="26" t="inlineStr"/>
+      <c r="Q75" s="12" t="inlineStr">
         <is>
           <t>Sales Operations</t>
         </is>
       </c>
-      <c r="P75" s="12" t="inlineStr">
+      <c r="R75" s="12" t="inlineStr">
         <is>
           <t>Calculated from CRM snapshots and roster</t>
         </is>
       </c>
-      <c r="Q75" s="12" t="inlineStr">
+      <c r="S75" s="12" t="inlineStr">
         <is>
           <t>Little's Law check fails</t>
         </is>
       </c>
-      <c r="R75" s="32">
-        <f>IF(OR(K75="",G75="",F75="Judgment"),"",IFERROR(K75/G75-1,""))</f>
-        <v/>
-      </c>
-      <c r="S75" s="11" t="n">
+      <c r="T75" s="11" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="76" ht="44.5" customHeight="1">
+    <row r="76" ht="139" customHeight="1">
       <c r="A76" s="11" t="n">
         <v>7</v>
       </c>
@@ -5477,51 +5598,56 @@
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
+          <t>One driver of sales force inefficiency is the amount of NON-selling time spent by sales people. Some companies estimate as much at 50% of their time is invested in "non-selling" activities. Our studies reveal that a larger portion of that time in spend in activitity that isn't value-added to customers. The best way to financially measure that impact is by monitoring the number of accounts any given sales person can effectively manage at the same time. The greater amount of time you allow your sales people to sell - the more opportunities they can work in a given year.</t>
+        </is>
+      </c>
+      <c r="F76" s="12" t="inlineStr">
+        <is>
           <t>count</t>
         </is>
       </c>
-      <c r="F76" s="26" t="inlineStr">
+      <c r="G76" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G76" s="33">
-        <f>IF(F76="Validated actual",IF(H76="","",H76),IF(F76="Calculated",IF(I76="","",I76),IF(F76="Reference value",IF(J76="","",J76),IF(F76="Judgment",IF(K76="","",K76),""))))</f>
-        <v/>
-      </c>
-      <c r="H76" s="34" t="n"/>
-      <c r="I76" s="29" t="n"/>
-      <c r="J76" s="34" t="n">
+      <c r="H76" s="33">
+        <f>IF(G76="Validated actual",IF(I76="","",I76),IF(G76="Calculated",IF(J76="","",J76),IF(G76="Reference value",IF(K76="","",K76),IF(G76="Judgment",IF(L76="","",L76),""))))</f>
+        <v/>
+      </c>
+      <c r="I76" s="34" t="n"/>
+      <c r="J76" s="29" t="n"/>
+      <c r="K76" s="34" t="n">
         <v>30</v>
       </c>
-      <c r="K76" s="34" t="n"/>
       <c r="L76" s="34" t="n"/>
-      <c r="M76" s="34" t="n"/>
-      <c r="N76" s="26" t="inlineStr">
+      <c r="M76" s="32">
+        <f>IF(OR(L76="",H76="",G76="Judgment"),"",IFERROR(L76/H76-1,""))</f>
+        <v/>
+      </c>
+      <c r="N76" s="34" t="n"/>
+      <c r="O76" s="34" t="n"/>
+      <c r="P76" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O76" s="12" t="inlineStr">
+      <c r="Q76" s="12" t="inlineStr">
         <is>
           <t>Sales Operations</t>
         </is>
       </c>
-      <c r="P76" s="12" t="inlineStr">
+      <c r="R76" s="12" t="inlineStr">
         <is>
           <t>Sales leader judgment</t>
         </is>
       </c>
-      <c r="Q76" s="12" t="inlineStr">
+      <c r="S76" s="12" t="inlineStr">
         <is>
           <t>Win rate and cycle hold steady at loads above this level</t>
         </is>
       </c>
-      <c r="R76" s="32">
-        <f>IF(OR(K76="",G76="",F76="Judgment"),"",IFERROR(K76/G76-1,""))</f>
-        <v/>
-      </c>
-      <c r="S76" s="11" t="n">
+      <c r="T76" s="11" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5549,8 +5675,9 @@
       <c r="Q77" s="21" t="n"/>
       <c r="R77" s="21" t="n"/>
       <c r="S77" s="21" t="n"/>
-    </row>
-    <row r="78" ht="31" customHeight="1">
+      <c r="T77" s="21" t="n"/>
+    </row>
+    <row r="78" ht="71.5" customHeight="1">
       <c r="A78" s="11" t="n">
         <v>8</v>
       </c>
@@ -5571,54 +5698,59 @@
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
+          <t>Commissions are the most logical and well understood driver of variable sales costs. Simply enter your sales forces average commission. Again, for simple analysis - just use an average. This model can be modified to accommodate your whole compensation plan.</t>
+        </is>
+      </c>
+      <c r="F78" s="12" t="inlineStr">
+        <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="F78" s="26" t="inlineStr">
+      <c r="G78" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G78" s="36">
-        <f>IF(F78="Validated actual",IF(H78="","",H78),IF(F78="Calculated",IF(I78="","",I78),IF(F78="Reference value",IF(J78="","",J78),IF(F78="Judgment",IF(K78="","",K78),""))))</f>
-        <v/>
-      </c>
-      <c r="H78" s="37" t="n"/>
-      <c r="I78" s="38">
+      <c r="H78" s="36">
+        <f>IF(G78="Validated actual",IF(I78="","",I78),IF(G78="Calculated",IF(J78="","",J78),IF(G78="Reference value",IF(K78="","",K78),IF(G78="Judgment",IF(L78="","",L78),""))))</f>
+        <v/>
+      </c>
+      <c r="I78" s="37" t="n"/>
+      <c r="J78" s="38">
         <f>IFERROR(v_commissions_paid/v_revenue,"")</f>
         <v/>
       </c>
-      <c r="J78" s="37" t="n">
+      <c r="K78" s="37" t="n">
         <v>0.08</v>
       </c>
-      <c r="K78" s="37" t="n"/>
       <c r="L78" s="37" t="n"/>
-      <c r="M78" s="37" t="n"/>
-      <c r="N78" s="26" t="inlineStr">
+      <c r="M78" s="32">
+        <f>IF(OR(L78="",H78="",G78="Judgment"),"",IFERROR(L78/H78-1,""))</f>
+        <v/>
+      </c>
+      <c r="N78" s="37" t="n"/>
+      <c r="O78" s="37" t="n"/>
+      <c r="P78" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O78" s="12" t="inlineStr">
+      <c r="Q78" s="12" t="inlineStr">
         <is>
           <t>Compensation</t>
         </is>
       </c>
-      <c r="P78" s="12" t="inlineStr">
+      <c r="R78" s="12" t="inlineStr">
         <is>
           <t>Compensation plan</t>
         </is>
       </c>
-      <c r="Q78" s="12" t="inlineStr">
+      <c r="S78" s="12" t="inlineStr">
         <is>
           <t>Commissions paid ÷ revenue differs from the plan rate</t>
         </is>
       </c>
-      <c r="R78" s="32">
-        <f>IF(OR(K78="",G78="",F78="Judgment"),"",IFERROR(K78/G78-1,""))</f>
-        <v/>
-      </c>
-      <c r="S78" s="11" t="n">
+      <c r="T78" s="11" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5646,8 +5778,9 @@
       <c r="Q79" s="21" t="n"/>
       <c r="R79" s="21" t="n"/>
       <c r="S79" s="21" t="n"/>
-    </row>
-    <row r="80" ht="31" customHeight="1">
+      <c r="T79" s="21" t="n"/>
+    </row>
+    <row r="80" ht="98.5" customHeight="1">
       <c r="A80" s="11" t="n">
         <v>9</v>
       </c>
@@ -5668,51 +5801,56 @@
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
+          <t>How long does it take to get a new sales person up to speed to where they are operating at maximum efficiency? Most high tech companies do a good job of training sales people on what their products are, but do very little to help them understand WHY the product is important or how to sell it. This leads to lengthy "ramp up" times. We recommend getting this figure from a sales manager.</t>
+        </is>
+      </c>
+      <c r="F80" s="12" t="inlineStr">
+        <is>
           <t>months</t>
         </is>
       </c>
-      <c r="F80" s="26" t="inlineStr">
+      <c r="G80" s="26" t="inlineStr">
         <is>
           <t>Reference value</t>
         </is>
       </c>
-      <c r="G80" s="43">
-        <f>IF(F80="Validated actual",IF(H80="","",H80),IF(F80="Calculated",IF(I80="","",I80),IF(F80="Reference value",IF(J80="","",J80),IF(F80="Judgment",IF(K80="","",K80),""))))</f>
-        <v/>
-      </c>
-      <c r="H80" s="44" t="n"/>
-      <c r="I80" s="29" t="n"/>
-      <c r="J80" s="44" t="n">
+      <c r="H80" s="43">
+        <f>IF(G80="Validated actual",IF(I80="","",I80),IF(G80="Calculated",IF(J80="","",J80),IF(G80="Reference value",IF(K80="","",K80),IF(G80="Judgment",IF(L80="","",L80),""))))</f>
+        <v/>
+      </c>
+      <c r="I80" s="44" t="n"/>
+      <c r="J80" s="29" t="n"/>
+      <c r="K80" s="44" t="n">
         <v>12</v>
       </c>
-      <c r="K80" s="44" t="n"/>
       <c r="L80" s="44" t="n"/>
-      <c r="M80" s="44" t="n"/>
-      <c r="N80" s="26" t="inlineStr">
+      <c r="M80" s="32">
+        <f>IF(OR(L80="",H80="",G80="Judgment"),"",IFERROR(L80/H80-1,""))</f>
+        <v/>
+      </c>
+      <c r="N80" s="44" t="n"/>
+      <c r="O80" s="44" t="n"/>
+      <c r="P80" s="26" t="inlineStr">
         <is>
           <t>As-is model sample (illustrative)</t>
         </is>
       </c>
-      <c r="O80" s="12" t="inlineStr">
+      <c r="Q80" s="12" t="inlineStr">
         <is>
           <t>HR and Finance</t>
         </is>
       </c>
-      <c r="P80" s="12" t="inlineStr">
+      <c r="R80" s="12" t="inlineStr">
         <is>
           <t>Sales manager, or productivity by tenure</t>
         </is>
       </c>
-      <c r="Q80" s="12" t="inlineStr">
+      <c r="S80" s="12" t="inlineStr">
         <is>
           <t>New-hire productivity by month differs</t>
         </is>
       </c>
-      <c r="R80" s="32">
-        <f>IF(OR(K80="",G80="",F80="Judgment"),"",IFERROR(K80/G80-1,""))</f>
-        <v/>
-      </c>
-      <c r="S80" s="11" t="n">
+      <c r="T80" s="11" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5735,47 +5873,48 @@
           <t>From vacancy to the new salesperson's start date</t>
         </is>
       </c>
-      <c r="E81" s="12" t="inlineStr">
+      <c r="E81" s="12" t="inlineStr"/>
+      <c r="F81" s="12" t="inlineStr">
         <is>
           <t>days</t>
         </is>
       </c>
-      <c r="F81" s="26" t="inlineStr">
+      <c r="G81" s="26" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="G81" s="33">
-        <f>IF(F81="Validated actual",IF(H81="","",H81),IF(F81="Calculated",IF(I81="","",I81),IF(F81="Reference value",IF(J81="","",J81),IF(F81="Judgment",IF(K81="","",K81),""))))</f>
-        <v/>
-      </c>
-      <c r="H81" s="34" t="n"/>
-      <c r="I81" s="29" t="n"/>
-      <c r="J81" s="34" t="n"/>
+      <c r="H81" s="33">
+        <f>IF(G81="Validated actual",IF(I81="","",I81),IF(G81="Calculated",IF(J81="","",J81),IF(G81="Reference value",IF(K81="","",K81),IF(G81="Judgment",IF(L81="","",L81),""))))</f>
+        <v/>
+      </c>
+      <c r="I81" s="34" t="n"/>
+      <c r="J81" s="29" t="n"/>
       <c r="K81" s="34" t="n"/>
       <c r="L81" s="34" t="n"/>
-      <c r="M81" s="34" t="n"/>
-      <c r="N81" s="26" t="inlineStr"/>
-      <c r="O81" s="12" t="inlineStr">
+      <c r="M81" s="32">
+        <f>IF(OR(L81="",H81="",G81="Judgment"),"",IFERROR(L81/H81-1,""))</f>
+        <v/>
+      </c>
+      <c r="N81" s="34" t="n"/>
+      <c r="O81" s="34" t="n"/>
+      <c r="P81" s="26" t="inlineStr"/>
+      <c r="Q81" s="12" t="inlineStr">
         <is>
           <t>HR and Finance</t>
         </is>
       </c>
-      <c r="P81" s="12" t="inlineStr">
+      <c r="R81" s="12" t="inlineStr">
         <is>
           <t>HR requisition records</t>
         </is>
       </c>
-      <c r="Q81" s="12" t="inlineStr">
+      <c r="S81" s="12" t="inlineStr">
         <is>
           <t>Vacancy records differ</t>
         </is>
       </c>
-      <c r="R81" s="32">
-        <f>IF(OR(K81="",G81="",F81="Judgment"),"",IFERROR(K81/G81-1,""))</f>
-        <v/>
-      </c>
-      <c r="S81" s="11" t="n">
+      <c r="T81" s="11" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5798,47 +5937,48 @@
           <t>From vacancy to approved requisition</t>
         </is>
       </c>
-      <c r="E82" s="12" t="inlineStr">
+      <c r="E82" s="12" t="inlineStr"/>
+      <c r="F82" s="12" t="inlineStr">
         <is>
           <t>days</t>
         </is>
       </c>
-      <c r="F82" s="26" t="inlineStr">
+      <c r="G82" s="26" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="G82" s="33">
-        <f>IF(F82="Validated actual",IF(H82="","",H82),IF(F82="Calculated",IF(I82="","",I82),IF(F82="Reference value",IF(J82="","",J82),IF(F82="Judgment",IF(K82="","",K82),""))))</f>
-        <v/>
-      </c>
-      <c r="H82" s="34" t="n"/>
-      <c r="I82" s="29" t="n"/>
-      <c r="J82" s="34" t="n"/>
+      <c r="H82" s="33">
+        <f>IF(G82="Validated actual",IF(I82="","",I82),IF(G82="Calculated",IF(J82="","",J82),IF(G82="Reference value",IF(K82="","",K82),IF(G82="Judgment",IF(L82="","",L82),""))))</f>
+        <v/>
+      </c>
+      <c r="I82" s="34" t="n"/>
+      <c r="J82" s="29" t="n"/>
       <c r="K82" s="34" t="n"/>
       <c r="L82" s="34" t="n"/>
-      <c r="M82" s="34" t="n"/>
-      <c r="N82" s="26" t="inlineStr"/>
-      <c r="O82" s="12" t="inlineStr">
+      <c r="M82" s="32">
+        <f>IF(OR(L82="",H82="",G82="Judgment"),"",IFERROR(L82/H82-1,""))</f>
+        <v/>
+      </c>
+      <c r="N82" s="34" t="n"/>
+      <c r="O82" s="34" t="n"/>
+      <c r="P82" s="26" t="inlineStr"/>
+      <c r="Q82" s="12" t="inlineStr">
         <is>
           <t>HR and Finance</t>
         </is>
       </c>
-      <c r="P82" s="12" t="inlineStr">
+      <c r="R82" s="12" t="inlineStr">
         <is>
           <t>HR and Finance approval records</t>
         </is>
       </c>
-      <c r="Q82" s="12" t="inlineStr">
+      <c r="S82" s="12" t="inlineStr">
         <is>
           <t>Approval records differ</t>
         </is>
       </c>
-      <c r="R82" s="32">
-        <f>IF(OR(K82="",G82="",F82="Judgment"),"",IFERROR(K82/G82-1,""))</f>
-        <v/>
-      </c>
-      <c r="S82" s="11" t="n">
+      <c r="T82" s="11" t="n">
         <v>9</v>
       </c>
     </row>
@@ -5866,8 +6006,9 @@
       <c r="Q83" s="21" t="n"/>
       <c r="R83" s="21" t="n"/>
       <c r="S83" s="21" t="n"/>
-    </row>
-    <row r="84" ht="31" customHeight="1">
+      <c r="T83" s="21" t="n"/>
+    </row>
+    <row r="84" ht="17.5" customHeight="1">
       <c r="A84" s="11" t="n">
         <v>10</v>
       </c>
@@ -5886,44 +6027,45 @@
           <t>The rule the CRM stage uses</t>
         </is>
       </c>
-      <c r="E84" s="12" t="inlineStr">
+      <c r="E84" s="12" t="inlineStr"/>
+      <c r="F84" s="12" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="F84" s="26" t="inlineStr">
+      <c r="G84" s="26" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="G84" s="27">
-        <f>IF(F84="Validated actual",IF(H84="","",H84),IF(F84="Calculated",IF(I84="","",I84),IF(F84="Reference value",IF(J84="","",J84),IF(F84="Judgment",IF(K84="","",K84),""))))</f>
-        <v/>
-      </c>
-      <c r="H84" s="28" t="n"/>
-      <c r="I84" s="29" t="n"/>
-      <c r="J84" s="28" t="n"/>
+      <c r="H84" s="27">
+        <f>IF(G84="Validated actual",IF(I84="","",I84),IF(G84="Calculated",IF(J84="","",J84),IF(G84="Reference value",IF(K84="","",K84),IF(G84="Judgment",IF(L84="","",L84),""))))</f>
+        <v/>
+      </c>
+      <c r="I84" s="28" t="n"/>
+      <c r="J84" s="29" t="n"/>
       <c r="K84" s="28" t="n"/>
       <c r="L84" s="28" t="n"/>
-      <c r="M84" s="28" t="n"/>
-      <c r="N84" s="26" t="inlineStr"/>
-      <c r="O84" s="12" t="inlineStr">
+      <c r="M84" s="12" t="n"/>
+      <c r="N84" s="28" t="n"/>
+      <c r="O84" s="28" t="n"/>
+      <c r="P84" s="26" t="inlineStr"/>
+      <c r="Q84" s="12" t="inlineStr">
         <is>
           <t>Sales Operations and Finance</t>
         </is>
       </c>
-      <c r="P84" s="12" t="inlineStr">
+      <c r="R84" s="12" t="inlineStr">
         <is>
           <t>Sales Operations</t>
         </is>
       </c>
-      <c r="Q84" s="12" t="inlineStr">
+      <c r="S84" s="12" t="inlineStr">
         <is>
           <t>Qualified opportunities do not meet the stated rule</t>
         </is>
       </c>
-      <c r="R84" s="12" t="n"/>
-      <c r="S84" s="11" t="n">
+      <c r="T84" s="11" t="n">
         <v>5</v>
       </c>
     </row>
@@ -5946,44 +6088,45 @@
           <t>Who approves a requisition, in what order</t>
         </is>
       </c>
-      <c r="E85" s="12" t="inlineStr">
+      <c r="E85" s="12" t="inlineStr"/>
+      <c r="F85" s="12" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="F85" s="26" t="inlineStr">
+      <c r="G85" s="26" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="G85" s="27">
-        <f>IF(F85="Validated actual",IF(H85="","",H85),IF(F85="Calculated",IF(I85="","",I85),IF(F85="Reference value",IF(J85="","",J85),IF(F85="Judgment",IF(K85="","",K85),""))))</f>
-        <v/>
-      </c>
-      <c r="H85" s="28" t="n"/>
-      <c r="I85" s="29" t="n"/>
-      <c r="J85" s="28" t="n"/>
+      <c r="H85" s="27">
+        <f>IF(G85="Validated actual",IF(I85="","",I85),IF(G85="Calculated",IF(J85="","",J85),IF(G85="Reference value",IF(K85="","",K85),IF(G85="Judgment",IF(L85="","",L85),""))))</f>
+        <v/>
+      </c>
+      <c r="I85" s="28" t="n"/>
+      <c r="J85" s="29" t="n"/>
       <c r="K85" s="28" t="n"/>
       <c r="L85" s="28" t="n"/>
-      <c r="M85" s="28" t="n"/>
-      <c r="N85" s="26" t="inlineStr"/>
-      <c r="O85" s="12" t="inlineStr">
+      <c r="M85" s="12" t="n"/>
+      <c r="N85" s="28" t="n"/>
+      <c r="O85" s="28" t="n"/>
+      <c r="P85" s="26" t="inlineStr"/>
+      <c r="Q85" s="12" t="inlineStr">
         <is>
           <t>Sales Operations and Finance</t>
         </is>
       </c>
-      <c r="P85" s="12" t="inlineStr">
+      <c r="R85" s="12" t="inlineStr">
         <is>
           <t>HR and Finance</t>
         </is>
       </c>
-      <c r="Q85" s="12" t="inlineStr">
+      <c r="S85" s="12" t="inlineStr">
         <is>
           <t>Approval records follow a different path</t>
         </is>
       </c>
-      <c r="R85" s="12" t="n"/>
-      <c r="S85" s="11" t="n">
+      <c r="T85" s="11" t="n">
         <v>5</v>
       </c>
     </row>
@@ -6006,44 +6149,45 @@
           <t>Who decides territories, coverage and roles</t>
         </is>
       </c>
-      <c r="E86" s="12" t="inlineStr">
+      <c r="E86" s="12" t="inlineStr"/>
+      <c r="F86" s="12" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="F86" s="26" t="inlineStr">
+      <c r="G86" s="26" t="inlineStr">
         <is>
           <t>Validated actual</t>
         </is>
       </c>
-      <c r="G86" s="27">
-        <f>IF(F86="Validated actual",IF(H86="","",H86),IF(F86="Calculated",IF(I86="","",I86),IF(F86="Reference value",IF(J86="","",J86),IF(F86="Judgment",IF(K86="","",K86),""))))</f>
-        <v/>
-      </c>
-      <c r="H86" s="28" t="n"/>
-      <c r="I86" s="29" t="n"/>
-      <c r="J86" s="28" t="n"/>
+      <c r="H86" s="27">
+        <f>IF(G86="Validated actual",IF(I86="","",I86),IF(G86="Calculated",IF(J86="","",J86),IF(G86="Reference value",IF(K86="","",K86),IF(G86="Judgment",IF(L86="","",L86),""))))</f>
+        <v/>
+      </c>
+      <c r="I86" s="28" t="n"/>
+      <c r="J86" s="29" t="n"/>
       <c r="K86" s="28" t="n"/>
       <c r="L86" s="28" t="n"/>
-      <c r="M86" s="28" t="n"/>
-      <c r="N86" s="26" t="inlineStr"/>
-      <c r="O86" s="12" t="inlineStr">
+      <c r="M86" s="12" t="n"/>
+      <c r="N86" s="28" t="n"/>
+      <c r="O86" s="28" t="n"/>
+      <c r="P86" s="26" t="inlineStr"/>
+      <c r="Q86" s="12" t="inlineStr">
         <is>
           <t>Sales Operations and Finance</t>
         </is>
       </c>
-      <c r="P86" s="12" t="inlineStr">
+      <c r="R86" s="12" t="inlineStr">
         <is>
           <t>Sponsor</t>
         </is>
       </c>
-      <c r="Q86" s="12" t="inlineStr">
+      <c r="S86" s="12" t="inlineStr">
         <is>
           <t>Changes were made by someone else</t>
         </is>
       </c>
-      <c r="R86" s="12" t="n"/>
-      <c r="S86" s="11" t="n">
+      <c r="T86" s="11" t="n">
         <v>4</v>
       </c>
     </row>
@@ -6071,6 +6215,7 @@
       <c r="Q88" s="21" t="n"/>
       <c r="R88" s="21" t="n"/>
       <c r="S88" s="21" t="n"/>
+      <c r="T88" s="21" t="n"/>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="B89" s="19" t="inlineStr">
@@ -6088,6 +6233,11 @@
           <t>What it compares</t>
         </is>
       </c>
+      <c r="E89" s="19" t="inlineStr">
+        <is>
+          <t>Entries that could be wrong</t>
+        </is>
+      </c>
       <c r="F89" s="19" t="inlineStr">
         <is>
           <t>Tolerance</t>
@@ -6115,26 +6265,21 @@
       </c>
       <c r="K89" s="19" t="inlineStr">
         <is>
-          <t>Entries that could be wrong</t>
+          <t>Resolution</t>
         </is>
       </c>
       <c r="L89" s="19" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="M89" s="19" t="inlineStr">
         <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="N89" s="19" t="inlineStr">
-        <is>
           <t>Note</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="17.5" customHeight="1">
+    <row r="90" ht="31" customHeight="1">
       <c r="B90" s="12" t="inlineStr">
         <is>
           <t>deal_size_triangulation</t>
@@ -6148,6 +6293,11 @@
       <c r="D90" s="12" t="inlineStr">
         <is>
           <t>Revenue ÷ contracts vs the deal size used</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="inlineStr">
+        <is>
+          <t>Revenue, contracts, deal size</t>
         </is>
       </c>
       <c r="F90" s="45" t="n">
@@ -6169,14 +6319,9 @@
         <f>IF(OR(H90="",I90=""),"",IFERROR(I90/H90-1,""))</f>
         <v/>
       </c>
-      <c r="K90" s="12" t="inlineStr">
-        <is>
-          <t>Revenue, contracts, deal size</t>
-        </is>
-      </c>
+      <c r="K90" s="15" t="n"/>
       <c r="L90" s="15" t="n"/>
       <c r="M90" s="15" t="n"/>
-      <c r="N90" s="15" t="n"/>
     </row>
     <row r="91" ht="31" customHeight="1">
       <c r="B91" s="12" t="inlineStr">
@@ -6194,6 +6339,11 @@
           <t>Territories × capacity × 12 ÷ cycle × close rate vs contracts</t>
         </is>
       </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>Territories, capacity, cycle, close rate</t>
+        </is>
+      </c>
       <c r="F91" s="45" t="n">
         <v>0.1</v>
       </c>
@@ -6213,14 +6363,9 @@
         <f>IF(OR(H91="",I91=""),"",IFERROR(I91/H91-1,""))</f>
         <v/>
       </c>
-      <c r="K91" s="12" t="inlineStr">
-        <is>
-          <t>Territories, capacity, cycle, close rate</t>
-        </is>
-      </c>
+      <c r="K91" s="15" t="n"/>
       <c r="L91" s="15" t="n"/>
       <c r="M91" s="15" t="n"/>
-      <c r="N91" s="15" t="n"/>
     </row>
     <row r="92" ht="31" customHeight="1">
       <c r="B92" s="12" t="inlineStr">
@@ -6238,6 +6383,11 @@
           <t>Implied contracts × deal size vs revenue</t>
         </is>
       </c>
+      <c r="E92" s="12" t="inlineStr">
+        <is>
+          <t>Territories, capacity, cycle, close rate, deal size</t>
+        </is>
+      </c>
       <c r="F92" s="45" t="n">
         <v>0.1</v>
       </c>
@@ -6257,14 +6407,9 @@
         <f>IF(OR(H92="",I92=""),"",IFERROR(I92/H92-1,""))</f>
         <v/>
       </c>
-      <c r="K92" s="12" t="inlineStr">
-        <is>
-          <t>Territories, capacity, cycle, close rate, deal size</t>
-        </is>
-      </c>
+      <c r="K92" s="15" t="n"/>
       <c r="L92" s="15" t="n"/>
       <c r="M92" s="15" t="n"/>
-      <c r="N92" s="15" t="n"/>
     </row>
     <row r="93" ht="44.5" customHeight="1">
       <c r="B93" s="12" t="inlineStr">
@@ -6282,6 +6427,11 @@
           <t>Contracts ÷ close rate ÷ productive salespeople × cycle ÷ 12 vs opportunities held</t>
         </is>
       </c>
+      <c r="E93" s="12" t="inlineStr">
+        <is>
+          <t>Contracts, close rate, productive salespeople, cycle, opportunities held</t>
+        </is>
+      </c>
       <c r="F93" s="45" t="n">
         <v>0.25</v>
       </c>
@@ -6301,14 +6451,9 @@
         <f>IF(OR(H93="",I93=""),"",IFERROR(I93/H93-1,""))</f>
         <v/>
       </c>
-      <c r="K93" s="12" t="inlineStr">
-        <is>
-          <t>Contracts, close rate, productive salespeople, cycle, opportunities held</t>
-        </is>
-      </c>
+      <c r="K93" s="15" t="n"/>
       <c r="L93" s="15" t="n"/>
       <c r="M93" s="15" t="n"/>
-      <c r="N93" s="15" t="n"/>
     </row>
     <row r="94" ht="31" customHeight="1">
       <c r="B94" s="12" t="inlineStr">
@@ -6326,6 +6471,11 @@
           <t>Filled seats + open territories vs funded territories</t>
         </is>
       </c>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t>Filled seats, open territories, funded territories</t>
+        </is>
+      </c>
       <c r="F94" s="45" t="n">
         <v>0</v>
       </c>
@@ -6345,14 +6495,9 @@
         <f>IF(OR(H94="",I94=""),"",IFERROR(I94/H94-1,""))</f>
         <v/>
       </c>
-      <c r="K94" s="12" t="inlineStr">
-        <is>
-          <t>Filled seats, open territories, funded territories</t>
-        </is>
-      </c>
+      <c r="K94" s="15" t="n"/>
       <c r="L94" s="15" t="n"/>
       <c r="M94" s="15" t="n"/>
-      <c r="N94" s="15" t="n"/>
     </row>
     <row r="95" ht="31" customHeight="1">
       <c r="B95" s="12" t="inlineStr">
@@ -6370,6 +6515,11 @@
           <t>Territories × expected yield vs revenue plan</t>
         </is>
       </c>
+      <c r="E95" s="12" t="inlineStr">
+        <is>
+          <t>Territories, expected yield, plan</t>
+        </is>
+      </c>
       <c r="F95" s="45" t="n">
         <v>0.05</v>
       </c>
@@ -6389,14 +6539,9 @@
         <f>IF(OR(H95="",I95=""),"",IFERROR(I95/H95-1,""))</f>
         <v/>
       </c>
-      <c r="K95" s="12" t="inlineStr">
-        <is>
-          <t>Territories, expected yield, plan</t>
-        </is>
-      </c>
+      <c r="K95" s="15" t="n"/>
       <c r="L95" s="15" t="n"/>
       <c r="M95" s="15" t="n"/>
-      <c r="N95" s="15" t="n"/>
     </row>
     <row r="96" ht="31" customHeight="1">
       <c r="B96" s="12" t="inlineStr">
@@ -6414,6 +6559,11 @@
           <t>Salespeople × loaded salary + commission × revenue vs ledger compensation</t>
         </is>
       </c>
+      <c r="E96" s="12" t="inlineStr">
+        <is>
+          <t>Salespeople, loaded salary, commission rate, revenue</t>
+        </is>
+      </c>
       <c r="F96" s="45" t="n">
         <v>0.1</v>
       </c>
@@ -6433,14 +6583,9 @@
         <f>IF(OR(H96="",I96=""),"",IFERROR(I96/H96-1,""))</f>
         <v/>
       </c>
-      <c r="K96" s="12" t="inlineStr">
-        <is>
-          <t>Salespeople, loaded salary, commission rate, revenue</t>
-        </is>
-      </c>
+      <c r="K96" s="15" t="n"/>
       <c r="L96" s="15" t="n"/>
       <c r="M96" s="15" t="n"/>
-      <c r="N96" s="15" t="n"/>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="B97" s="12" t="inlineStr">
@@ -6458,6 +6603,11 @@
           <t>Opportunities held ÷ opportunities a salesperson can manage; cannot exceed 100%</t>
         </is>
       </c>
+      <c r="E97" s="12" t="inlineStr">
+        <is>
+          <t>Opportunities held, capacity</t>
+        </is>
+      </c>
       <c r="F97" s="45" t="n">
         <v>1</v>
       </c>
@@ -6471,14 +6621,9 @@
       </c>
       <c r="I97" s="51" t="n"/>
       <c r="J97" s="51" t="n"/>
-      <c r="K97" s="12" t="inlineStr">
-        <is>
-          <t>Opportunities held, capacity</t>
-        </is>
-      </c>
+      <c r="K97" s="15" t="n"/>
       <c r="L97" s="15" t="n"/>
       <c r="M97" s="15" t="n"/>
-      <c r="N97" s="15" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6500,16 +6645,16 @@
     <dataValidation sqref="D4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Draft,Working model,In Finance review,Signed by Finance"</formula1>
     </dataValidation>
-    <dataValidation sqref="F17 F18 F19 F21 F22 F23 F24 F25 F26 F27 F28 F29 F31 F32 F33 F34 F35 F36 F37 F38 F39 F40 F41 F42 F43 F44 F45 F46 F47 F48 F49 F50 F51 F52 F53 F54 F55 F56 F57 F58 F60 F61 F62 F63 F65 F66 F67 F69 F70 F71 F72 F73 F74 F75 F76 F78 F80 F81 F82 F84 F85 F86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G17 G18 G19 G21 G22 G23 G24 G25 G26 G27 G28 G29 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56 G57 G58 G60 G61 G62 G63 G65 G66 G67 G69 G70 G71 G72 G73 G74 G75 G76 G78 G80 G81 G82 G84 G85 G86" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Validated actual,Calculated,Reference value,Judgment"</formula1>
     </dataValidation>
-    <dataValidation sqref="G15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="H15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Recognized revenue,Bookings"</formula1>
     </dataValidation>
-    <dataValidation sqref="L90 L91 L92 L93 L94 L95 L96 L97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K90 K91 K92 K93 K94 K95 K96 K97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Fixed,Explained,Accepted as known gap"</formula1>
     </dataValidation>
-    <dataValidation sqref="M90 M91 M92 M93 M94 M95 M96 M97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L90 L91 L92 L93 L94 L95 L96 L97" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Definition,Timing,Scope,Data quality,Reference value,Other"</formula1>
     </dataValidation>
   </dataValidations>

--- a/workbook/Commercial_Effectiveness_Model.xlsx
+++ b/workbook/Commercial_Effectiveness_Model.xlsx
@@ -9,8 +9,10 @@
   <sheets>
     <sheet name="Orientation" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="1) Data Entry" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2) What-If Scenarios" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="v_baseline_banner">'1) Data Entry'!$F$4</definedName>
     <definedName name="v_scope_business">'1) Data Entry'!$H$11</definedName>
     <definedName name="v_period_start">'1) Data Entry'!$H$12</definedName>
     <definedName name="v_period_end">'1) Data Entry'!$H$13</definedName>
@@ -78,6 +80,8 @@
     <definedName name="v_qualification_definition">'1) Data Entry'!$H$84</definedName>
     <definedName name="v_hiring_approval_rule">'1) Data Entry'!$H$85</definedName>
     <definedName name="v_design_authority">'1) Data Entry'!$H$86</definedName>
+    <definedName name="wi_view">'2) What-If Scenarios'!$B$4</definedName>
+    <definedName name="wi_compare">'2) What-If Scenarios'!$B$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'1) Data Entry'!$9:$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -86,13 +90,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="+0%;-0%;0%"/>
     <numFmt numFmtId="167" formatCode="0.0%"/>
     <numFmt numFmtId="168" formatCode="#,##0.0"/>
     <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="+0%;-0%;&quot;&quot;"/>
+    <numFmt numFmtId="171" formatCode="+0.0%;-0.0%;0.0%"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -228,7 +234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -355,6 +361,23 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="171" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -743,7 +766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:E65"/>
+  <dimension ref="B2:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -872,10 +895,10 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="31" customHeight="1">
+    <row r="23" ht="44.5" customHeight="1">
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>3.  Explore what-if scenarios (later tabs). Change assumptions one at a time or in combination: territory design, hiring and fill speed, salesperson capacity, win rate, cycle, deal size, costs. Every change flows through to operating income, with nothing unexplained.</t>
+          <t>3.  Explore what-if scenarios (2) What-If Scenarios). Each column is a scenario you can rename and change: territory design, filling open territories, fill speed, ramp, salesperson capacity, opportunities held, win rate, cycle, deal size, costs and the cost of the improvement itself. Every change flows through to operating income, and a true-up row confirms nothing is unexplained.</t>
         </is>
       </c>
     </row>
@@ -1282,33 +1305,40 @@
     <row r="61" ht="31" customHeight="1">
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>•  Later tabs (to be rebuilt): performance breakdown, impact on the income statement, scenario diagnostics. They read only the Value used cells on tab 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="17.5" customHeight="1">
-      <c r="B63" s="3" t="inlineStr">
+          <t>•  2) What-If Scenarios: baseline plus nine editable scenarios, from territory design and staffing through salesperson throughput to operating income, with a true-up and a break-even budget for each.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="17.5" customHeight="1">
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>•  Later tabs (to be rebuilt): detailed income statement and scenario diagnostics. Every tab reads only the Value used cells on tab 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="17.5" customHeight="1">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>A few points</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="31" customHeight="1">
-      <c r="B64" s="4" t="inlineStr">
+    <row r="65" ht="31" customHeight="1">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>This is a general model. For a sharper analysis, run it separately for each sales channel and product line, and separate new-customer revenue from revenue from existing customers. The model can be tailored to your business.</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="44.5" customHeight="1">
-      <c r="B65" s="4" t="inlineStr">
+    <row r="66" ht="44.5" customHeight="1">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>“Increase leads” is not listed as a business scenario because we consider lead generation to be a more leveraged way to conduct sales prospecting. The number of leads, how to acquire them, and how much you can invest to acquire those leads are all handled in the tactical “drill down” spreadsheets that accompany this model.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="40">
     <mergeCell ref="B65:E65"/>
     <mergeCell ref="B37:E37"/>
     <mergeCell ref="B6:E6"/>
@@ -1318,14 +1348,15 @@
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B63:E63"/>
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B35:E35"/>
     <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B62:E62"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B59:E59"/>
     <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B66:E66"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B43:E43"/>
@@ -6661,4 +6692,3015 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M76"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="3" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>2) What-If Scenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Each column is a scenario built on the tab 1 baseline. Rename it, describe the question, and enter changes in the yellow cells (blank means no change). Everything below is calculated from tab 1's Value used cells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16">
+        <f>v_baseline_banner</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Year one</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Compare break-even against</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Add territories +10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>How it works</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>Add territories +10%</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>Fill open territories</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>Close rate +10%</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>Cycle −10%</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>Deal size +10%</t>
+        </is>
+      </c>
+      <c r="J7" s="19" t="inlineStr">
+        <is>
+          <t>Opportunities held +10%</t>
+        </is>
+      </c>
+      <c r="K7" s="19" t="inlineStr">
+        <is>
+          <t>Close, cycle and deal size</t>
+        </is>
+      </c>
+      <c r="L7" s="19" t="inlineStr">
+        <is>
+          <t>All four with territories</t>
+        </is>
+      </c>
+      <c r="M7" s="19" t="inlineStr">
+        <is>
+          <t>Your scenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Question it answers</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Tab 1, as entered</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>What if we fund 10% more territories and hire into them?</t>
+        </is>
+      </c>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>What if we fill every open territory this year?</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t>What if we close 10% more of the opportunities we work?</t>
+        </is>
+      </c>
+      <c r="H8" s="26" t="inlineStr">
+        <is>
+          <t>What if deals take 10% less time?</t>
+        </is>
+      </c>
+      <c r="I8" s="26" t="inlineStr">
+        <is>
+          <t>What if each contract is worth 10% more?</t>
+        </is>
+      </c>
+      <c r="J8" s="26" t="inlineStr">
+        <is>
+          <t>What if 10% more qualified opportunities reach each salesperson?</t>
+        </is>
+      </c>
+      <c r="K8" s="26" t="inlineStr">
+        <is>
+          <t>What if all three quality levers improve 10%?</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="inlineStr">
+        <is>
+          <t>What if we add territories and improve all three quality levers?</t>
+        </is>
+      </c>
+      <c r="M8" s="26" t="inlineStr">
+        <is>
+          <t>Describe the question this scenario answers</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>Changes from baseline (blank means no change)</t>
+        </is>
+      </c>
+      <c r="B10" s="21" t="n"/>
+      <c r="D10" s="21" t="n"/>
+      <c r="E10" s="21" t="n"/>
+      <c r="F10" s="21" t="n"/>
+      <c r="G10" s="21" t="n"/>
+      <c r="H10" s="21" t="n"/>
+      <c r="I10" s="21" t="n"/>
+      <c r="J10" s="21" t="n"/>
+      <c r="K10" s="21" t="n"/>
+      <c r="L10" s="21" t="n"/>
+      <c r="M10" s="21" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>Funded territories</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Territory design: how many territories the company funds · leverage point 10</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F11" s="52" t="n"/>
+      <c r="G11" s="52" t="n"/>
+      <c r="H11" s="52" t="n"/>
+      <c r="I11" s="52" t="n"/>
+      <c r="J11" s="52" t="n"/>
+      <c r="K11" s="52" t="n"/>
+      <c r="L11" s="52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M11" s="52" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Open territories filled</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Staffing: open territories filled during the year (up to the number open) · leverage point 10</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="53" t="n"/>
+      <c r="F12" s="53">
+        <f>N(v_open_territories)</f>
+        <v/>
+      </c>
+      <c r="G12" s="53" t="n"/>
+      <c r="H12" s="53" t="n"/>
+      <c r="I12" s="53" t="n"/>
+      <c r="J12" s="53" t="n"/>
+      <c r="K12" s="53" t="n"/>
+      <c r="L12" s="53" t="n"/>
+      <c r="M12" s="53" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Days to fill a territory</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Delay: approvals and recruiting · leverage point 9</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="52" t="n"/>
+      <c r="F13" s="52" t="n"/>
+      <c r="G13" s="52" t="n"/>
+      <c r="H13" s="52" t="n"/>
+      <c r="I13" s="52" t="n"/>
+      <c r="J13" s="52" t="n"/>
+      <c r="K13" s="52" t="n"/>
+      <c r="L13" s="52" t="n"/>
+      <c r="M13" s="52" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Ramp time</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Delay: months until a new salesperson is fully productive · leverage point 9</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="52" t="n"/>
+      <c r="F14" s="52" t="n"/>
+      <c r="G14" s="52" t="n"/>
+      <c r="H14" s="52" t="n"/>
+      <c r="I14" s="52" t="n"/>
+      <c r="J14" s="52" t="n"/>
+      <c r="K14" s="52" t="n"/>
+      <c r="L14" s="52" t="n"/>
+      <c r="M14" s="52" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Opportunities a salesperson can manage</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Capacity: how many opportunities a salesperson can hold and advance well · leverage point 12</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="52" t="n"/>
+      <c r="F15" s="52" t="n"/>
+      <c r="G15" s="52" t="n"/>
+      <c r="H15" s="52" t="n"/>
+      <c r="I15" s="52" t="n"/>
+      <c r="J15" s="52" t="n"/>
+      <c r="K15" s="52" t="n"/>
+      <c r="L15" s="52" t="n"/>
+      <c r="M15" s="52" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Opportunities each salesperson holds</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline: qualified opportunities reaching salespeople (needs pipeline data on tab 1) · leverage point 11</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="52" t="n"/>
+      <c r="F16" s="52" t="n"/>
+      <c r="G16" s="52" t="n"/>
+      <c r="H16" s="52" t="n"/>
+      <c r="I16" s="52" t="n"/>
+      <c r="J16" s="52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K16" s="52" t="n"/>
+      <c r="L16" s="52" t="n"/>
+      <c r="M16" s="52" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Sales cycle</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Delay: time from qualified opportunity to signature · leverage point 9</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="52" t="n"/>
+      <c r="F17" s="52" t="n"/>
+      <c r="G17" s="52" t="n"/>
+      <c r="H17" s="52" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I17" s="52" t="n"/>
+      <c r="J17" s="52" t="n"/>
+      <c r="K17" s="52" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L17" s="52" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M17" s="52" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>Close rate</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Conversion · leverage point 12</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="52" t="n"/>
+      <c r="F18" s="52" t="n"/>
+      <c r="G18" s="52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H18" s="52" t="n"/>
+      <c r="I18" s="52" t="n"/>
+      <c r="J18" s="52" t="n"/>
+      <c r="K18" s="52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L18" s="52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M18" s="52" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Average revenue per contract</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Value per contract · leverage point 12</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="52" t="n"/>
+      <c r="F19" s="52" t="n"/>
+      <c r="G19" s="52" t="n"/>
+      <c r="H19" s="52" t="n"/>
+      <c r="I19" s="52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J19" s="52" t="n"/>
+      <c r="K19" s="52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L19" s="52" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M19" s="52" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Salesperson compensation (salary and load)</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Cost per salesperson · leverage point 12</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="52" t="n"/>
+      <c r="F20" s="52" t="n"/>
+      <c r="G20" s="52" t="n"/>
+      <c r="H20" s="52" t="n"/>
+      <c r="I20" s="52" t="n"/>
+      <c r="J20" s="52" t="n"/>
+      <c r="K20" s="52" t="n"/>
+      <c r="L20" s="52" t="n"/>
+      <c r="M20" s="52" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>Commission rate</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Rule: compensation plan · leverage point 5</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="52" t="n"/>
+      <c r="F21" s="52" t="n"/>
+      <c r="G21" s="52" t="n"/>
+      <c r="H21" s="52" t="n"/>
+      <c r="I21" s="52" t="n"/>
+      <c r="J21" s="52" t="n"/>
+      <c r="K21" s="52" t="n"/>
+      <c r="L21" s="52" t="n"/>
+      <c r="M21" s="52" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Sales overhead</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Change in dollars · leverage point 12</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="54" t="n"/>
+      <c r="F22" s="54" t="n"/>
+      <c r="G22" s="54" t="n"/>
+      <c r="H22" s="54" t="n"/>
+      <c r="I22" s="54" t="n"/>
+      <c r="J22" s="54" t="n"/>
+      <c r="K22" s="54" t="n"/>
+      <c r="L22" s="54" t="n"/>
+      <c r="M22" s="54" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Change in dollars · leverage point 12</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n"/>
+      <c r="E23" s="54" t="n"/>
+      <c r="F23" s="54" t="n"/>
+      <c r="G23" s="54" t="n"/>
+      <c r="H23" s="54" t="n"/>
+      <c r="I23" s="54" t="n"/>
+      <c r="J23" s="54" t="n"/>
+      <c r="K23" s="54" t="n"/>
+      <c r="L23" s="54" t="n"/>
+      <c r="M23" s="54" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Cost of making the change (one-time)</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Enablement, tools, hiring, consulting: what the improvement costs this year · leverage point 12</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="54" t="n"/>
+      <c r="F24" s="54" t="n"/>
+      <c r="G24" s="54" t="n"/>
+      <c r="H24" s="54" t="n"/>
+      <c r="I24" s="54" t="n"/>
+      <c r="J24" s="54" t="n"/>
+      <c r="K24" s="54" t="n"/>
+      <c r="L24" s="54" t="n"/>
+      <c r="M24" s="54" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>Territory design and staffing</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="n"/>
+      <c r="D26" s="21" t="n"/>
+      <c r="E26" s="21" t="n"/>
+      <c r="F26" s="21" t="n"/>
+      <c r="G26" s="21" t="n"/>
+      <c r="H26" s="21" t="n"/>
+      <c r="I26" s="21" t="n"/>
+      <c r="J26" s="21" t="n"/>
+      <c r="K26" s="21" t="n"/>
+      <c r="L26" s="21" t="n"/>
+      <c r="M26" s="21" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Funded territories</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Tab 1 funded territories × change</t>
+        </is>
+      </c>
+      <c r="D27" s="55">
+        <f>v_territory_count*(1+D11)</f>
+        <v/>
+      </c>
+      <c r="E27" s="55">
+        <f>v_territory_count*(1+E11)</f>
+        <v/>
+      </c>
+      <c r="F27" s="55">
+        <f>v_territory_count*(1+F11)</f>
+        <v/>
+      </c>
+      <c r="G27" s="55">
+        <f>v_territory_count*(1+G11)</f>
+        <v/>
+      </c>
+      <c r="H27" s="55">
+        <f>v_territory_count*(1+H11)</f>
+        <v/>
+      </c>
+      <c r="I27" s="55">
+        <f>v_territory_count*(1+I11)</f>
+        <v/>
+      </c>
+      <c r="J27" s="55">
+        <f>v_territory_count*(1+J11)</f>
+        <v/>
+      </c>
+      <c r="K27" s="55">
+        <f>v_territory_count*(1+K11)</f>
+        <v/>
+      </c>
+      <c r="L27" s="55">
+        <f>v_territory_count*(1+L11)</f>
+        <v/>
+      </c>
+      <c r="M27" s="55">
+        <f>v_territory_count*(1+M11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Open territories at start</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Tab 1 (0 if not provided)</t>
+        </is>
+      </c>
+      <c r="D28" s="55">
+        <f>N(v_open_territories)</f>
+        <v/>
+      </c>
+      <c r="E28" s="55">
+        <f>N(v_open_territories)</f>
+        <v/>
+      </c>
+      <c r="F28" s="55">
+        <f>N(v_open_territories)</f>
+        <v/>
+      </c>
+      <c r="G28" s="55">
+        <f>N(v_open_territories)</f>
+        <v/>
+      </c>
+      <c r="H28" s="55">
+        <f>N(v_open_territories)</f>
+        <v/>
+      </c>
+      <c r="I28" s="55">
+        <f>N(v_open_territories)</f>
+        <v/>
+      </c>
+      <c r="J28" s="55">
+        <f>N(v_open_territories)</f>
+        <v/>
+      </c>
+      <c r="K28" s="55">
+        <f>N(v_open_territories)</f>
+        <v/>
+      </c>
+      <c r="L28" s="55">
+        <f>N(v_open_territories)</f>
+        <v/>
+      </c>
+      <c r="M28" s="55">
+        <f>N(v_open_territories)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Filled territories at start</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Funded − open</t>
+        </is>
+      </c>
+      <c r="D29" s="55">
+        <f>v_territory_count-D28</f>
+        <v/>
+      </c>
+      <c r="E29" s="55">
+        <f>v_territory_count-E28</f>
+        <v/>
+      </c>
+      <c r="F29" s="55">
+        <f>v_territory_count-F28</f>
+        <v/>
+      </c>
+      <c r="G29" s="55">
+        <f>v_territory_count-G28</f>
+        <v/>
+      </c>
+      <c r="H29" s="55">
+        <f>v_territory_count-H28</f>
+        <v/>
+      </c>
+      <c r="I29" s="55">
+        <f>v_territory_count-I28</f>
+        <v/>
+      </c>
+      <c r="J29" s="55">
+        <f>v_territory_count-J28</f>
+        <v/>
+      </c>
+      <c r="K29" s="55">
+        <f>v_territory_count-K28</f>
+        <v/>
+      </c>
+      <c r="L29" s="55">
+        <f>v_territory_count-L28</f>
+        <v/>
+      </c>
+      <c r="M29" s="55">
+        <f>v_territory_count-M28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>New territories added</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Design change</t>
+        </is>
+      </c>
+      <c r="D30" s="55">
+        <f>D27-v_territory_count</f>
+        <v/>
+      </c>
+      <c r="E30" s="55">
+        <f>E27-v_territory_count</f>
+        <v/>
+      </c>
+      <c r="F30" s="55">
+        <f>F27-v_territory_count</f>
+        <v/>
+      </c>
+      <c r="G30" s="55">
+        <f>G27-v_territory_count</f>
+        <v/>
+      </c>
+      <c r="H30" s="55">
+        <f>H27-v_territory_count</f>
+        <v/>
+      </c>
+      <c r="I30" s="55">
+        <f>I27-v_territory_count</f>
+        <v/>
+      </c>
+      <c r="J30" s="55">
+        <f>J27-v_territory_count</f>
+        <v/>
+      </c>
+      <c r="K30" s="55">
+        <f>K27-v_territory_count</f>
+        <v/>
+      </c>
+      <c r="L30" s="55">
+        <f>L27-v_territory_count</f>
+        <v/>
+      </c>
+      <c r="M30" s="55">
+        <f>M27-v_territory_count</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>Open territories filled</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Up to the number open</t>
+        </is>
+      </c>
+      <c r="D31" s="55">
+        <f>MIN(N(D12),D28)</f>
+        <v/>
+      </c>
+      <c r="E31" s="55">
+        <f>MIN(N(E12),E28)</f>
+        <v/>
+      </c>
+      <c r="F31" s="55">
+        <f>MIN(N(F12),F28)</f>
+        <v/>
+      </c>
+      <c r="G31" s="55">
+        <f>MIN(N(G12),G28)</f>
+        <v/>
+      </c>
+      <c r="H31" s="55">
+        <f>MIN(N(H12),H28)</f>
+        <v/>
+      </c>
+      <c r="I31" s="55">
+        <f>MIN(N(I12),I28)</f>
+        <v/>
+      </c>
+      <c r="J31" s="55">
+        <f>MIN(N(J12),J28)</f>
+        <v/>
+      </c>
+      <c r="K31" s="55">
+        <f>MIN(N(K12),K28)</f>
+        <v/>
+      </c>
+      <c r="L31" s="55">
+        <f>MIN(N(L12),L28)</f>
+        <v/>
+      </c>
+      <c r="M31" s="55">
+        <f>MIN(N(M12),M28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Territories still open</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Each one is expected yield not produced</t>
+        </is>
+      </c>
+      <c r="D32" s="55">
+        <f>D28-D31</f>
+        <v/>
+      </c>
+      <c r="E32" s="55">
+        <f>E28-E31</f>
+        <v/>
+      </c>
+      <c r="F32" s="55">
+        <f>F28-F31</f>
+        <v/>
+      </c>
+      <c r="G32" s="55">
+        <f>G28-G31</f>
+        <v/>
+      </c>
+      <c r="H32" s="55">
+        <f>H28-H31</f>
+        <v/>
+      </c>
+      <c r="I32" s="55">
+        <f>I28-I31</f>
+        <v/>
+      </c>
+      <c r="J32" s="55">
+        <f>J28-J31</f>
+        <v/>
+      </c>
+      <c r="K32" s="55">
+        <f>K28-K31</f>
+        <v/>
+      </c>
+      <c r="L32" s="55">
+        <f>L28-L31</f>
+        <v/>
+      </c>
+      <c r="M32" s="55">
+        <f>M28-M31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Months to fill a territory</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Tab 1 days ÷ 30.4 × change</t>
+        </is>
+      </c>
+      <c r="D33" s="56">
+        <f>N(v_time_to_fill_days)/30.4*(1+D13)</f>
+        <v/>
+      </c>
+      <c r="E33" s="56">
+        <f>N(v_time_to_fill_days)/30.4*(1+E13)</f>
+        <v/>
+      </c>
+      <c r="F33" s="56">
+        <f>N(v_time_to_fill_days)/30.4*(1+F13)</f>
+        <v/>
+      </c>
+      <c r="G33" s="56">
+        <f>N(v_time_to_fill_days)/30.4*(1+G13)</f>
+        <v/>
+      </c>
+      <c r="H33" s="56">
+        <f>N(v_time_to_fill_days)/30.4*(1+H13)</f>
+        <v/>
+      </c>
+      <c r="I33" s="56">
+        <f>N(v_time_to_fill_days)/30.4*(1+I13)</f>
+        <v/>
+      </c>
+      <c r="J33" s="56">
+        <f>N(v_time_to_fill_days)/30.4*(1+J13)</f>
+        <v/>
+      </c>
+      <c r="K33" s="56">
+        <f>N(v_time_to_fill_days)/30.4*(1+K13)</f>
+        <v/>
+      </c>
+      <c r="L33" s="56">
+        <f>N(v_time_to_fill_days)/30.4*(1+L13)</f>
+        <v/>
+      </c>
+      <c r="M33" s="56">
+        <f>N(v_time_to_fill_days)/30.4*(1+M13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>Ramp time (months)</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Tab 1 × change</t>
+        </is>
+      </c>
+      <c r="D34" s="56">
+        <f>v_ramp_months*(1+D14)</f>
+        <v/>
+      </c>
+      <c r="E34" s="56">
+        <f>v_ramp_months*(1+E14)</f>
+        <v/>
+      </c>
+      <c r="F34" s="56">
+        <f>v_ramp_months*(1+F14)</f>
+        <v/>
+      </c>
+      <c r="G34" s="56">
+        <f>v_ramp_months*(1+G14)</f>
+        <v/>
+      </c>
+      <c r="H34" s="56">
+        <f>v_ramp_months*(1+H14)</f>
+        <v/>
+      </c>
+      <c r="I34" s="56">
+        <f>v_ramp_months*(1+I14)</f>
+        <v/>
+      </c>
+      <c r="J34" s="56">
+        <f>v_ramp_months*(1+J14)</f>
+        <v/>
+      </c>
+      <c r="K34" s="56">
+        <f>v_ramp_months*(1+K14)</f>
+        <v/>
+      </c>
+      <c r="L34" s="56">
+        <f>v_ramp_months*(1+L14)</f>
+        <v/>
+      </c>
+      <c r="M34" s="56">
+        <f>v_ramp_months*(1+M14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Share of year a newly staffed territory produces</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Year one: (12 − fill − ramp) ÷ 12; steady state: 1</t>
+        </is>
+      </c>
+      <c r="D35" s="57">
+        <f>IF(wi_view="Steady state",1,MAX(0,12-D33-D34)/12)</f>
+        <v/>
+      </c>
+      <c r="E35" s="57">
+        <f>IF(wi_view="Steady state",1,MAX(0,12-E33-E34)/12)</f>
+        <v/>
+      </c>
+      <c r="F35" s="57">
+        <f>IF(wi_view="Steady state",1,MAX(0,12-F33-F34)/12)</f>
+        <v/>
+      </c>
+      <c r="G35" s="57">
+        <f>IF(wi_view="Steady state",1,MAX(0,12-G33-G34)/12)</f>
+        <v/>
+      </c>
+      <c r="H35" s="57">
+        <f>IF(wi_view="Steady state",1,MAX(0,12-H33-H34)/12)</f>
+        <v/>
+      </c>
+      <c r="I35" s="57">
+        <f>IF(wi_view="Steady state",1,MAX(0,12-I33-I34)/12)</f>
+        <v/>
+      </c>
+      <c r="J35" s="57">
+        <f>IF(wi_view="Steady state",1,MAX(0,12-J33-J34)/12)</f>
+        <v/>
+      </c>
+      <c r="K35" s="57">
+        <f>IF(wi_view="Steady state",1,MAX(0,12-K33-K34)/12)</f>
+        <v/>
+      </c>
+      <c r="L35" s="57">
+        <f>IF(wi_view="Steady state",1,MAX(0,12-L33-L34)/12)</f>
+        <v/>
+      </c>
+      <c r="M35" s="57">
+        <f>IF(wi_view="Steady state",1,MAX(0,12-M33-M34)/12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>Share of year a new salesperson is paid</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Year one: (12 − fill) ÷ 12; steady state: 1</t>
+        </is>
+      </c>
+      <c r="D36" s="57">
+        <f>IF(wi_view="Steady state",1,MAX(0,12-D33)/12)</f>
+        <v/>
+      </c>
+      <c r="E36" s="57">
+        <f>IF(wi_view="Steady state",1,MAX(0,12-E33)/12)</f>
+        <v/>
+      </c>
+      <c r="F36" s="57">
+        <f>IF(wi_view="Steady state",1,MAX(0,12-F33)/12)</f>
+        <v/>
+      </c>
+      <c r="G36" s="57">
+        <f>IF(wi_view="Steady state",1,MAX(0,12-G33)/12)</f>
+        <v/>
+      </c>
+      <c r="H36" s="57">
+        <f>IF(wi_view="Steady state",1,MAX(0,12-H33)/12)</f>
+        <v/>
+      </c>
+      <c r="I36" s="57">
+        <f>IF(wi_view="Steady state",1,MAX(0,12-I33)/12)</f>
+        <v/>
+      </c>
+      <c r="J36" s="57">
+        <f>IF(wi_view="Steady state",1,MAX(0,12-J33)/12)</f>
+        <v/>
+      </c>
+      <c r="K36" s="57">
+        <f>IF(wi_view="Steady state",1,MAX(0,12-K33)/12)</f>
+        <v/>
+      </c>
+      <c r="L36" s="57">
+        <f>IF(wi_view="Steady state",1,MAX(0,12-L33)/12)</f>
+        <v/>
+      </c>
+      <c r="M36" s="57">
+        <f>IF(wi_view="Steady state",1,MAX(0,12-M33)/12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Productive salespeople in filled territories</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Tab 1 productive salespeople, if provided</t>
+        </is>
+      </c>
+      <c r="D37" s="55">
+        <f>IF(N(v_productive_salespeople)&gt;0,MIN(D29,v_productive_salespeople),D29)</f>
+        <v/>
+      </c>
+      <c r="E37" s="55">
+        <f>IF(N(v_productive_salespeople)&gt;0,MIN(E29,v_productive_salespeople),E29)</f>
+        <v/>
+      </c>
+      <c r="F37" s="55">
+        <f>IF(N(v_productive_salespeople)&gt;0,MIN(F29,v_productive_salespeople),F29)</f>
+        <v/>
+      </c>
+      <c r="G37" s="55">
+        <f>IF(N(v_productive_salespeople)&gt;0,MIN(G29,v_productive_salespeople),G29)</f>
+        <v/>
+      </c>
+      <c r="H37" s="55">
+        <f>IF(N(v_productive_salespeople)&gt;0,MIN(H29,v_productive_salespeople),H29)</f>
+        <v/>
+      </c>
+      <c r="I37" s="55">
+        <f>IF(N(v_productive_salespeople)&gt;0,MIN(I29,v_productive_salespeople),I29)</f>
+        <v/>
+      </c>
+      <c r="J37" s="55">
+        <f>IF(N(v_productive_salespeople)&gt;0,MIN(J29,v_productive_salespeople),J29)</f>
+        <v/>
+      </c>
+      <c r="K37" s="55">
+        <f>IF(N(v_productive_salespeople)&gt;0,MIN(K29,v_productive_salespeople),K29)</f>
+        <v/>
+      </c>
+      <c r="L37" s="55">
+        <f>IF(N(v_productive_salespeople)&gt;0,MIN(L29,v_productive_salespeople),L29)</f>
+        <v/>
+      </c>
+      <c r="M37" s="55">
+        <f>IF(N(v_productive_salespeople)&gt;0,MIN(M29,v_productive_salespeople),M29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Productive territory-years</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>What actually produces revenue this year</t>
+        </is>
+      </c>
+      <c r="D38" s="55">
+        <f>D37+(D31+D30)*D35</f>
+        <v/>
+      </c>
+      <c r="E38" s="55">
+        <f>E37+(E31+E30)*E35</f>
+        <v/>
+      </c>
+      <c r="F38" s="55">
+        <f>F37+(F31+F30)*F35</f>
+        <v/>
+      </c>
+      <c r="G38" s="55">
+        <f>G37+(G31+G30)*G35</f>
+        <v/>
+      </c>
+      <c r="H38" s="55">
+        <f>H37+(H31+H30)*H35</f>
+        <v/>
+      </c>
+      <c r="I38" s="55">
+        <f>I37+(I31+I30)*I35</f>
+        <v/>
+      </c>
+      <c r="J38" s="55">
+        <f>J37+(J31+J30)*J35</f>
+        <v/>
+      </c>
+      <c r="K38" s="55">
+        <f>K37+(K31+K30)*K35</f>
+        <v/>
+      </c>
+      <c r="L38" s="55">
+        <f>L37+(L31+L30)*L35</f>
+        <v/>
+      </c>
+      <c r="M38" s="55">
+        <f>M37+(M31+M30)*M35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Salesperson-years paid</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>What the company pays for this year</t>
+        </is>
+      </c>
+      <c r="D39" s="55">
+        <f>D29+(D31+D30)*D36</f>
+        <v/>
+      </c>
+      <c r="E39" s="55">
+        <f>E29+(E31+E30)*E36</f>
+        <v/>
+      </c>
+      <c r="F39" s="55">
+        <f>F29+(F31+F30)*F36</f>
+        <v/>
+      </c>
+      <c r="G39" s="55">
+        <f>G29+(G31+G30)*G36</f>
+        <v/>
+      </c>
+      <c r="H39" s="55">
+        <f>H29+(H31+H30)*H36</f>
+        <v/>
+      </c>
+      <c r="I39" s="55">
+        <f>I29+(I31+I30)*I36</f>
+        <v/>
+      </c>
+      <c r="J39" s="55">
+        <f>J29+(J31+J30)*J36</f>
+        <v/>
+      </c>
+      <c r="K39" s="55">
+        <f>K29+(K31+K30)*K36</f>
+        <v/>
+      </c>
+      <c r="L39" s="55">
+        <f>L29+(L31+L30)*L36</f>
+        <v/>
+      </c>
+      <c r="M39" s="55">
+        <f>M29+(M31+M30)*M36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="inlineStr">
+        <is>
+          <t>Salesperson throughput</t>
+        </is>
+      </c>
+      <c r="B40" s="21" t="n"/>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="21" t="n"/>
+      <c r="G40" s="21" t="n"/>
+      <c r="H40" s="21" t="n"/>
+      <c r="I40" s="21" t="n"/>
+      <c r="J40" s="21" t="n"/>
+      <c r="K40" s="21" t="n"/>
+      <c r="L40" s="21" t="n"/>
+      <c r="M40" s="21" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Opportunities a salesperson can manage</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Tab 1 × change</t>
+        </is>
+      </c>
+      <c r="D41" s="55">
+        <f>v_opportunities_capacity*(1+D15)</f>
+        <v/>
+      </c>
+      <c r="E41" s="55">
+        <f>v_opportunities_capacity*(1+E15)</f>
+        <v/>
+      </c>
+      <c r="F41" s="55">
+        <f>v_opportunities_capacity*(1+F15)</f>
+        <v/>
+      </c>
+      <c r="G41" s="55">
+        <f>v_opportunities_capacity*(1+G15)</f>
+        <v/>
+      </c>
+      <c r="H41" s="55">
+        <f>v_opportunities_capacity*(1+H15)</f>
+        <v/>
+      </c>
+      <c r="I41" s="55">
+        <f>v_opportunities_capacity*(1+I15)</f>
+        <v/>
+      </c>
+      <c r="J41" s="55">
+        <f>v_opportunities_capacity*(1+J15)</f>
+        <v/>
+      </c>
+      <c r="K41" s="55">
+        <f>v_opportunities_capacity*(1+K15)</f>
+        <v/>
+      </c>
+      <c r="L41" s="55">
+        <f>v_opportunities_capacity*(1+L15)</f>
+        <v/>
+      </c>
+      <c r="M41" s="55">
+        <f>v_opportunities_capacity*(1+M15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Opportunities each salesperson holds</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Tab 1 pipeline data × change (blank if not provided)</t>
+        </is>
+      </c>
+      <c r="D42" s="55">
+        <f>IF(N(v_opportunities_load)=0,"",v_opportunities_load*(1+D16))</f>
+        <v/>
+      </c>
+      <c r="E42" s="55">
+        <f>IF(N(v_opportunities_load)=0,"",v_opportunities_load*(1+E16))</f>
+        <v/>
+      </c>
+      <c r="F42" s="55">
+        <f>IF(N(v_opportunities_load)=0,"",v_opportunities_load*(1+F16))</f>
+        <v/>
+      </c>
+      <c r="G42" s="55">
+        <f>IF(N(v_opportunities_load)=0,"",v_opportunities_load*(1+G16))</f>
+        <v/>
+      </c>
+      <c r="H42" s="55">
+        <f>IF(N(v_opportunities_load)=0,"",v_opportunities_load*(1+H16))</f>
+        <v/>
+      </c>
+      <c r="I42" s="55">
+        <f>IF(N(v_opportunities_load)=0,"",v_opportunities_load*(1+I16))</f>
+        <v/>
+      </c>
+      <c r="J42" s="55">
+        <f>IF(N(v_opportunities_load)=0,"",v_opportunities_load*(1+J16))</f>
+        <v/>
+      </c>
+      <c r="K42" s="55">
+        <f>IF(N(v_opportunities_load)=0,"",v_opportunities_load*(1+K16))</f>
+        <v/>
+      </c>
+      <c r="L42" s="55">
+        <f>IF(N(v_opportunities_load)=0,"",v_opportunities_load*(1+L16))</f>
+        <v/>
+      </c>
+      <c r="M42" s="55">
+        <f>IF(N(v_opportunities_load)=0,"",v_opportunities_load*(1+M16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>Opportunities worked at once</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>The lower of what they hold and what they can manage</t>
+        </is>
+      </c>
+      <c r="D43" s="55">
+        <f>IF(D42="",D41,MIN(D42,D41))</f>
+        <v/>
+      </c>
+      <c r="E43" s="55">
+        <f>IF(E42="",E41,MIN(E42,E41))</f>
+        <v/>
+      </c>
+      <c r="F43" s="55">
+        <f>IF(F42="",F41,MIN(F42,F41))</f>
+        <v/>
+      </c>
+      <c r="G43" s="55">
+        <f>IF(G42="",G41,MIN(G42,G41))</f>
+        <v/>
+      </c>
+      <c r="H43" s="55">
+        <f>IF(H42="",H41,MIN(H42,H41))</f>
+        <v/>
+      </c>
+      <c r="I43" s="55">
+        <f>IF(I42="",I41,MIN(I42,I41))</f>
+        <v/>
+      </c>
+      <c r="J43" s="55">
+        <f>IF(J42="",J41,MIN(J42,J41))</f>
+        <v/>
+      </c>
+      <c r="K43" s="55">
+        <f>IF(K42="",K41,MIN(K42,K41))</f>
+        <v/>
+      </c>
+      <c r="L43" s="55">
+        <f>IF(L42="",L41,MIN(L42,L41))</f>
+        <v/>
+      </c>
+      <c r="M43" s="55">
+        <f>IF(M42="",M41,MIN(M42,M41))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Utilization of capacity</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Held ÷ can manage</t>
+        </is>
+      </c>
+      <c r="D44" s="57">
+        <f>IF(D42="","",D42/D41)</f>
+        <v/>
+      </c>
+      <c r="E44" s="57">
+        <f>IF(E42="","",E42/E41)</f>
+        <v/>
+      </c>
+      <c r="F44" s="57">
+        <f>IF(F42="","",F42/F41)</f>
+        <v/>
+      </c>
+      <c r="G44" s="57">
+        <f>IF(G42="","",G42/G41)</f>
+        <v/>
+      </c>
+      <c r="H44" s="57">
+        <f>IF(H42="","",H42/H41)</f>
+        <v/>
+      </c>
+      <c r="I44" s="57">
+        <f>IF(I42="","",I42/I41)</f>
+        <v/>
+      </c>
+      <c r="J44" s="57">
+        <f>IF(J42="","",J42/J41)</f>
+        <v/>
+      </c>
+      <c r="K44" s="57">
+        <f>IF(K42="","",K42/K41)</f>
+        <v/>
+      </c>
+      <c r="L44" s="57">
+        <f>IF(L42="","",L42/L41)</f>
+        <v/>
+      </c>
+      <c r="M44" s="57">
+        <f>IF(M42="","",M42/M41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Sales cycle (months)</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Tab 1 × change</t>
+        </is>
+      </c>
+      <c r="D45" s="56">
+        <f>v_cycle_months*(1+D17)</f>
+        <v/>
+      </c>
+      <c r="E45" s="56">
+        <f>v_cycle_months*(1+E17)</f>
+        <v/>
+      </c>
+      <c r="F45" s="56">
+        <f>v_cycle_months*(1+F17)</f>
+        <v/>
+      </c>
+      <c r="G45" s="56">
+        <f>v_cycle_months*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="H45" s="56">
+        <f>v_cycle_months*(1+H17)</f>
+        <v/>
+      </c>
+      <c r="I45" s="56">
+        <f>v_cycle_months*(1+I17)</f>
+        <v/>
+      </c>
+      <c r="J45" s="56">
+        <f>v_cycle_months*(1+J17)</f>
+        <v/>
+      </c>
+      <c r="K45" s="56">
+        <f>v_cycle_months*(1+K17)</f>
+        <v/>
+      </c>
+      <c r="L45" s="56">
+        <f>v_cycle_months*(1+L17)</f>
+        <v/>
+      </c>
+      <c r="M45" s="56">
+        <f>v_cycle_months*(1+M17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Opportunities resolved per salesperson per year</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Little's Law: worked × 12 ÷ cycle</t>
+        </is>
+      </c>
+      <c r="D46" s="55">
+        <f>D43*12/D45</f>
+        <v/>
+      </c>
+      <c r="E46" s="55">
+        <f>E43*12/E45</f>
+        <v/>
+      </c>
+      <c r="F46" s="55">
+        <f>F43*12/F45</f>
+        <v/>
+      </c>
+      <c r="G46" s="55">
+        <f>G43*12/G45</f>
+        <v/>
+      </c>
+      <c r="H46" s="55">
+        <f>H43*12/H45</f>
+        <v/>
+      </c>
+      <c r="I46" s="55">
+        <f>I43*12/I45</f>
+        <v/>
+      </c>
+      <c r="J46" s="55">
+        <f>J43*12/J45</f>
+        <v/>
+      </c>
+      <c r="K46" s="55">
+        <f>K43*12/K45</f>
+        <v/>
+      </c>
+      <c r="L46" s="55">
+        <f>L43*12/L45</f>
+        <v/>
+      </c>
+      <c r="M46" s="55">
+        <f>M43*12/M45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>Close rate</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Tab 1 × change</t>
+        </is>
+      </c>
+      <c r="D47" s="58">
+        <f>v_win_rate*(1+D18)</f>
+        <v/>
+      </c>
+      <c r="E47" s="58">
+        <f>v_win_rate*(1+E18)</f>
+        <v/>
+      </c>
+      <c r="F47" s="58">
+        <f>v_win_rate*(1+F18)</f>
+        <v/>
+      </c>
+      <c r="G47" s="58">
+        <f>v_win_rate*(1+G18)</f>
+        <v/>
+      </c>
+      <c r="H47" s="58">
+        <f>v_win_rate*(1+H18)</f>
+        <v/>
+      </c>
+      <c r="I47" s="58">
+        <f>v_win_rate*(1+I18)</f>
+        <v/>
+      </c>
+      <c r="J47" s="58">
+        <f>v_win_rate*(1+J18)</f>
+        <v/>
+      </c>
+      <c r="K47" s="58">
+        <f>v_win_rate*(1+K18)</f>
+        <v/>
+      </c>
+      <c r="L47" s="58">
+        <f>v_win_rate*(1+L18)</f>
+        <v/>
+      </c>
+      <c r="M47" s="58">
+        <f>v_win_rate*(1+M18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>Contracts per productive territory</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Resolved × close rate</t>
+        </is>
+      </c>
+      <c r="D48" s="55">
+        <f>D46*D47</f>
+        <v/>
+      </c>
+      <c r="E48" s="55">
+        <f>E46*E47</f>
+        <v/>
+      </c>
+      <c r="F48" s="55">
+        <f>F46*F47</f>
+        <v/>
+      </c>
+      <c r="G48" s="55">
+        <f>G46*G47</f>
+        <v/>
+      </c>
+      <c r="H48" s="55">
+        <f>H46*H47</f>
+        <v/>
+      </c>
+      <c r="I48" s="55">
+        <f>I46*I47</f>
+        <v/>
+      </c>
+      <c r="J48" s="55">
+        <f>J46*J47</f>
+        <v/>
+      </c>
+      <c r="K48" s="55">
+        <f>K46*K47</f>
+        <v/>
+      </c>
+      <c r="L48" s="55">
+        <f>L46*L47</f>
+        <v/>
+      </c>
+      <c r="M48" s="55">
+        <f>M46*M47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Average revenue per contract</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Tab 1 × change</t>
+        </is>
+      </c>
+      <c r="D49" s="59">
+        <f>v_deal_size*(1+D19)</f>
+        <v/>
+      </c>
+      <c r="E49" s="59">
+        <f>v_deal_size*(1+E19)</f>
+        <v/>
+      </c>
+      <c r="F49" s="59">
+        <f>v_deal_size*(1+F19)</f>
+        <v/>
+      </c>
+      <c r="G49" s="59">
+        <f>v_deal_size*(1+G19)</f>
+        <v/>
+      </c>
+      <c r="H49" s="59">
+        <f>v_deal_size*(1+H19)</f>
+        <v/>
+      </c>
+      <c r="I49" s="59">
+        <f>v_deal_size*(1+I19)</f>
+        <v/>
+      </c>
+      <c r="J49" s="59">
+        <f>v_deal_size*(1+J19)</f>
+        <v/>
+      </c>
+      <c r="K49" s="59">
+        <f>v_deal_size*(1+K19)</f>
+        <v/>
+      </c>
+      <c r="L49" s="59">
+        <f>v_deal_size*(1+L19)</f>
+        <v/>
+      </c>
+      <c r="M49" s="59">
+        <f>v_deal_size*(1+M19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>Revenue per productive territory</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Contracts × revenue per contract</t>
+        </is>
+      </c>
+      <c r="D50" s="59">
+        <f>D48*D49</f>
+        <v/>
+      </c>
+      <c r="E50" s="59">
+        <f>E48*E49</f>
+        <v/>
+      </c>
+      <c r="F50" s="59">
+        <f>F48*F49</f>
+        <v/>
+      </c>
+      <c r="G50" s="59">
+        <f>G48*G49</f>
+        <v/>
+      </c>
+      <c r="H50" s="59">
+        <f>H48*H49</f>
+        <v/>
+      </c>
+      <c r="I50" s="59">
+        <f>I48*I49</f>
+        <v/>
+      </c>
+      <c r="J50" s="59">
+        <f>J48*J49</f>
+        <v/>
+      </c>
+      <c r="K50" s="59">
+        <f>K48*K49</f>
+        <v/>
+      </c>
+      <c r="L50" s="59">
+        <f>L48*L49</f>
+        <v/>
+      </c>
+      <c r="M50" s="59">
+        <f>M48*M49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>Income statement</t>
+        </is>
+      </c>
+      <c r="B51" s="21" t="n"/>
+      <c r="D51" s="21" t="n"/>
+      <c r="E51" s="21" t="n"/>
+      <c r="F51" s="21" t="n"/>
+      <c r="G51" s="21" t="n"/>
+      <c r="H51" s="21" t="n"/>
+      <c r="I51" s="21" t="n"/>
+      <c r="J51" s="21" t="n"/>
+      <c r="K51" s="21" t="n"/>
+      <c r="L51" s="21" t="n"/>
+      <c r="M51" s="21" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Contracts</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Per territory × productive territory-years</t>
+        </is>
+      </c>
+      <c r="D52" s="60">
+        <f>D48*D38</f>
+        <v/>
+      </c>
+      <c r="E52" s="60">
+        <f>E48*E38</f>
+        <v/>
+      </c>
+      <c r="F52" s="60">
+        <f>F48*F38</f>
+        <v/>
+      </c>
+      <c r="G52" s="60">
+        <f>G48*G38</f>
+        <v/>
+      </c>
+      <c r="H52" s="60">
+        <f>H48*H38</f>
+        <v/>
+      </c>
+      <c r="I52" s="60">
+        <f>I48*I38</f>
+        <v/>
+      </c>
+      <c r="J52" s="60">
+        <f>J48*J38</f>
+        <v/>
+      </c>
+      <c r="K52" s="60">
+        <f>K48*K38</f>
+        <v/>
+      </c>
+      <c r="L52" s="60">
+        <f>L48*L38</f>
+        <v/>
+      </c>
+      <c r="M52" s="60">
+        <f>M48*M38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Per territory × productive territory-years</t>
+        </is>
+      </c>
+      <c r="D53" s="61">
+        <f>D50*D38</f>
+        <v/>
+      </c>
+      <c r="E53" s="61">
+        <f>E50*E38</f>
+        <v/>
+      </c>
+      <c r="F53" s="61">
+        <f>F50*F38</f>
+        <v/>
+      </c>
+      <c r="G53" s="61">
+        <f>G50*G38</f>
+        <v/>
+      </c>
+      <c r="H53" s="61">
+        <f>H50*H38</f>
+        <v/>
+      </c>
+      <c r="I53" s="61">
+        <f>I50*I38</f>
+        <v/>
+      </c>
+      <c r="J53" s="61">
+        <f>J50*J38</f>
+        <v/>
+      </c>
+      <c r="K53" s="61">
+        <f>K50*K38</f>
+        <v/>
+      </c>
+      <c r="L53" s="61">
+        <f>L50*L38</f>
+        <v/>
+      </c>
+      <c r="M53" s="61">
+        <f>M50*M38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>Cost of revenue</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Revenue × tab 1 %</t>
+        </is>
+      </c>
+      <c r="D54" s="59">
+        <f>D53*v_cost_of_revenue_pct</f>
+        <v/>
+      </c>
+      <c r="E54" s="59">
+        <f>E53*v_cost_of_revenue_pct</f>
+        <v/>
+      </c>
+      <c r="F54" s="59">
+        <f>F53*v_cost_of_revenue_pct</f>
+        <v/>
+      </c>
+      <c r="G54" s="59">
+        <f>G53*v_cost_of_revenue_pct</f>
+        <v/>
+      </c>
+      <c r="H54" s="59">
+        <f>H53*v_cost_of_revenue_pct</f>
+        <v/>
+      </c>
+      <c r="I54" s="59">
+        <f>I53*v_cost_of_revenue_pct</f>
+        <v/>
+      </c>
+      <c r="J54" s="59">
+        <f>J53*v_cost_of_revenue_pct</f>
+        <v/>
+      </c>
+      <c r="K54" s="59">
+        <f>K53*v_cost_of_revenue_pct</f>
+        <v/>
+      </c>
+      <c r="L54" s="59">
+        <f>L53*v_cost_of_revenue_pct</f>
+        <v/>
+      </c>
+      <c r="M54" s="59">
+        <f>M53*v_cost_of_revenue_pct</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>Research and development</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Revenue × tab 1 %</t>
+        </is>
+      </c>
+      <c r="D55" s="59">
+        <f>D53*v_rnd_pct</f>
+        <v/>
+      </c>
+      <c r="E55" s="59">
+        <f>E53*v_rnd_pct</f>
+        <v/>
+      </c>
+      <c r="F55" s="59">
+        <f>F53*v_rnd_pct</f>
+        <v/>
+      </c>
+      <c r="G55" s="59">
+        <f>G53*v_rnd_pct</f>
+        <v/>
+      </c>
+      <c r="H55" s="59">
+        <f>H53*v_rnd_pct</f>
+        <v/>
+      </c>
+      <c r="I55" s="59">
+        <f>I53*v_rnd_pct</f>
+        <v/>
+      </c>
+      <c r="J55" s="59">
+        <f>J53*v_rnd_pct</f>
+        <v/>
+      </c>
+      <c r="K55" s="59">
+        <f>K53*v_rnd_pct</f>
+        <v/>
+      </c>
+      <c r="L55" s="59">
+        <f>L53*v_rnd_pct</f>
+        <v/>
+      </c>
+      <c r="M55" s="59">
+        <f>M53*v_rnd_pct</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Revenue × tab 1 %</t>
+        </is>
+      </c>
+      <c r="D56" s="59">
+        <f>D53*v_gna_pct</f>
+        <v/>
+      </c>
+      <c r="E56" s="59">
+        <f>E53*v_gna_pct</f>
+        <v/>
+      </c>
+      <c r="F56" s="59">
+        <f>F53*v_gna_pct</f>
+        <v/>
+      </c>
+      <c r="G56" s="59">
+        <f>G53*v_gna_pct</f>
+        <v/>
+      </c>
+      <c r="H56" s="59">
+        <f>H53*v_gna_pct</f>
+        <v/>
+      </c>
+      <c r="I56" s="59">
+        <f>I53*v_gna_pct</f>
+        <v/>
+      </c>
+      <c r="J56" s="59">
+        <f>J53*v_gna_pct</f>
+        <v/>
+      </c>
+      <c r="K56" s="59">
+        <f>K53*v_gna_pct</f>
+        <v/>
+      </c>
+      <c r="L56" s="59">
+        <f>L53*v_gna_pct</f>
+        <v/>
+      </c>
+      <c r="M56" s="59">
+        <f>M53*v_gna_pct</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>Salesperson salaries, load and travel</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>(Loaded salary + travel) × salesperson-years paid</t>
+        </is>
+      </c>
+      <c r="D57" s="59">
+        <f>(v_loaded_salary*(1+D20)+v_travel_per_salesperson)*D39</f>
+        <v/>
+      </c>
+      <c r="E57" s="59">
+        <f>(v_loaded_salary*(1+E20)+v_travel_per_salesperson)*E39</f>
+        <v/>
+      </c>
+      <c r="F57" s="59">
+        <f>(v_loaded_salary*(1+F20)+v_travel_per_salesperson)*F39</f>
+        <v/>
+      </c>
+      <c r="G57" s="59">
+        <f>(v_loaded_salary*(1+G20)+v_travel_per_salesperson)*G39</f>
+        <v/>
+      </c>
+      <c r="H57" s="59">
+        <f>(v_loaded_salary*(1+H20)+v_travel_per_salesperson)*H39</f>
+        <v/>
+      </c>
+      <c r="I57" s="59">
+        <f>(v_loaded_salary*(1+I20)+v_travel_per_salesperson)*I39</f>
+        <v/>
+      </c>
+      <c r="J57" s="59">
+        <f>(v_loaded_salary*(1+J20)+v_travel_per_salesperson)*J39</f>
+        <v/>
+      </c>
+      <c r="K57" s="59">
+        <f>(v_loaded_salary*(1+K20)+v_travel_per_salesperson)*K39</f>
+        <v/>
+      </c>
+      <c r="L57" s="59">
+        <f>(v_loaded_salary*(1+L20)+v_travel_per_salesperson)*L39</f>
+        <v/>
+      </c>
+      <c r="M57" s="59">
+        <f>(v_loaded_salary*(1+M20)+v_travel_per_salesperson)*M39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>Commissions</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Rate × revenue (only on revenue produced)</t>
+        </is>
+      </c>
+      <c r="D58" s="59">
+        <f>v_commission_rate*(1+D21)*D53</f>
+        <v/>
+      </c>
+      <c r="E58" s="59">
+        <f>v_commission_rate*(1+E21)*E53</f>
+        <v/>
+      </c>
+      <c r="F58" s="59">
+        <f>v_commission_rate*(1+F21)*F53</f>
+        <v/>
+      </c>
+      <c r="G58" s="59">
+        <f>v_commission_rate*(1+G21)*G53</f>
+        <v/>
+      </c>
+      <c r="H58" s="59">
+        <f>v_commission_rate*(1+H21)*H53</f>
+        <v/>
+      </c>
+      <c r="I58" s="59">
+        <f>v_commission_rate*(1+I21)*I53</f>
+        <v/>
+      </c>
+      <c r="J58" s="59">
+        <f>v_commission_rate*(1+J21)*J53</f>
+        <v/>
+      </c>
+      <c r="K58" s="59">
+        <f>v_commission_rate*(1+K21)*K53</f>
+        <v/>
+      </c>
+      <c r="L58" s="59">
+        <f>v_commission_rate*(1+L21)*L53</f>
+        <v/>
+      </c>
+      <c r="M58" s="59">
+        <f>v_commission_rate*(1+M21)*M53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Sales overhead</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Tab 1 + change</t>
+        </is>
+      </c>
+      <c r="D59" s="59">
+        <f>v_sales_overhead+D22</f>
+        <v/>
+      </c>
+      <c r="E59" s="59">
+        <f>v_sales_overhead+E22</f>
+        <v/>
+      </c>
+      <c r="F59" s="59">
+        <f>v_sales_overhead+F22</f>
+        <v/>
+      </c>
+      <c r="G59" s="59">
+        <f>v_sales_overhead+G22</f>
+        <v/>
+      </c>
+      <c r="H59" s="59">
+        <f>v_sales_overhead+H22</f>
+        <v/>
+      </c>
+      <c r="I59" s="59">
+        <f>v_sales_overhead+I22</f>
+        <v/>
+      </c>
+      <c r="J59" s="59">
+        <f>v_sales_overhead+J22</f>
+        <v/>
+      </c>
+      <c r="K59" s="59">
+        <f>v_sales_overhead+K22</f>
+        <v/>
+      </c>
+      <c r="L59" s="59">
+        <f>v_sales_overhead+L22</f>
+        <v/>
+      </c>
+      <c r="M59" s="59">
+        <f>v_sales_overhead+M22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Tab 1 + change</t>
+        </is>
+      </c>
+      <c r="D60" s="59">
+        <f>v_marketing+D23</f>
+        <v/>
+      </c>
+      <c r="E60" s="59">
+        <f>v_marketing+E23</f>
+        <v/>
+      </c>
+      <c r="F60" s="59">
+        <f>v_marketing+F23</f>
+        <v/>
+      </c>
+      <c r="G60" s="59">
+        <f>v_marketing+G23</f>
+        <v/>
+      </c>
+      <c r="H60" s="59">
+        <f>v_marketing+H23</f>
+        <v/>
+      </c>
+      <c r="I60" s="59">
+        <f>v_marketing+I23</f>
+        <v/>
+      </c>
+      <c r="J60" s="59">
+        <f>v_marketing+J23</f>
+        <v/>
+      </c>
+      <c r="K60" s="59">
+        <f>v_marketing+K23</f>
+        <v/>
+      </c>
+      <c r="L60" s="59">
+        <f>v_marketing+L23</f>
+        <v/>
+      </c>
+      <c r="M60" s="59">
+        <f>v_marketing+M23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Cost of making the change</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>From the change rows</t>
+        </is>
+      </c>
+      <c r="D61" s="59">
+        <f>D24</f>
+        <v/>
+      </c>
+      <c r="E61" s="59">
+        <f>E24</f>
+        <v/>
+      </c>
+      <c r="F61" s="59">
+        <f>F24</f>
+        <v/>
+      </c>
+      <c r="G61" s="59">
+        <f>G24</f>
+        <v/>
+      </c>
+      <c r="H61" s="59">
+        <f>H24</f>
+        <v/>
+      </c>
+      <c r="I61" s="59">
+        <f>I24</f>
+        <v/>
+      </c>
+      <c r="J61" s="59">
+        <f>J24</f>
+        <v/>
+      </c>
+      <c r="K61" s="59">
+        <f>K24</f>
+        <v/>
+      </c>
+      <c r="L61" s="59">
+        <f>L24</f>
+        <v/>
+      </c>
+      <c r="M61" s="59">
+        <f>M24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>Total costs</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Sum of the lines above</t>
+        </is>
+      </c>
+      <c r="D62" s="59">
+        <f>D54+D55+D56+D57+D58+D59+D60+D61</f>
+        <v/>
+      </c>
+      <c r="E62" s="59">
+        <f>E54+E55+E56+E57+E58+E59+E60+E61</f>
+        <v/>
+      </c>
+      <c r="F62" s="59">
+        <f>F54+F55+F56+F57+F58+F59+F60+F61</f>
+        <v/>
+      </c>
+      <c r="G62" s="59">
+        <f>G54+G55+G56+G57+G58+G59+G60+G61</f>
+        <v/>
+      </c>
+      <c r="H62" s="59">
+        <f>H54+H55+H56+H57+H58+H59+H60+H61</f>
+        <v/>
+      </c>
+      <c r="I62" s="59">
+        <f>I54+I55+I56+I57+I58+I59+I60+I61</f>
+        <v/>
+      </c>
+      <c r="J62" s="59">
+        <f>J54+J55+J56+J57+J58+J59+J60+J61</f>
+        <v/>
+      </c>
+      <c r="K62" s="59">
+        <f>K54+K55+K56+K57+K58+K59+K60+K61</f>
+        <v/>
+      </c>
+      <c r="L62" s="59">
+        <f>L54+L55+L56+L57+L58+L59+L60+L61</f>
+        <v/>
+      </c>
+      <c r="M62" s="59">
+        <f>M54+M55+M56+M57+M58+M59+M60+M61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Revenue − total costs</t>
+        </is>
+      </c>
+      <c r="D63" s="61">
+        <f>D53-D62</f>
+        <v/>
+      </c>
+      <c r="E63" s="61">
+        <f>E53-E62</f>
+        <v/>
+      </c>
+      <c r="F63" s="61">
+        <f>F53-F62</f>
+        <v/>
+      </c>
+      <c r="G63" s="61">
+        <f>G53-G62</f>
+        <v/>
+      </c>
+      <c r="H63" s="61">
+        <f>H53-H62</f>
+        <v/>
+      </c>
+      <c r="I63" s="61">
+        <f>I53-I62</f>
+        <v/>
+      </c>
+      <c r="J63" s="61">
+        <f>J53-J62</f>
+        <v/>
+      </c>
+      <c r="K63" s="61">
+        <f>K53-K62</f>
+        <v/>
+      </c>
+      <c r="L63" s="61">
+        <f>L53-L62</f>
+        <v/>
+      </c>
+      <c r="M63" s="61">
+        <f>M53-M62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>Operating margin</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Operating income ÷ revenue</t>
+        </is>
+      </c>
+      <c r="D64" s="58">
+        <f>IFERROR(D63/D53,"")</f>
+        <v/>
+      </c>
+      <c r="E64" s="58">
+        <f>IFERROR(E63/E53,"")</f>
+        <v/>
+      </c>
+      <c r="F64" s="58">
+        <f>IFERROR(F63/F53,"")</f>
+        <v/>
+      </c>
+      <c r="G64" s="58">
+        <f>IFERROR(G63/G53,"")</f>
+        <v/>
+      </c>
+      <c r="H64" s="58">
+        <f>IFERROR(H63/H53,"")</f>
+        <v/>
+      </c>
+      <c r="I64" s="58">
+        <f>IFERROR(I63/I53,"")</f>
+        <v/>
+      </c>
+      <c r="J64" s="58">
+        <f>IFERROR(J63/J53,"")</f>
+        <v/>
+      </c>
+      <c r="K64" s="58">
+        <f>IFERROR(K63/K53,"")</f>
+        <v/>
+      </c>
+      <c r="L64" s="58">
+        <f>IFERROR(L63/L53,"")</f>
+        <v/>
+      </c>
+      <c r="M64" s="58">
+        <f>IFERROR(M63/M53,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="20" t="inlineStr">
+        <is>
+          <t>Change from baseline and true-up</t>
+        </is>
+      </c>
+      <c r="B65" s="21" t="n"/>
+      <c r="D65" s="21" t="n"/>
+      <c r="E65" s="21" t="n"/>
+      <c r="F65" s="21" t="n"/>
+      <c r="G65" s="21" t="n"/>
+      <c r="H65" s="21" t="n"/>
+      <c r="I65" s="21" t="n"/>
+      <c r="J65" s="21" t="n"/>
+      <c r="K65" s="21" t="n"/>
+      <c r="L65" s="21" t="n"/>
+      <c r="M65" s="21" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>Change in revenue</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="D66" s="59" t="n"/>
+      <c r="E66" s="59">
+        <f>E53-$D$53</f>
+        <v/>
+      </c>
+      <c r="F66" s="59">
+        <f>F53-$D$53</f>
+        <v/>
+      </c>
+      <c r="G66" s="59">
+        <f>G53-$D$53</f>
+        <v/>
+      </c>
+      <c r="H66" s="59">
+        <f>H53-$D$53</f>
+        <v/>
+      </c>
+      <c r="I66" s="59">
+        <f>I53-$D$53</f>
+        <v/>
+      </c>
+      <c r="J66" s="59">
+        <f>J53-$D$53</f>
+        <v/>
+      </c>
+      <c r="K66" s="59">
+        <f>K53-$D$53</f>
+        <v/>
+      </c>
+      <c r="L66" s="59">
+        <f>L53-$D$53</f>
+        <v/>
+      </c>
+      <c r="M66" s="59">
+        <f>M53-$D$53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>Change in total costs</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="D67" s="59" t="n"/>
+      <c r="E67" s="59">
+        <f>E62-$D$62</f>
+        <v/>
+      </c>
+      <c r="F67" s="59">
+        <f>F62-$D$62</f>
+        <v/>
+      </c>
+      <c r="G67" s="59">
+        <f>G62-$D$62</f>
+        <v/>
+      </c>
+      <c r="H67" s="59">
+        <f>H62-$D$62</f>
+        <v/>
+      </c>
+      <c r="I67" s="59">
+        <f>I62-$D$62</f>
+        <v/>
+      </c>
+      <c r="J67" s="59">
+        <f>J62-$D$62</f>
+        <v/>
+      </c>
+      <c r="K67" s="59">
+        <f>K62-$D$62</f>
+        <v/>
+      </c>
+      <c r="L67" s="59">
+        <f>L62-$D$62</f>
+        <v/>
+      </c>
+      <c r="M67" s="59">
+        <f>M62-$D$62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Change in operating income</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="D68" s="61" t="n"/>
+      <c r="E68" s="61">
+        <f>E63-$D$63</f>
+        <v/>
+      </c>
+      <c r="F68" s="61">
+        <f>F63-$D$63</f>
+        <v/>
+      </c>
+      <c r="G68" s="61">
+        <f>G63-$D$63</f>
+        <v/>
+      </c>
+      <c r="H68" s="61">
+        <f>H63-$D$63</f>
+        <v/>
+      </c>
+      <c r="I68" s="61">
+        <f>I63-$D$63</f>
+        <v/>
+      </c>
+      <c r="J68" s="61">
+        <f>J63-$D$63</f>
+        <v/>
+      </c>
+      <c r="K68" s="61">
+        <f>K63-$D$63</f>
+        <v/>
+      </c>
+      <c r="L68" s="61">
+        <f>L63-$D$63</f>
+        <v/>
+      </c>
+      <c r="M68" s="61">
+        <f>M63-$D$63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
+        <is>
+          <t>Change in operating income, %</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="D69" s="62" t="n"/>
+      <c r="E69" s="62">
+        <f>IFERROR(E68/ABS($D$63),"")</f>
+        <v/>
+      </c>
+      <c r="F69" s="62">
+        <f>IFERROR(F68/ABS($D$63),"")</f>
+        <v/>
+      </c>
+      <c r="G69" s="62">
+        <f>IFERROR(G68/ABS($D$63),"")</f>
+        <v/>
+      </c>
+      <c r="H69" s="62">
+        <f>IFERROR(H68/ABS($D$63),"")</f>
+        <v/>
+      </c>
+      <c r="I69" s="62">
+        <f>IFERROR(I68/ABS($D$63),"")</f>
+        <v/>
+      </c>
+      <c r="J69" s="62">
+        <f>IFERROR(J68/ABS($D$63),"")</f>
+        <v/>
+      </c>
+      <c r="K69" s="62">
+        <f>IFERROR(K68/ABS($D$63),"")</f>
+        <v/>
+      </c>
+      <c r="L69" s="62">
+        <f>IFERROR(L68/ABS($D$63),"")</f>
+        <v/>
+      </c>
+      <c r="M69" s="62">
+        <f>IFERROR(M68/ABS($D$63),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>Unexplained difference (must be 0)</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Change in revenue − change in costs − change in operating income</t>
+        </is>
+      </c>
+      <c r="D70" s="59">
+        <f>D66-D67-D68</f>
+        <v/>
+      </c>
+      <c r="E70" s="59">
+        <f>E66-E67-E68</f>
+        <v/>
+      </c>
+      <c r="F70" s="59">
+        <f>F66-F67-F68</f>
+        <v/>
+      </c>
+      <c r="G70" s="59">
+        <f>G66-G67-G68</f>
+        <v/>
+      </c>
+      <c r="H70" s="59">
+        <f>H66-H67-H68</f>
+        <v/>
+      </c>
+      <c r="I70" s="59">
+        <f>I66-I67-I68</f>
+        <v/>
+      </c>
+      <c r="J70" s="59">
+        <f>J66-J67-J68</f>
+        <v/>
+      </c>
+      <c r="K70" s="59">
+        <f>K66-K67-K68</f>
+        <v/>
+      </c>
+      <c r="L70" s="59">
+        <f>L66-L67-L68</f>
+        <v/>
+      </c>
+      <c r="M70" s="59">
+        <f>M66-M67-M68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>True-up</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Every change in profit is explained by a change in revenue or cost</t>
+        </is>
+      </c>
+      <c r="D71" s="63">
+        <f>IF(ABS(D70)&lt;0.5,"Balanced","Check")</f>
+        <v/>
+      </c>
+      <c r="E71" s="63">
+        <f>IF(ABS(E70)&lt;0.5,"Balanced","Check")</f>
+        <v/>
+      </c>
+      <c r="F71" s="63">
+        <f>IF(ABS(F70)&lt;0.5,"Balanced","Check")</f>
+        <v/>
+      </c>
+      <c r="G71" s="63">
+        <f>IF(ABS(G70)&lt;0.5,"Balanced","Check")</f>
+        <v/>
+      </c>
+      <c r="H71" s="63">
+        <f>IF(ABS(H70)&lt;0.5,"Balanced","Check")</f>
+        <v/>
+      </c>
+      <c r="I71" s="63">
+        <f>IF(ABS(I70)&lt;0.5,"Balanced","Check")</f>
+        <v/>
+      </c>
+      <c r="J71" s="63">
+        <f>IF(ABS(J70)&lt;0.5,"Balanced","Check")</f>
+        <v/>
+      </c>
+      <c r="K71" s="63">
+        <f>IF(ABS(K70)&lt;0.5,"Balanced","Check")</f>
+        <v/>
+      </c>
+      <c r="L71" s="63">
+        <f>IF(ABS(L70)&lt;0.5,"Balanced","Check")</f>
+        <v/>
+      </c>
+      <c r="M71" s="63">
+        <f>IF(ABS(M70)&lt;0.5,"Balanced","Check")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="20" t="inlineStr">
+        <is>
+          <t>Decision measures</t>
+        </is>
+      </c>
+      <c r="B72" s="21" t="n"/>
+      <c r="D72" s="21" t="n"/>
+      <c r="E72" s="21" t="n"/>
+      <c r="F72" s="21" t="n"/>
+      <c r="G72" s="21" t="n"/>
+      <c r="H72" s="21" t="n"/>
+      <c r="I72" s="21" t="n"/>
+      <c r="J72" s="21" t="n"/>
+      <c r="K72" s="21" t="n"/>
+      <c r="L72" s="21" t="n"/>
+      <c r="M72" s="21" t="n"/>
+    </row>
+    <row r="73" ht="28" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>Change in operating income before the cost of making the change</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="D73" s="59" t="n"/>
+      <c r="E73" s="59">
+        <f>E68+E61</f>
+        <v/>
+      </c>
+      <c r="F73" s="59">
+        <f>F68+F61</f>
+        <v/>
+      </c>
+      <c r="G73" s="59">
+        <f>G68+G61</f>
+        <v/>
+      </c>
+      <c r="H73" s="59">
+        <f>H68+H61</f>
+        <v/>
+      </c>
+      <c r="I73" s="59">
+        <f>I68+I61</f>
+        <v/>
+      </c>
+      <c r="J73" s="59">
+        <f>J68+J61</f>
+        <v/>
+      </c>
+      <c r="K73" s="59">
+        <f>K68+K61</f>
+        <v/>
+      </c>
+      <c r="L73" s="59">
+        <f>L68+L61</f>
+        <v/>
+      </c>
+      <c r="M73" s="59">
+        <f>M68+M61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" ht="28" customHeight="1">
+      <c r="A74" s="64" t="inlineStr">
+        <is>
+          <t>Most you could spend on this change and still match the comparison scenario</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>This scenario's gain before its cost − the comparison scenario's gain</t>
+        </is>
+      </c>
+      <c r="D74" s="61" t="n"/>
+      <c r="E74" s="61">
+        <f>E73-INDEX($D$73:$M$73,MATCH(wi_compare,$D$7:$M$7,0))</f>
+        <v/>
+      </c>
+      <c r="F74" s="61">
+        <f>F73-INDEX($D$73:$M$73,MATCH(wi_compare,$D$7:$M$7,0))</f>
+        <v/>
+      </c>
+      <c r="G74" s="61">
+        <f>G73-INDEX($D$73:$M$73,MATCH(wi_compare,$D$7:$M$7,0))</f>
+        <v/>
+      </c>
+      <c r="H74" s="61">
+        <f>H73-INDEX($D$73:$M$73,MATCH(wi_compare,$D$7:$M$7,0))</f>
+        <v/>
+      </c>
+      <c r="I74" s="61">
+        <f>I73-INDEX($D$73:$M$73,MATCH(wi_compare,$D$7:$M$7,0))</f>
+        <v/>
+      </c>
+      <c r="J74" s="61">
+        <f>J73-INDEX($D$73:$M$73,MATCH(wi_compare,$D$7:$M$7,0))</f>
+        <v/>
+      </c>
+      <c r="K74" s="61">
+        <f>K73-INDEX($D$73:$M$73,MATCH(wi_compare,$D$7:$M$7,0))</f>
+        <v/>
+      </c>
+      <c r="L74" s="61">
+        <f>L73-INDEX($D$73:$M$73,MATCH(wi_compare,$D$7:$M$7,0))</f>
+        <v/>
+      </c>
+      <c r="M74" s="61">
+        <f>M73-INDEX($D$73:$M$73,MATCH(wi_compare,$D$7:$M$7,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>Revenue per salesperson-year paid</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="D75" s="59">
+        <f>IFERROR(D53/D39,"")</f>
+        <v/>
+      </c>
+      <c r="E75" s="59">
+        <f>IFERROR(E53/E39,"")</f>
+        <v/>
+      </c>
+      <c r="F75" s="59">
+        <f>IFERROR(F53/F39,"")</f>
+        <v/>
+      </c>
+      <c r="G75" s="59">
+        <f>IFERROR(G53/G39,"")</f>
+        <v/>
+      </c>
+      <c r="H75" s="59">
+        <f>IFERROR(H53/H39,"")</f>
+        <v/>
+      </c>
+      <c r="I75" s="59">
+        <f>IFERROR(I53/I39,"")</f>
+        <v/>
+      </c>
+      <c r="J75" s="59">
+        <f>IFERROR(J53/J39,"")</f>
+        <v/>
+      </c>
+      <c r="K75" s="59">
+        <f>IFERROR(K53/K39,"")</f>
+        <v/>
+      </c>
+      <c r="L75" s="59">
+        <f>IFERROR(L53/L39,"")</f>
+        <v/>
+      </c>
+      <c r="M75" s="59">
+        <f>IFERROR(M53/M39,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" ht="66" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>Guardrails</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Flags results that leave known reality</t>
+        </is>
+      </c>
+      <c r="D76" s="63">
+        <f>IF(D47&gt;1,"Close rate above 100%: not possible",IF(D45&lt;=0,"Cycle must be above zero",IF(AND(D42&lt;&gt;"",D16&lt;&gt;0,D42&gt;D41),"Salespeople would hold more than they can manage: the extra opportunities are not worked",IF(AND(D42&lt;&gt;"",D15&gt;0,D42&lt;=v_opportunities_capacity),"Capacity increase has no effect: salespeople already hold fewer opportunities than they can manage",IF(AND(D42="",D16&lt;&gt;0),"No pipeline data on tab 1: this change has no effect until opportunities held is entered",IF(AND(D28=0,OR(D12&lt;&gt;0,_xlfn.ISFORMULA(D12))),"No open territories entered on tab 1 yet: this change has no effect","OK"))))))</f>
+        <v/>
+      </c>
+      <c r="E76" s="63">
+        <f>IF(E47&gt;1,"Close rate above 100%: not possible",IF(E45&lt;=0,"Cycle must be above zero",IF(AND(E42&lt;&gt;"",E16&lt;&gt;0,E42&gt;E41),"Salespeople would hold more than they can manage: the extra opportunities are not worked",IF(AND(E42&lt;&gt;"",E15&gt;0,E42&lt;=v_opportunities_capacity),"Capacity increase has no effect: salespeople already hold fewer opportunities than they can manage",IF(AND(E42="",E16&lt;&gt;0),"No pipeline data on tab 1: this change has no effect until opportunities held is entered",IF(AND(E28=0,OR(E12&lt;&gt;0,_xlfn.ISFORMULA(E12))),"No open territories entered on tab 1 yet: this change has no effect","OK"))))))</f>
+        <v/>
+      </c>
+      <c r="F76" s="63">
+        <f>IF(F47&gt;1,"Close rate above 100%: not possible",IF(F45&lt;=0,"Cycle must be above zero",IF(AND(F42&lt;&gt;"",F16&lt;&gt;0,F42&gt;F41),"Salespeople would hold more than they can manage: the extra opportunities are not worked",IF(AND(F42&lt;&gt;"",F15&gt;0,F42&lt;=v_opportunities_capacity),"Capacity increase has no effect: salespeople already hold fewer opportunities than they can manage",IF(AND(F42="",F16&lt;&gt;0),"No pipeline data on tab 1: this change has no effect until opportunities held is entered",IF(AND(F28=0,OR(F12&lt;&gt;0,_xlfn.ISFORMULA(F12))),"No open territories entered on tab 1 yet: this change has no effect","OK"))))))</f>
+        <v/>
+      </c>
+      <c r="G76" s="63">
+        <f>IF(G47&gt;1,"Close rate above 100%: not possible",IF(G45&lt;=0,"Cycle must be above zero",IF(AND(G42&lt;&gt;"",G16&lt;&gt;0,G42&gt;G41),"Salespeople would hold more than they can manage: the extra opportunities are not worked",IF(AND(G42&lt;&gt;"",G15&gt;0,G42&lt;=v_opportunities_capacity),"Capacity increase has no effect: salespeople already hold fewer opportunities than they can manage",IF(AND(G42="",G16&lt;&gt;0),"No pipeline data on tab 1: this change has no effect until opportunities held is entered",IF(AND(G28=0,OR(G12&lt;&gt;0,_xlfn.ISFORMULA(G12))),"No open territories entered on tab 1 yet: this change has no effect","OK"))))))</f>
+        <v/>
+      </c>
+      <c r="H76" s="63">
+        <f>IF(H47&gt;1,"Close rate above 100%: not possible",IF(H45&lt;=0,"Cycle must be above zero",IF(AND(H42&lt;&gt;"",H16&lt;&gt;0,H42&gt;H41),"Salespeople would hold more than they can manage: the extra opportunities are not worked",IF(AND(H42&lt;&gt;"",H15&gt;0,H42&lt;=v_opportunities_capacity),"Capacity increase has no effect: salespeople already hold fewer opportunities than they can manage",IF(AND(H42="",H16&lt;&gt;0),"No pipeline data on tab 1: this change has no effect until opportunities held is entered",IF(AND(H28=0,OR(H12&lt;&gt;0,_xlfn.ISFORMULA(H12))),"No open territories entered on tab 1 yet: this change has no effect","OK"))))))</f>
+        <v/>
+      </c>
+      <c r="I76" s="63">
+        <f>IF(I47&gt;1,"Close rate above 100%: not possible",IF(I45&lt;=0,"Cycle must be above zero",IF(AND(I42&lt;&gt;"",I16&lt;&gt;0,I42&gt;I41),"Salespeople would hold more than they can manage: the extra opportunities are not worked",IF(AND(I42&lt;&gt;"",I15&gt;0,I42&lt;=v_opportunities_capacity),"Capacity increase has no effect: salespeople already hold fewer opportunities than they can manage",IF(AND(I42="",I16&lt;&gt;0),"No pipeline data on tab 1: this change has no effect until opportunities held is entered",IF(AND(I28=0,OR(I12&lt;&gt;0,_xlfn.ISFORMULA(I12))),"No open territories entered on tab 1 yet: this change has no effect","OK"))))))</f>
+        <v/>
+      </c>
+      <c r="J76" s="63">
+        <f>IF(J47&gt;1,"Close rate above 100%: not possible",IF(J45&lt;=0,"Cycle must be above zero",IF(AND(J42&lt;&gt;"",J16&lt;&gt;0,J42&gt;J41),"Salespeople would hold more than they can manage: the extra opportunities are not worked",IF(AND(J42&lt;&gt;"",J15&gt;0,J42&lt;=v_opportunities_capacity),"Capacity increase has no effect: salespeople already hold fewer opportunities than they can manage",IF(AND(J42="",J16&lt;&gt;0),"No pipeline data on tab 1: this change has no effect until opportunities held is entered",IF(AND(J28=0,OR(J12&lt;&gt;0,_xlfn.ISFORMULA(J12))),"No open territories entered on tab 1 yet: this change has no effect","OK"))))))</f>
+        <v/>
+      </c>
+      <c r="K76" s="63">
+        <f>IF(K47&gt;1,"Close rate above 100%: not possible",IF(K45&lt;=0,"Cycle must be above zero",IF(AND(K42&lt;&gt;"",K16&lt;&gt;0,K42&gt;K41),"Salespeople would hold more than they can manage: the extra opportunities are not worked",IF(AND(K42&lt;&gt;"",K15&gt;0,K42&lt;=v_opportunities_capacity),"Capacity increase has no effect: salespeople already hold fewer opportunities than they can manage",IF(AND(K42="",K16&lt;&gt;0),"No pipeline data on tab 1: this change has no effect until opportunities held is entered",IF(AND(K28=0,OR(K12&lt;&gt;0,_xlfn.ISFORMULA(K12))),"No open territories entered on tab 1 yet: this change has no effect","OK"))))))</f>
+        <v/>
+      </c>
+      <c r="L76" s="63">
+        <f>IF(L47&gt;1,"Close rate above 100%: not possible",IF(L45&lt;=0,"Cycle must be above zero",IF(AND(L42&lt;&gt;"",L16&lt;&gt;0,L42&gt;L41),"Salespeople would hold more than they can manage: the extra opportunities are not worked",IF(AND(L42&lt;&gt;"",L15&gt;0,L42&lt;=v_opportunities_capacity),"Capacity increase has no effect: salespeople already hold fewer opportunities than they can manage",IF(AND(L42="",L16&lt;&gt;0),"No pipeline data on tab 1: this change has no effect until opportunities held is entered",IF(AND(L28=0,OR(L12&lt;&gt;0,_xlfn.ISFORMULA(L12))),"No open territories entered on tab 1 yet: this change has no effect","OK"))))))</f>
+        <v/>
+      </c>
+      <c r="M76" s="63">
+        <f>IF(M47&gt;1,"Close rate above 100%: not possible",IF(M45&lt;=0,"Cycle must be above zero",IF(AND(M42&lt;&gt;"",M16&lt;&gt;0,M42&gt;M41),"Salespeople would hold more than they can manage: the extra opportunities are not worked",IF(AND(M42&lt;&gt;"",M15&gt;0,M42&lt;=v_opportunities_capacity),"Capacity increase has no effect: salespeople already hold fewer opportunities than they can manage",IF(AND(M42="",M16&lt;&gt;0),"No pipeline data on tab 1: this change has no effect until opportunities held is entered",IF(AND(M28=0,OR(M12&lt;&gt;0,_xlfn.ISFORMULA(M12))),"No open territories entered on tab 1 yet: this change has no effect","OK"))))))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:M2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D71:M71">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"Balanced"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"Check"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D76:M76">
+    <cfRule type="expression" priority="3" dxfId="1">
+      <formula>D76&lt;&gt;"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Year one,Steady state"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>$E$7:$M$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>